--- a/iTrack/scraped_jobs.xlsx
+++ b/iTrack/scraped_jobs.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH12"/>
+  <dimension ref="A1:AH27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -607,39 +607,47 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>li-4346667822</t>
+          <t>in-225d4b3b461348b2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>indeed</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4346667822</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>https://ph.indeed.com/viewjob?jk=225d4b3b461348b2</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://intrepid.bamboohr.com/careers/1521?source=indeed&amp;src=indeed&amp;postedDate=2026-01-11</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Tech Svc Desk - L1</t>
+          <t>Finance Intern (Required Internship Only)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Unisys</t>
+          <t>Intrepid</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Manila, National Capital Region, Philippines</t>
+          <t>Manila, P00, PH</t>
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>46022</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
+        <v>46033</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>internship</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -652,11 +660,53 @@
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>**Who we are**
+Intrepid Asia is a leading Ecommerce and Digital Solutions Provider in South East Asia. We offer end\-to\-end omni\-channel ecommerce management, Livestreaming, Video production \&amp; Affiliate Management for Social Commerce plus full funnel Digital Marketing Services and advanced Market Intelligence, all powered by state of the art inhouse Technology to our client base of leading international brands across all key marketplaces and social platforms in all 6 SEA countries. Brands love our regional presence, our excellent data\-driven and growth\-focused services which are enabled by the strongest team in the industry, and our advanced marketing and tech capabilities.
+We are growing rapidly and as the exclusive partner of Flywheel in SEA, we offer many exciting opportunities to work with leading brands across multiple categories and key industry players. By joining us, you will work on the cutting edge of digital and social commerce in SEA, and experience what it takes to drive a successful ecommerce business end\-to\-end.
+ **The team you will be part of**
+Our Finance Team is at the core of every major decision we make. We don’t just keep the books — we shape the direction of the business. By delivering on financial insights, strategic analysis, and data\-driven recommendations, the team plays a critical role in guiding growth and ensuring long\-term success. From planning and forecasting to optimizing performance and supporting key commercial initiatives, Our Finance team is a key partner across every function. With a strong focus on integrity, accuracy, and collaboration, its goal is to ensure the company remains financially strong, agile, and ready for the future.
+ **The part you will play**
+We are looking for a Finance Intern who will be an active contributor to our Finance team. This role will report directly to the Senior Accountant and will provide hands\-on exposure to day\-to\-day finance operations, including accounting support, documentation, and financial administrative tasks. You will work closely with the Finance team and gain practical experience in a fast\-paced ecommerce environment.
+ **As a Finance Intern, you will take charge of**
+* Assisting in the preparation and issuance of retail sales invoices
+* Filing, organizing, and maintaining accounting and finance documents
+* Supporting liquidation, reimbursement, and expense claims processes
+* Assisting in accounts receivable and accounts payable tracking
+* Helping ensure completeness and accuracy of financial records
+* Supporting month\-end and ad\-hoc finance reporting tasks
+* Coordinating with internal teams regarding finance\-related documentation
+* Performing other administrative and operational finance tasks as assigned
+**What we are looking for \- the ideal profile**
+* Currently pursuing a Bachelor’s degree in Finance, Accounting, Management Accounting, Business Administration, or a related course
+* Internship **must be a required internship** as part of the university curriculum
+* Able to commit for the full required internship period (minimum duration as required by school)
+* Basic understanding of accounting and finance principles
+* Proficient in Microsoft Suite and Google Workspace
+* Strong attention to detail and good organizational skills
+* Able to handle confidential financial information with integrity
+* Willing to learn, proactive, and able to work in a team environment
+**In return, you will be getting**
+* Join an all\-star Finance team which continues to raise the bar, with systems and processes (and company stability) at the level of sophistication of a small multinational, but with a 'start\-up' spirit of innovation and continuous improvement in an ever\-evolving world
+* In terms of learning opportunities, our organization is second to none. You will get to work on a variety of business models across many different clients as if we are 5 companies in one, and everyone is involved in projects to drive further improvement.
+* Regional teams and country Finance teams collaborate closely to ensure all finance aspects of our business are optimized, giving you a wide exposure and enhanced learning curve in a close\-knit and supportive team
+**We also offer**
+**Best of Both Worlds**
+We are a scale up: the sophistication of a small multinational, with the agility of a start\-up. This means you get to work on cutting\-edge projects, and besides your 'standard' job description, we love to see you show entrepreneurial initiative and want to see your take on how you can take your role and our company to the next level. Good ideas get implemented. You are the master of your own destiny.
+ **Culture that Brings Out the Best**
+At Intrepid, culture is not just a buzzword, it is what we practice at work every day. We believe in collaboration over competition, transparency over politics, and willingness to learn over ego. You will be part of a team where people genuinely support one another, celebrate wins together, and face challenges head\-on as one. We put our all into the work but we balance it with fun, whether that is through team lunches, after\-work hangouts, events or shared laughter in the office. This is a place where you can thrive professionally while having a great time.
+ **Grow Without Limits**
+Learning at Intrepid is constant and dynamic. You will have access to formal training through face\-to\-face sessions, coaching and our very own Intrepid Academy. On top of that, real\-world experience such as leading clients, working with advanced tech, and mastering best\-in\-class processes will accelerate your growth every step of the way. Surrounded by a talented team that raises the bar daily, in a rapidly growing and ever\-expanding business, the opportunities for your development are endless.
+ **Rewarding You Right**
+We believe great work deserves great rewards at Intrepid. That’s why we offer competitive compensation and generous benefits, including comprehensive insurance and ample leave, to support you both in and out of the workplace. We want you to feel valued, cared for, and empowered to bring your best self to work every day.
+ *Note: We will not be accepting any unsolicited resumes or CVs from headhunting or recruitment agencies at this point. Any CVs or profiles shared with us will not be entertained, and in the event of dispute, Intrepid will not be liable for any material compensation to third parties*</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/unisys</t>
+          <t>https://ph.indeed.com/cmp/Intrepid-1c14aa57</t>
         </is>
       </c>
       <c r="W2" t="inlineStr"/>
@@ -675,39 +725,47 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>li-4346725522</t>
+          <t>in-2dbb6c5d669cc55a</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>indeed</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4346725522</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>https://ph.indeed.com/viewjob?jk=2dbb6c5d669cc55a</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://intrepid.bamboohr.com/careers/1520?source=indeed&amp;src=indeed&amp;postedDate=2026-01-11</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Evening Cleaning Tech</t>
+          <t>Human Resources Intern (Required Internship Only)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Office Pride Franchise Opportunity</t>
+          <t>Intrepid</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Quezon City, National Capital Region, Philippines</t>
+          <t>Manila, P00, PH</t>
         </is>
       </c>
       <c r="H3" s="2" t="n">
-        <v>46022</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
+        <v>46033</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>internship</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
@@ -720,11 +778,53 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>**Who we are**
+Intrepid Asia is a leading Ecommerce and Digital Solutions Provider in South East Asia. We offer end\-to\-end omni\-channel ecommerce management, Livestreaming, Video production \&amp; Affiliate Management for Social Commerce plus full funnel Digital Marketing Services and advanced Market Intelligence, all powered by state of the art inhouse Technology to our client base of leading international brands across all key marketplaces and social platforms in all 6 SEA countries. Brands love our regional presence, our excellent data\-driven and growth\-focused services which are enabled by the strongest team in the industry, and our advanced marketing and tech capabilities.
+We are growing rapidly and as the exclusive partner of Flywheel in SEA, we offer many exciting opportunities to work with leading brands across multiple categories and key industry players. By joining us, you will work on the cutting edge of digital and social commerce in SEA, and experience what it takes to drive a successful ecommerce business end\-to\-end.
+ **The team you will be part of**
+Our Talent \&amp; People Team is the heartbeat of our organization \- championing a culture where people thrive and potential is unlocked. From attracting top talent and shaping employee experiences to driving development, engagement, and retention, the team plays a strategic role in building and maintaining a high\-performing, empowered workforce. We are here to grow with the business and for the people behind it.
+ **The part you will play**
+We are looking for a Human Resources Intern who will be an active contributor to our People Operations team. This role will report directly to our People Operations Specialist and will provide hands\-on exposure to various HR functions, supporting daily operations and ongoing initiatives.
+ **As an HR Intern, you will take charge of**
+* Assisting in preparing orientation materials and schedules for new employees
+* Helping maintain employee records and ensure confidentiality
+* Supporting the resolution of employee queries and concerns
+* Assisting in organizing employee engagement activities and events
+* Assisting in maintaining and updating HR 201 files and database
+* Assisting in the preparation of HR\-related reports and documents as needed
+* Assisting in coordinating training sessions and workshops
+* Participating in the development of training materials
+* Providing general administrative support to the HR department
+* Participating in HR projects and initiatives as assigned
+**What we are looking for \- the ideal profile**
+* Currently pursuing a degree in Human Resource Management, Psychology, or other related fields, **with an internship requirement**
+* Strong written and verbal communication skills
+* Proficient in MS Office applications and Google Workspace
+* Detail\-oriented with the ability to handle sensitive and confidential information
+* Strong organizational skills with the ability to manage multiple tasks and meet deadlines
+**In return, you will be getting**
+* Tackling the sophisticated people's challenges in the rapidly evolving e\-commerce landscape with data insights and innovative solutions.
+* You will be joining an all\-star People Team that consistently raises the bar by combining the systems and processes of a small multinational with the collaborative, innovative, and agile spirit of a startup in an ever\-evolving world.
+* With our team’s rapid growth and the People Team launching new initiatives to enhance both employee experience and performance, you will benefit from a wide range of opportunities for development. Our structured learning programs covering both functional skills and broader growth are designed to support you at every stage of your journey
+* Our supportive culture and close collaboration between regional and local teams create a close\-knit work environment which many in our team love and thrive in
+**We also offer**
+**Best of Both Worlds**
+We are a scale up: the sophistication of a small multinational, with the agility of a start\-up. This means you get to work on cutting\-edge projects, and besides your 'standard' job description, we love to see you show entrepreneurial initiative and want to see your take on how you can take your role and our company to the next level. Good ideas get implemented. You are the master of your own destiny.
+ **Culture that Brings Out the Best**
+At Intrepid, culture is not just a buzzword, it is what we practice at work every day. We believe in collaboration over competition, transparency over politics, and willingness to learn over ego. You will be part of a team where people genuinely support one another, celebrate wins together, and face challenges head\-on as one. We put our all into the work but we balance it with fun, whether that is through team lunches, after\-work hangouts, events or shared laughter in the office. This is a place where you can thrive professionally while having a great time.
+ **Grow Without Limits**
+Learning at Intrepid is constant and dynamic. You will have access to formal training through face\-to\-face sessions, coaching and our very own Intrepid Academy. On top of that, real\-world experience such as leading clients, working with advanced tech, and mastering best\-in\-class processes will accelerate your growth every step of the way. Surrounded by a talented team that raises the bar daily, in a rapidly growing and ever\-expanding business, the opportunities for your development are endless.
+ **Rewarding You Right**
+We believe great work deserves great rewards at Intrepid. That’s why we offer competitive compensation and generous benefits, including comprehensive insurance and ample leave, to support you both in and out of the workplace. We want you to feel valued, cared for, and empowered to bring your best self to work every day.
+ *Note: We will not be accepting any unsolicited resumes or CVs from headhunting or recruitment agencies at this point. Any CVs or profiles shared with us will not be entertained, and in the event of dispute, Intrepid will not be liable for any material compensation to third parties*</t>
+        </is>
+      </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/office-pride-franchise-opportunity</t>
+          <t>https://ph.indeed.com/cmp/Intrepid-1c14aa57</t>
         </is>
       </c>
       <c r="W3" t="inlineStr"/>
@@ -743,39 +843,47 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>li-4308717661</t>
+          <t>in-f1e13e490a93b540</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>indeed</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4308717661</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>https://ph.indeed.com/viewjob?jk=f1e13e490a93b540</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>http://ph.indeed.com/job/it-programming-intern-f1e13e490a93b540</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Technician</t>
+          <t>IT / Programming Intern</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Konecranes</t>
+          <t>Lucky Boba</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pampanga, Central Luzon, Philippines</t>
+          <t>Sangandaan, P00, PH</t>
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>46022</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
+        <v>46032</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>temporary, internship</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -787,12 +895,54 @@
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>luckyboba.hr@gmail.com</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>**We're Hiring Interns!**
+Are you passionate about technology and eager to gain  
+hands\-on experience in IT and programming? Join our team and kickstart your  
+career!
+**Position:** IT / Programming Intern
+**Who We’re Looking For:**  
+**Students currently pursuing:**
+IT Programming  
+Computer Engineering  
+Computer Science  
+Any Programming\-related course
+**What You’ll Do:**  
+Assist in software development and coding projects  
+Support IT operations and system maintenance  
+Collaborate with our tech team on real\-world projects  
+Learn best practices in programming, debugging, and testing
+**What We’re Looking For:**  
+Strong interest in programming and technology  
+Basic knowledge of programming languages (e.g., Java, Python, C\#, or JavaScript)  
+Eagerness to learn and take on challenges  
+Good communication and teamwork skills
+**Perks \&amp; Benefits:**  
+Hands\-on experience in real projects  
+Mentorship from experienced developers  
+Flexible working hours  
+Certificate of Internship upon completion
+**How to Apply:**  
+Submit your CV \&amp; Portfolio**: luckyboba.hr@gmail.com**
+Start your tech journey with us!
+Job Types: Temporary, OJT (On the job training)  
+Contract length: 3 months
+Benefits:
+* Flexible schedule
+* Flextime
+Work Location: In person</t>
+        </is>
+      </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>https://fi.linkedin.com/company/konecranes</t>
+          <t>https://ph.indeed.com/cmp/Lucky-Boba-1</t>
         </is>
       </c>
       <c r="W4" t="inlineStr"/>
@@ -811,39 +961,47 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>li-4329605575</t>
+          <t>in-87c8416ce707a201</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>indeed</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4329605575</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>https://ph.indeed.com/viewjob?jk=87c8416ce707a201</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>http://ph.indeed.com/job/business-development-intern-paid-ojt-87c8416ce707a201</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Reefer Technician</t>
+          <t>Business Development Intern (Paid OJT)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>IRS Eastern, Inc.</t>
+          <t>Achieve Without Borders, Inc. (AWB)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Malabon, National Capital Region, Philippines</t>
+          <t>Makati, P00, PH</t>
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>46021</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
+        <v>46032</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>internship</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -856,16 +1014,63 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>**About the Role:**  
+If you’ve ever wanted to learn how to charm clients, close deals, and sound smart while doing it, this one’s for you. Achieve Without Borders, Inc. (AWB) is opening its doors to aspiring sales superheroes who are ready to roll up their sleeves, dive into the business world, and make things happen with free lunch to fuel the hustle.
+**What You’ll Be Doing:**
+* Help our sales team turn leads into happy clients (and happy clients into loyal ones).
+* Assist in making presentations that wow, not zzz.
+* Keep our CRM up to date because organized data equals world domination.
+* Join team huddles, pitch your ideas, and learn the fine art of selling without sounding salesy.
+* Track leads, send follow\-ups, and help us build relationships that last longer than most New Year’s resolutions.
+**Who You Are:**
+* A student in Business, Marketing, or Communications (or someone who just loves making connections).
+* Confident, proactive, and just the right amount of persuasive.
+* Knows how to use Microsoft Office (and maybe even CRM tools if you’re feeling fancy).
+* Detail\-oriented and professional, even when you’re having fun.
+* **Makati bound.**
+**Why Join AWB?**
+* Real\-world experience with mentors who’ve been there, sold that.
+* Paid training and free meals because good ideas need fuel.
+* A chance to grow your career in tech\-driven business development.
+* **Perform well, and we might just hire you for real.**
+**ABOUT ACHIEVE WITHOUT BORDERS (AWB)** 
+Achieve Without Borders Inc. (AWB) is a Philippine\-based IT solutions company headquartered in Makati City. We are a **Gold Odoo Partner and Google Partner**, dedicated to helping Filipino businesses streamline operations and scale through ERP, cloud, and digital transformation solutions.
+Our expertise spans ERP systems (Odoo, NetSuite), cloud platforms (Google Cloud), and enterprise productivity tools (Microsoft 365, Google Workspace). We combine business insight and technology to deliver smart, integrated systems that empower organizations to work smarter and grow faster.
+Job Type: OJT (On the job training)  
+Contract length: 3 months
+Benefits:
+* Paid training
+* Promotion to permanent employee
+* Staff meals provided
+Work Location: In person</t>
+        </is>
+      </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
-          <t>https://ph.linkedin.com/company/irs-eastern-inc</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
+          <t>https://ph.indeed.com/cmp/Achieve-Without-Borders,-Inc.-(awb)</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>https://d2q79iu7y748jz.cloudfront.net/s/_squarelogo/256x256/5108215db8072827f110d419c3f8313d</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>https://www.achievewithoutborders.com</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2029 Gen Mascardo Street
+    Barangay Bangkal
+    Makati City MM
+    Philippines</t>
+        </is>
+      </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
@@ -879,39 +1084,47 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>li-4340991467</t>
+          <t>in-b20557a09f0fdf0f</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>indeed</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4340991467</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>https://ph.indeed.com/viewjob?jk=b20557a09f0fdf0f</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>http://ph.indeed.com/job/sales-and-marketing-intern-paid-ojt-b20557a09f0fdf0f</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tech Coord, Fund Acctng</t>
+          <t>Sales and Marketing Intern (Paid OJT)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Northern Trust</t>
+          <t>Achieve Without Borders, Inc. (AWB)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Manila, National Capital Region, Philippines</t>
+          <t>Makati, P00, PH</t>
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>46021</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
+        <v>46032</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>internship</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -924,16 +1137,67 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>**Be the Hype Behind the Tech**
+Can you sell sand in a desert, or at least convince your friends to join your group project?  
+Do you scroll through ads and think, "*I could totally write something better*"?  
+If so, Achieve Without Borders Inc. (AWB) wants you on our team as our next **Sales and Marketing Intern.**
+We are a Gold Odoo Partner, Google Partner, and an all\-around IT wizard squad that helps businesses modernize through ERP, Cloud, and Network Solutions. Translation: we make companies smarter, faster, and slightly cooler.
+Now, we need creative minds who can tell that story to the world.
+**What You’ll Be Doing (a.k.a. How You’ll Look Busy on LinkedIn)**
+* Cook up digital marketing campaigns that actually make people stop scrolling.
+* Turn coffee and creativity into engaging social media content, blogs, and visuals.
+* Help launch webinars, events, and promos that make our brand shine brighter than your screen’s blue light.
+* Research market trends like a detective with Wi\-Fi.
+* Join sales and marketing projects that connect our tech magic to real business growth.
+* Collaborate with awesome people (yes, we’re biased).
+**What We’re Looking For**
+* Currently taking up Marketing, Business, Communications, or something equally awesome.
+* Fluent in English, creativity, and Google Workspace.
+* Knows a thing or two about social media marketing, content creation, and branding.
+* Canva or Adobe familiarity equals instant brownie points.
+* Organized, proactive, and allergic to boredom.
+* **Can join us onsite in Makati City.**
+**What’s In It For You**
+* Real\-world experience in digital marketing, sales strategy, and tech branding.
+* Mentorship from professionals who actually care about your growth.
+* Exposure to ERP, cloud, and network technologies (a.k.a. resume gold).
+* **Paid training and free daily lunch (yes, free).**
+* A shot at becoming part of the AWB family after your internship.
+Job Type: OJT (On the job training)  
+Contract length: 3 months
+Benefits:
+* Paid training
+* Promotion to permanent employee
+* Staff meals provided
+Work Location: In person</t>
+        </is>
+      </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/northern-trust</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
+          <t>https://ph.indeed.com/cmp/Achieve-Without-Borders,-Inc.-(awb)</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>https://d2q79iu7y748jz.cloudfront.net/s/_squarelogo/256x256/5108215db8072827f110d419c3f8313d</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>https://www.achievewithoutborders.com</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2029 Gen Mascardo Street
+    Barangay Bangkal
+    Makati City MM
+    Philippines</t>
+        </is>
+      </c>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
@@ -947,56 +1211,104 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>li-4336353053</t>
+          <t>in-14ad7cd35cfbb3dc</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>indeed</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4336353053</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>https://ph.indeed.com/viewjob?jk=14ad7cd35cfbb3dc</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>http://ph.indeed.com/job/business-development-intern-14ad7cd35cfbb3dc</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Service Technical Support IX</t>
+          <t>Business Development Intern</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vertiv</t>
+          <t>Founders Launchpad</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Mandaluyong, National Capital Region, Philippines</t>
+          <t>Makati, P00, PH</t>
         </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>46021</v>
-      </c>
-      <c r="I7" t="inlineStr"/>
+        <v>46031</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>parttime, internship</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>**Job Summary**
+As an **Analyst Intern**, you will work hands\-on with one of our ventures to drive growth through sales pipeline development, GTM strategy execution, and strategic partnerships—taking a founder's mindset while supporting operational initiatives and growth experiments in a fast\-paced startup environment.
+**Job Responsibilities**
+**Business Development for a Venture**
+* **Market Expansion:** Support sales pipeline building, customer outreach, and partnerships for one of our ventures.
+* **Go\-to\-Market Execution:** Assist in building and executing GTM strategies, including messaging, materials, CRM management, and lead generation.
+* **Growth Experiments:** Test and analyze marketing, sales, and operational experiments to help scale the venture.
+* **Operations Support:** Collaborate with the venture’s founders on internal tools, process design, and strategic projects as needed.
+**Qualifications**
+* Currently enrolled in a Bachelor's degree program, preferably in their third or fourth year, with a focus on Business, Finance, Economics, or a related field.
+* Prior internship experience or relevant coursework is a plus, but not required.
+* Strong analytical skills with the ability to break down problems and use data to drive decisions.
+* Proven initiative and comfort with ambiguity — you are resourceful, solutions\-driven, and thrive in fast\-paced environments.
+* Deep curiosity about startups, innovation, and building from 0 to 1\.
+* Excellent written and verbal communication skills.
+* A hands\-on, founder\-like mentality — you’re not afraid to take ownership.
+* Available to commit to a minimum 3\-month internship, with potential for extension into a long\-term internship or full\-time opportunity.
+**Bonus Points**
+* Familiarity with tools like Notion, Airtable, Monday.com, Hubspot, or SQL.
+* Prior startup experience.
+* Passion for a specific domain such as fintech, logistics, healthtech, or consumer tech.
+**Why Work with Us?**
+* Work with a young, passionate, and fun team
+* We offer a diverse and international work environment
+* Hybrid exposure to venture capital and startup building — unique experience for future founders or operators.
+* Mentorship from experienced founders and operators.
+* A high\-growth environment with ownership and learning from day one.
+Job Types: Part\-time, OJT (On the job training), Fresh graduate  
+Contract length: 3 months
+Pay: Php5,000\.00 \- Php10,000\.00 per month
+Expected hours: 30 – 40 per week
+Benefits:
+* Flexible schedule
+* Flextime
+* Paid training
+* Work from home
+Work Location: In person</t>
+        </is>
+      </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/vertiv</t>
+          <t>https://ph.indeed.com/cmp/Founders-Launchpad</t>
         </is>
       </c>
       <c r="W7" t="inlineStr"/>
@@ -1015,7 +1327,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>li-4326334571</t>
+          <t>li-4345212547</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1025,27 +1337,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4326334571</t>
+          <t>https://www.linkedin.com/jobs/view/4345212547</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>On Site Service Technician - Level I</t>
+          <t>Deskside Technician</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cummins Asia Pacific</t>
+          <t>Stefanini North America and APAC</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Laguna, Calabarzon, Philippines</t>
+          <t>Pasay, National Capital Region, Philippines</t>
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>46021</v>
+        <v>46032</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
@@ -1064,7 +1376,7 @@
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>https://au.linkedin.com/company/cummins-asiapacific</t>
+          <t>https://br.linkedin.com/company/stefanini-na-apac</t>
         </is>
       </c>
       <c r="W8" t="inlineStr"/>
@@ -1083,7 +1395,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>li-4336403679</t>
+          <t>li-4334598816</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1093,27 +1405,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4336403679</t>
+          <t>https://www.linkedin.com/jobs/view/4334598816</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Senior Technician, Reliability</t>
+          <t>Service Technician Castilla y León</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Allegro MicroSystems</t>
+          <t>Vestas</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>National Capital Region, Philippines</t>
+          <t>Buenavista, Western Visayas, Philippines</t>
         </is>
       </c>
       <c r="H9" s="2" t="n">
-        <v>46021</v>
+        <v>46032</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
@@ -1132,7 +1444,7 @@
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/allegro-microsystems</t>
+          <t>https://dk.linkedin.com/company/vestas</t>
         </is>
       </c>
       <c r="W9" t="inlineStr"/>
@@ -1151,7 +1463,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>li-4329620923</t>
+          <t>li-4350286936</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1161,18 +1473,18 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4329620923</t>
+          <t>https://www.linkedin.com/jobs/view/4350286936</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Air Condition Technician</t>
+          <t>Technician I, Managed Sevices</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ardenhills Suites Corporation</t>
+          <t>Copeland</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1181,7 +1493,7 @@
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>46020</v>
+        <v>46032</v>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
@@ -1200,7 +1512,7 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>https://ph.linkedin.com/company/ardenhillssuites</t>
+          <t>https://www.linkedin.com/company/copeland</t>
         </is>
       </c>
       <c r="W10" t="inlineStr"/>
@@ -1219,7 +1531,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>li-4336896543</t>
+          <t>li-4350237071</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1229,26 +1541,28 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4336896543</t>
+          <t>https://www.linkedin.com/jobs/view/4350237071</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Back-end Technical Lead</t>
+          <t>Technician I, Managed Services</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cebu Pacific Air</t>
+          <t>Copeland</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pasay, National Capital Region, Philippines</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Quezon City, National Capital Region, Philippines</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>46032</v>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
@@ -1266,7 +1580,7 @@
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
-          <t>https://ph.linkedin.com/company/cebupacificair</t>
+          <t>https://www.linkedin.com/company/copeland</t>
         </is>
       </c>
       <c r="W11" t="inlineStr"/>
@@ -1285,7 +1599,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>li-4346786201</t>
+          <t>li-4350187030</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1295,22 +1609,28 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4346786201</t>
+          <t>https://www.linkedin.com/jobs/view/4350187030</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Japanese Tech Bilingual – Java Spring Boot</t>
+          <t>Technician I, Managed Services</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>PROTALENTNEXUS CONSULTING</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+          <t>Copeland</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Quezon City, National Capital Region, Philippines</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>46032</v>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
@@ -1328,7 +1648,7 @@
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
-          <t>https://ng.linkedin.com/company/protalentnexus</t>
+          <t>https://www.linkedin.com/company/copeland</t>
         </is>
       </c>
       <c r="W12" t="inlineStr"/>
@@ -1344,6 +1664,1012 @@
       <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>li-4359465790</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>linkedin</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4359465790</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Platform Technician I</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>BlueVoyant</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Manila, National Capital Region, Philippines</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>46031</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="b">
+        <v>0</v>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bluevoyant</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>li-4332222982</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>linkedin</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4332222982</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Technical Services Technician</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Datumstruct Philippines, Inc.</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Makati, National Capital Region, Philippines</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>46031</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="b">
+        <v>0</v>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>https://ph.linkedin.com/company/datumstructph</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>li-4314154195</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>linkedin</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4314154195</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026 Data Center Technician Intern</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Amazon Web Services (AWS)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Bolinao, Ilocos Region, Philippines</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>46031</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="b">
+        <v>0</v>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/amazon-web-services</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>li-4331574126</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>linkedin</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4331574126</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Multi-Skilled Technician - Makati</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>CBRE Asia Pacific</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Makati, National Capital Region, Philippines</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>46031</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="b">
+        <v>0</v>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>https://sg.linkedin.com/company/cbre-asia-pacific</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>li-4352057410</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>linkedin</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4352057410</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Associate, Technical Services</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vena Group</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Ilocos Region, Philippines</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>46031</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>https://sg.linkedin.com/company/venagroup</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>li-4359761815</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>linkedin</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4359761815</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Technician I - Reliability</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Microchip Technology Inc.</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Davao, Davao Region, Philippines</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>46031</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="b">
+        <v>0</v>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/microchip-technology</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>li-4359761816</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>linkedin</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4359761816</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Technician I - Reliability</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Microchip Technology Inc.</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Davao, Davao Region, Philippines</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>46031</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="b">
+        <v>0</v>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/microchip-technology</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>li-4359611660</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>linkedin</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4359611660</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Multi-Skilled Technician</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>JLL</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Makati, National Capital Region, Philippines</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>46031</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="b">
+        <v>0</v>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/jll</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>li-4358913747</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>linkedin</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4358913747</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Tech Svc Desk</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Unisys</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Manila, National Capital Region, Philippines</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>46030</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="b">
+        <v>0</v>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/unisys</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>li-4358576241</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>linkedin</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4358576241</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sr Tech Svc Desk</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Unisys</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Manila, National Capital Region, Philippines</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>46030</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="b">
+        <v>0</v>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/unisys</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>li-4359757191</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>linkedin</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4359757191</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Medewerker Technische Dienst</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Stayokay</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Bacnotan, Ilocos Region, Philippines</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>https://nl.linkedin.com/company/stayokay</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>li-4359964843</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>linkedin</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4359964843</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Multi Skilled Technician</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>JLL</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Makati, National Capital Region, Philippines</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="b">
+        <v>0</v>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/jll</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>li-4345800265</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>linkedin</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4345800265</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>SRE Technician</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>STMicroelectronics</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Calamba, Northern Mindanao, Philippines</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="b">
+        <v>0</v>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>https://ch.linkedin.com/company/stmicroelectronics</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>li-4334726725</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>linkedin</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4334726725</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Renewables Technical Lead</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Aggreko</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="b">
+        <v>0</v>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/aggreko</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>li-4360643379</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>linkedin</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4360643379</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Multi Skilled Technician</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>JLL</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Batangas, Calabarzon, Philippines</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="b">
+        <v>0</v>
+      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/jll</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/iTrack/scraped_jobs.xlsx
+++ b/iTrack/scraped_jobs.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH27"/>
+  <dimension ref="A1:AH25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -607,7 +607,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>in-225d4b3b461348b2</t>
+          <t>in-a0f2177ec4d1d3ea</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -617,31 +617,31 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://ph.indeed.com/viewjob?jk=225d4b3b461348b2</t>
+          <t>https://ph.indeed.com/viewjob?jk=a0f2177ec4d1d3ea</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://intrepid.bamboohr.com/careers/1521?source=indeed&amp;src=indeed&amp;postedDate=2026-01-11</t>
+          <t>http://ph.indeed.com/job/accounting-intern-a0f2177ec4d1d3ea</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Finance Intern (Required Internship Only)</t>
+          <t>Accounting Intern</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Intrepid</t>
+          <t>Agile Tech Ops Ince</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Manila, P00, PH</t>
+          <t>Ayala Avenue-Paseo de Roxas, P00, PH</t>
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>46033</v>
+        <v>46035</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -661,6 +661,113 @@
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr">
+        <is>
+          <t>**JOB TITLE:** Accounting Intern
+**COMPANY:** Agile Tech Ops Inc.
+**LOCATION:** Makati (On\-site / Hybrid)
+**INTERNSHIP TYPE:** Internship / OJT
+**JOB SUMMARY**  
+Agile Tech Ops Inc. is seeking a motivated and detail\-oriented **Accounting Intern** to support our Finance and Accounting team. This internship provides hands\-on experience in basic accounting processes, financial documentation, and office operations while working closely with experienced professionals.
+**KEY RESPONSIBILITIES**  
+Assist in preparing, encoding, and maintaining accounting records and documents
+Support accounts payable and receivable monitoring
+Organize invoices, receipts, vouchers, and other financial files
+Assist in bank reconciliations and expense tracking
+Provide support during audits and month\-end reporting
+Perform other accounting and administrative tasks as assigned
+**QUALIFICATIONS**
+Currently taking **BS Accountancy, BS Accounting Technology, or any Finance\-related course**
+Must be endorsed by school for internship / OJT
+Basic knowledge of accounting principles is an advantage
+Proficient in MS Excel and MS Word
+Detail\-oriented, organized, and willing to learn
+Able to work independently and meet deadlines
+**WHAT WE OFFER**
+Hands\-on accounting experience in a corporate setting
+Mentorship from experienced accounting professionals
+Internship allowance (if applicable)
+Certificate of Completion upon successful internship
+Opportunity for future employment based on performance
+Job Type: OJT (On the job training)
+Work Location: In person</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>https://ph.indeed.com/cmp/Agile-Tech-Ops-Ince</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>in-225d4b3b461348b2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>indeed</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://ph.indeed.com/viewjob?jk=225d4b3b461348b2</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://intrepid.bamboohr.com/careers/1521?source=indeed&amp;src=indeed&amp;postedDate=2026-01-11</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Finance Intern (Required Internship Only)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Intrepid</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Manila, P00, PH</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>46033</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>internship</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="b">
+        <v>0</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
         <is>
           <t>**Who we are**
 Intrepid Asia is a leading Ecommerce and Digital Solutions Provider in South East Asia. We offer end\-to\-end omni\-channel ecommerce management, Livestreaming, Video production \&amp; Affiliate Management for Social Commerce plus full funnel Digital Marketing Services and advanced Market Intelligence, all powered by state of the art inhouse Technology to our client base of leading international brands across all key marketplaces and social platforms in all 6 SEA countries. Brands love our regional presence, our excellent data\-driven and growth\-focused services which are enabled by the strongest team in the industry, and our advanced marketing and tech capabilities.
@@ -703,82 +810,82 @@
  *Note: We will not be accepting any unsolicited resumes or CVs from headhunting or recruitment agencies at this point. Any CVs or profiles shared with us will not be entertained, and in the event of dispute, Intrepid will not be liable for any material compensation to third parties*</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr">
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
         <is>
           <t>https://ph.indeed.com/cmp/Intrepid-1c14aa57</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>in-2dbb6c5d669cc55a</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>indeed</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>https://ph.indeed.com/viewjob?jk=2dbb6c5d669cc55a</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>https://intrepid.bamboohr.com/careers/1520?source=indeed&amp;src=indeed&amp;postedDate=2026-01-11</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Human Resources Intern (Required Internship Only)</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Intrepid</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Manila, P00, PH</t>
         </is>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="H4" s="2" t="n">
         <v>46033</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>internship</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="b">
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="b">
         <v>0</v>
       </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr">
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
         <is>
           <t>**Who we are**
 Intrepid Asia is a leading Ecommerce and Digital Solutions Provider in South East Asia. We offer end\-to\-end omni\-channel ecommerce management, Livestreaming, Video production \&amp; Affiliate Management for Social Commerce plus full funnel Digital Marketing Services and advanced Market Intelligence, all powered by state of the art inhouse Technology to our client base of leading international brands across all key marketplaces and social platforms in all 6 SEA countries. Brands love our regional presence, our excellent data\-driven and growth\-focused services which are enabled by the strongest team in the industry, and our advanced marketing and tech capabilities.
@@ -821,86 +928,86 @@
  *Note: We will not be accepting any unsolicited resumes or CVs from headhunting or recruitment agencies at this point. Any CVs or profiles shared with us will not be entertained, and in the event of dispute, Intrepid will not be liable for any material compensation to third parties*</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr">
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
         <is>
           <t>https://ph.indeed.com/cmp/Intrepid-1c14aa57</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>in-f1e13e490a93b540</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>indeed</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>https://ph.indeed.com/viewjob?jk=f1e13e490a93b540</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>http://ph.indeed.com/job/it-programming-intern-f1e13e490a93b540</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>IT / Programming Intern</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Lucky Boba</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Sangandaan, P00, PH</t>
         </is>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H5" s="2" t="n">
         <v>46032</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>temporary, internship</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="b">
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="b">
         <v>0</v>
       </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr">
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
         <is>
           <t>luckyboba.hr@gmail.com</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>**We're Hiring Interns!**
 Are you passionate about technology and eager to gain  
@@ -939,138 +1046,15 @@
 Work Location: In person</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>https://ph.indeed.com/cmp/Lucky-Boba-1</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>in-87c8416ce707a201</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>indeed</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://ph.indeed.com/viewjob?jk=87c8416ce707a201</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>http://ph.indeed.com/job/business-development-intern-paid-ojt-87c8416ce707a201</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Business Development Intern (Paid OJT)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Achieve Without Borders, Inc. (AWB)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Makati, P00, PH</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>46032</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>internship</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="b">
-        <v>0</v>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>**About the Role:**  
-If you’ve ever wanted to learn how to charm clients, close deals, and sound smart while doing it, this one’s for you. Achieve Without Borders, Inc. (AWB) is opening its doors to aspiring sales superheroes who are ready to roll up their sleeves, dive into the business world, and make things happen with free lunch to fuel the hustle.
-**What You’ll Be Doing:**
-* Help our sales team turn leads into happy clients (and happy clients into loyal ones).
-* Assist in making presentations that wow, not zzz.
-* Keep our CRM up to date because organized data equals world domination.
-* Join team huddles, pitch your ideas, and learn the fine art of selling without sounding salesy.
-* Track leads, send follow\-ups, and help us build relationships that last longer than most New Year’s resolutions.
-**Who You Are:**
-* A student in Business, Marketing, or Communications (or someone who just loves making connections).
-* Confident, proactive, and just the right amount of persuasive.
-* Knows how to use Microsoft Office (and maybe even CRM tools if you’re feeling fancy).
-* Detail\-oriented and professional, even when you’re having fun.
-* **Makati bound.**
-**Why Join AWB?**
-* Real\-world experience with mentors who’ve been there, sold that.
-* Paid training and free meals because good ideas need fuel.
-* A chance to grow your career in tech\-driven business development.
-* **Perform well, and we might just hire you for real.**
-**ABOUT ACHIEVE WITHOUT BORDERS (AWB)** 
-Achieve Without Borders Inc. (AWB) is a Philippine\-based IT solutions company headquartered in Makati City. We are a **Gold Odoo Partner and Google Partner**, dedicated to helping Filipino businesses streamline operations and scale through ERP, cloud, and digital transformation solutions.
-Our expertise spans ERP systems (Odoo, NetSuite), cloud platforms (Google Cloud), and enterprise productivity tools (Microsoft 365, Google Workspace). We combine business insight and technology to deliver smart, integrated systems that empower organizations to work smarter and grow faster.
-Job Type: OJT (On the job training)  
-Contract length: 3 months
-Benefits:
-* Paid training
-* Promotion to permanent employee
-* Staff meals provided
-Work Location: In person</t>
-        </is>
-      </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
-          <t>https://ph.indeed.com/cmp/Achieve-Without-Borders,-Inc.-(awb)</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>https://d2q79iu7y748jz.cloudfront.net/s/_squarelogo/256x256/5108215db8072827f110d419c3f8313d</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>https://www.achievewithoutborders.com</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2029 Gen Mascardo Street
-    Barangay Bangkal
-    Makati City MM
-    Philippines</t>
-        </is>
-      </c>
+          <t>https://ph.indeed.com/cmp/Lucky-Boba-1</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
@@ -1084,47 +1068,39 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>in-b20557a09f0fdf0f</t>
+          <t>li-4332535951</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>indeed</t>
+          <t>linkedin</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://ph.indeed.com/viewjob?jk=b20557a09f0fdf0f</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>http://ph.indeed.com/job/sales-and-marketing-intern-paid-ojt-b20557a09f0fdf0f</t>
-        </is>
-      </c>
+          <t>https://www.linkedin.com/jobs/view/4332535951</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sales and Marketing Intern (Paid OJT)</t>
+          <t>Technician 1 Monitoring Services (Technical Support)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Achieve Without Borders, Inc. (AWB)</t>
+          <t>Risewave Consulting, Inc.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Makati, P00, PH</t>
+          <t>Quezon City, National Capital Region, Philippines</t>
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>46032</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>internship</t>
-        </is>
-      </c>
+        <v>46034</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -1137,67 +1113,16 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>**Be the Hype Behind the Tech**
-Can you sell sand in a desert, or at least convince your friends to join your group project?  
-Do you scroll through ads and think, "*I could totally write something better*"?  
-If so, Achieve Without Borders Inc. (AWB) wants you on our team as our next **Sales and Marketing Intern.**
-We are a Gold Odoo Partner, Google Partner, and an all\-around IT wizard squad that helps businesses modernize through ERP, Cloud, and Network Solutions. Translation: we make companies smarter, faster, and slightly cooler.
-Now, we need creative minds who can tell that story to the world.
-**What You’ll Be Doing (a.k.a. How You’ll Look Busy on LinkedIn)**
-* Cook up digital marketing campaigns that actually make people stop scrolling.
-* Turn coffee and creativity into engaging social media content, blogs, and visuals.
-* Help launch webinars, events, and promos that make our brand shine brighter than your screen’s blue light.
-* Research market trends like a detective with Wi\-Fi.
-* Join sales and marketing projects that connect our tech magic to real business growth.
-* Collaborate with awesome people (yes, we’re biased).
-**What We’re Looking For**
-* Currently taking up Marketing, Business, Communications, or something equally awesome.
-* Fluent in English, creativity, and Google Workspace.
-* Knows a thing or two about social media marketing, content creation, and branding.
-* Canva or Adobe familiarity equals instant brownie points.
-* Organized, proactive, and allergic to boredom.
-* **Can join us onsite in Makati City.**
-**What’s In It For You**
-* Real\-world experience in digital marketing, sales strategy, and tech branding.
-* Mentorship from professionals who actually care about your growth.
-* Exposure to ERP, cloud, and network technologies (a.k.a. resume gold).
-* **Paid training and free daily lunch (yes, free).**
-* A shot at becoming part of the AWB family after your internship.
-Job Type: OJT (On the job training)  
-Contract length: 3 months
-Benefits:
-* Paid training
-* Promotion to permanent employee
-* Staff meals provided
-Work Location: In person</t>
-        </is>
-      </c>
+      <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>https://ph.indeed.com/cmp/Achieve-Without-Borders,-Inc.-(awb)</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>https://d2q79iu7y748jz.cloudfront.net/s/_squarelogo/256x256/5108215db8072827f110d419c3f8313d</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>https://www.achievewithoutborders.com</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2029 Gen Mascardo Street
-    Barangay Bangkal
-    Makati City MM
-    Philippines</t>
-        </is>
-      </c>
+          <t>https://ph.linkedin.com/company/risewave-consulting-inc</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
@@ -1211,104 +1136,56 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>in-14ad7cd35cfbb3dc</t>
+          <t>li-4359997663</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>indeed</t>
+          <t>linkedin</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://ph.indeed.com/viewjob?jk=14ad7cd35cfbb3dc</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>http://ph.indeed.com/job/business-development-intern-14ad7cd35cfbb3dc</t>
-        </is>
-      </c>
+          <t>https://www.linkedin.com/jobs/view/4359997663</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Business Development Intern</t>
+          <t>Multi Skilled Technician (Taguig)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Founders Launchpad</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Makati, P00, PH</t>
+          <t>Taguig, National Capital Region, Philippines</t>
         </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>46031</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>parttime, internship</t>
-        </is>
-      </c>
+        <v>46034</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>**Job Summary**
-As an **Analyst Intern**, you will work hands\-on with one of our ventures to drive growth through sales pipeline development, GTM strategy execution, and strategic partnerships—taking a founder's mindset while supporting operational initiatives and growth experiments in a fast\-paced startup environment.
-**Job Responsibilities**
-**Business Development for a Venture**
-* **Market Expansion:** Support sales pipeline building, customer outreach, and partnerships for one of our ventures.
-* **Go\-to\-Market Execution:** Assist in building and executing GTM strategies, including messaging, materials, CRM management, and lead generation.
-* **Growth Experiments:** Test and analyze marketing, sales, and operational experiments to help scale the venture.
-* **Operations Support:** Collaborate with the venture’s founders on internal tools, process design, and strategic projects as needed.
-**Qualifications**
-* Currently enrolled in a Bachelor's degree program, preferably in their third or fourth year, with a focus on Business, Finance, Economics, or a related field.
-* Prior internship experience or relevant coursework is a plus, but not required.
-* Strong analytical skills with the ability to break down problems and use data to drive decisions.
-* Proven initiative and comfort with ambiguity — you are resourceful, solutions\-driven, and thrive in fast\-paced environments.
-* Deep curiosity about startups, innovation, and building from 0 to 1\.
-* Excellent written and verbal communication skills.
-* A hands\-on, founder\-like mentality — you’re not afraid to take ownership.
-* Available to commit to a minimum 3\-month internship, with potential for extension into a long\-term internship or full\-time opportunity.
-**Bonus Points**
-* Familiarity with tools like Notion, Airtable, Monday.com, Hubspot, or SQL.
-* Prior startup experience.
-* Passion for a specific domain such as fintech, logistics, healthtech, or consumer tech.
-**Why Work with Us?**
-* Work with a young, passionate, and fun team
-* We offer a diverse and international work environment
-* Hybrid exposure to venture capital and startup building — unique experience for future founders or operators.
-* Mentorship from experienced founders and operators.
-* A high\-growth environment with ownership and learning from day one.
-Job Types: Part\-time, OJT (On the job training), Fresh graduate  
-Contract length: 3 months
-Pay: Php5,000\.00 \- Php10,000\.00 per month
-Expected hours: 30 – 40 per week
-Benefits:
-* Flexible schedule
-* Flextime
-* Paid training
-* Work from home
-Work Location: In person</t>
-        </is>
-      </c>
+      <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
-          <t>https://ph.indeed.com/cmp/Founders-Launchpad</t>
+          <t>https://www.linkedin.com/company/jll</t>
         </is>
       </c>
       <c r="W7" t="inlineStr"/>
@@ -1327,7 +1204,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>li-4345212547</t>
+          <t>li-4352672394</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1337,27 +1214,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4345212547</t>
+          <t>https://www.linkedin.com/jobs/view/4352672394</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Deskside Technician</t>
+          <t>PHL Senior Technician - L3 - Represented/Tariff</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stefanini North America and APAC</t>
+          <t>Dow</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pasay, National Capital Region, Philippines</t>
+          <t>Las Piñas, National Capital Region, Philippines</t>
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>46032</v>
+        <v>46034</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
@@ -1376,7 +1253,7 @@
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>https://br.linkedin.com/company/stefanini-na-apac</t>
+          <t>https://www.linkedin.com/company/dow-chemical</t>
         </is>
       </c>
       <c r="W8" t="inlineStr"/>
@@ -1395,7 +1272,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>li-4334598816</t>
+          <t>li-4351866176</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1405,27 +1282,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4334598816</t>
+          <t>https://www.linkedin.com/jobs/view/4351866176</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Service Technician Castilla y León</t>
+          <t>Multi-Skilled Technician -Lipa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vestas</t>
+          <t>CBRE Asia Pacific</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Buenavista, Western Visayas, Philippines</t>
+          <t>Lipa, Calabarzon, Philippines</t>
         </is>
       </c>
       <c r="H9" s="2" t="n">
-        <v>46032</v>
+        <v>46034</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
@@ -1444,7 +1321,7 @@
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/company/vestas</t>
+          <t>https://sg.linkedin.com/company/cbre-asia-pacific</t>
         </is>
       </c>
       <c r="W9" t="inlineStr"/>
@@ -1463,7 +1340,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>li-4350286936</t>
+          <t>li-4345396142</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1473,27 +1350,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4350286936</t>
+          <t>https://www.linkedin.com/jobs/view/4345396142</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Technician I, Managed Sevices</t>
+          <t>Multi-Skilled Technician - Lipa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Copeland</t>
+          <t>CBRE Asia Pacific</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Quezon City, National Capital Region, Philippines</t>
+          <t>Lipa, Calabarzon, Philippines</t>
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>46032</v>
+        <v>46034</v>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
@@ -1512,7 +1389,7 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/copeland</t>
+          <t>https://sg.linkedin.com/company/cbre-asia-pacific</t>
         </is>
       </c>
       <c r="W10" t="inlineStr"/>
@@ -1531,7 +1408,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>li-4350237071</t>
+          <t>li-4334726725</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1541,27 +1418,23 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4350237071</t>
+          <t>https://www.linkedin.com/jobs/view/4334726725</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Technician I, Managed Services</t>
+          <t>Renewables Technical Lead</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Copeland</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Quezon City, National Capital Region, Philippines</t>
-        </is>
-      </c>
+          <t>Aggreko</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" s="2" t="n">
-        <v>46032</v>
+        <v>46033</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
@@ -1580,7 +1453,7 @@
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/copeland</t>
+          <t>https://uk.linkedin.com/company/aggreko</t>
         </is>
       </c>
       <c r="W11" t="inlineStr"/>
@@ -1599,7 +1472,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>li-4350187030</t>
+          <t>li-4359964843</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1609,27 +1482,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4350187030</t>
+          <t>https://www.linkedin.com/jobs/view/4359964843</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Technician I, Managed Services</t>
+          <t>Multi Skilled Technician</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Copeland</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Quezon City, National Capital Region, Philippines</t>
+          <t>Makati, National Capital Region, Philippines</t>
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>46032</v>
+        <v>46033</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
@@ -1648,7 +1521,7 @@
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/copeland</t>
+          <t>https://www.linkedin.com/company/jll</t>
         </is>
       </c>
       <c r="W12" t="inlineStr"/>
@@ -1667,7 +1540,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>li-4359465790</t>
+          <t>li-4360643379</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1677,27 +1550,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4359465790</t>
+          <t>https://www.linkedin.com/jobs/view/4360643379</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Platform Technician I</t>
+          <t>Multi Skilled Technician</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>BlueVoyant</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Manila, National Capital Region, Philippines</t>
+          <t>Batangas, Calabarzon, Philippines</t>
         </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>46031</v>
+        <v>46033</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
@@ -1716,7 +1589,7 @@
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/bluevoyant</t>
+          <t>https://www.linkedin.com/company/jll</t>
         </is>
       </c>
       <c r="W13" t="inlineStr"/>
@@ -1735,7 +1608,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>li-4332222982</t>
+          <t>li-4345212547</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1745,27 +1618,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4332222982</t>
+          <t>https://www.linkedin.com/jobs/view/4345212547</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Technical Services Technician</t>
+          <t>Deskside Technician</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Datumstruct Philippines, Inc.</t>
+          <t>Stefanini North America and APAC</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Makati, National Capital Region, Philippines</t>
+          <t>Pasay, National Capital Region, Philippines</t>
         </is>
       </c>
       <c r="H14" s="2" t="n">
-        <v>46031</v>
+        <v>46032</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
@@ -1784,7 +1657,7 @@
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr">
         <is>
-          <t>https://ph.linkedin.com/company/datumstructph</t>
+          <t>https://br.linkedin.com/company/stefanini-na-apac</t>
         </is>
       </c>
       <c r="W14" t="inlineStr"/>
@@ -1803,7 +1676,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>li-4314154195</t>
+          <t>li-4334598816</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1813,27 +1686,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4314154195</t>
+          <t>https://www.linkedin.com/jobs/view/4334598816</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026 Data Center Technician Intern</t>
+          <t>Service Technician Castilla y León</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Amazon Web Services (AWS)</t>
+          <t>Vestas</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bolinao, Ilocos Region, Philippines</t>
+          <t>Buenavista, Western Visayas, Philippines</t>
         </is>
       </c>
       <c r="H15" s="2" t="n">
-        <v>46031</v>
+        <v>46032</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
@@ -1852,7 +1725,7 @@
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/amazon-web-services</t>
+          <t>https://dk.linkedin.com/company/vestas</t>
         </is>
       </c>
       <c r="W15" t="inlineStr"/>
@@ -1871,7 +1744,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>li-4331574126</t>
+          <t>li-4350237071</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1881,27 +1754,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4331574126</t>
+          <t>https://www.linkedin.com/jobs/view/4350237071</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Multi-Skilled Technician - Makati</t>
+          <t>Technician I, Managed Services</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CBRE Asia Pacific</t>
+          <t>Copeland</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Makati, National Capital Region, Philippines</t>
+          <t>Quezon City, National Capital Region, Philippines</t>
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>46031</v>
+        <v>46032</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
@@ -1920,7 +1793,7 @@
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr">
         <is>
-          <t>https://sg.linkedin.com/company/cbre-asia-pacific</t>
+          <t>https://www.linkedin.com/company/copeland</t>
         </is>
       </c>
       <c r="W16" t="inlineStr"/>
@@ -1939,7 +1812,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>li-4352057410</t>
+          <t>li-4350286936</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1949,27 +1822,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4352057410</t>
+          <t>https://www.linkedin.com/jobs/view/4350286936</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Associate, Technical Services</t>
+          <t>Technician I, Managed Sevices</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vena Group</t>
+          <t>Copeland</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ilocos Region, Philippines</t>
+          <t>Quezon City, National Capital Region, Philippines</t>
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>46031</v>
+        <v>46032</v>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
@@ -1988,7 +1861,7 @@
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr">
         <is>
-          <t>https://sg.linkedin.com/company/venagroup</t>
+          <t>https://www.linkedin.com/company/copeland</t>
         </is>
       </c>
       <c r="W17" t="inlineStr"/>
@@ -2007,7 +1880,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>li-4359761815</t>
+          <t>li-4359757191</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2017,27 +1890,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4359761815</t>
+          <t>https://www.linkedin.com/jobs/view/4359757191</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Technician I - Reliability</t>
+          <t>Medewerker Technische Dienst</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Microchip Technology Inc.</t>
+          <t>Stayokay</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Davao, Davao Region, Philippines</t>
+          <t>Bacnotan, Ilocos Region, Philippines</t>
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>46031</v>
+        <v>46032</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
@@ -2056,7 +1929,7 @@
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/microchip-technology</t>
+          <t>https://nl.linkedin.com/company/stayokay</t>
         </is>
       </c>
       <c r="W18" t="inlineStr"/>
@@ -2075,7 +1948,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>li-4359761816</t>
+          <t>li-4350187030</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2085,27 +1958,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4359761816</t>
+          <t>https://www.linkedin.com/jobs/view/4350187030</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Technician I - Reliability</t>
+          <t>Technician I, Managed Services</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Microchip Technology Inc.</t>
+          <t>Copeland</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Davao, Davao Region, Philippines</t>
+          <t>Quezon City, National Capital Region, Philippines</t>
         </is>
       </c>
       <c r="H19" s="2" t="n">
-        <v>46031</v>
+        <v>46032</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
@@ -2124,7 +1997,7 @@
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/microchip-technology</t>
+          <t>https://www.linkedin.com/company/copeland</t>
         </is>
       </c>
       <c r="W19" t="inlineStr"/>
@@ -2143,7 +2016,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>li-4359611660</t>
+          <t>li-4345577544</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2153,28 +2026,26 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4359611660</t>
+          <t>https://www.linkedin.com/jobs/view/4345577544</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Multi-Skilled Technician</t>
+          <t>IS Technician - ISHELP</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>GHD</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Makati, National Capital Region, Philippines</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>46031</v>
-      </c>
+          <t>Cebu, Central Visayas, Philippines</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
@@ -2192,7 +2063,7 @@
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/jll</t>
+          <t>https://au.linkedin.com/company/ghd</t>
         </is>
       </c>
       <c r="W20" t="inlineStr"/>
@@ -2211,7 +2082,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>li-4358913747</t>
+          <t>li-4351819555</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2221,28 +2092,26 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4358913747</t>
+          <t>https://www.linkedin.com/jobs/view/4351819555</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tech Svc Desk</t>
+          <t>Multi Skilled Technician</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Unisys</t>
+          <t>FPD ASIA PROPERTY SERVICES, INC.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Manila, National Capital Region, Philippines</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>46030</v>
-      </c>
+          <t>Taguig, National Capital Region, Philippines</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
@@ -2260,7 +2129,7 @@
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/unisys</t>
+          <t>https://ph.linkedin.com/company/fpd-asia-property-services-inc-</t>
         </is>
       </c>
       <c r="W21" t="inlineStr"/>
@@ -2279,7 +2148,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>li-4358576241</t>
+          <t>li-4332549682</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2289,28 +2158,26 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4358576241</t>
+          <t>https://www.linkedin.com/jobs/view/4332549682</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sr Tech Svc Desk</t>
+          <t>Pump Technician</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Unisys</t>
+          <t>Trade One Incorporated</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Manila, National Capital Region, Philippines</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>46030</v>
-      </c>
+          <t>Quezon City, National Capital Region, Philippines</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
@@ -2328,7 +2195,7 @@
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/unisys</t>
+          <t>https://ph.linkedin.com/company/tradeoneincorporated</t>
         </is>
       </c>
       <c r="W22" t="inlineStr"/>
@@ -2347,7 +2214,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>li-4359757191</t>
+          <t>li-4361161826</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2357,23 +2224,23 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4359757191</t>
+          <t>https://www.linkedin.com/jobs/view/4361161826</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Medewerker Technische Dienst</t>
+          <t>Multi-Skilled Technician</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stayokay</t>
+          <t>CBRE Asia Pacific</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bacnotan, Ilocos Region, Philippines</t>
+          <t>Lipa, Calabarzon, Philippines</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
@@ -2394,7 +2261,7 @@
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/company/stayokay</t>
+          <t>https://sg.linkedin.com/company/cbre-asia-pacific</t>
         </is>
       </c>
       <c r="W23" t="inlineStr"/>
@@ -2413,7 +2280,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>li-4359964843</t>
+          <t>li-4354460426</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2423,23 +2290,23 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4359964843</t>
+          <t>https://www.linkedin.com/jobs/view/4354460426</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Multi Skilled Technician</t>
+          <t>Multi-Skilled Technician - Lipa</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>CBRE Asia Pacific</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Makati, National Capital Region, Philippines</t>
+          <t>Lipa, Calabarzon, Philippines</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -2460,7 +2327,7 @@
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/jll</t>
+          <t>https://sg.linkedin.com/company/cbre-asia-pacific</t>
         </is>
       </c>
       <c r="W24" t="inlineStr"/>
@@ -2479,7 +2346,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>li-4345800265</t>
+          <t>li-4345634591</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2489,23 +2356,23 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4345800265</t>
+          <t>https://www.linkedin.com/jobs/view/4345634591</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>SRE Technician</t>
+          <t>SAP Academy for Services &amp; Consulting (APAC) - Technical Quality Manager (TQM) - Philippines</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>STMicroelectronics</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Calamba, Northern Mindanao, Philippines</t>
+          <t>Taguig, National Capital Region, Philippines</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -2526,7 +2393,7 @@
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr">
         <is>
-          <t>https://ch.linkedin.com/company/stmicroelectronics</t>
+          <t>https://de.linkedin.com/company/sap</t>
         </is>
       </c>
       <c r="W25" t="inlineStr"/>
@@ -2542,134 +2409,6 @@
       <c r="AG25" t="inlineStr"/>
       <c r="AH25" t="inlineStr"/>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>li-4334726725</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>linkedin</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4334726725</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Renewables Technical Lead</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Aggreko</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="b">
-        <v>0</v>
-      </c>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>https://uk.linkedin.com/company/aggreko</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
-      <c r="AA26" t="inlineStr"/>
-      <c r="AB26" t="inlineStr"/>
-      <c r="AC26" t="inlineStr"/>
-      <c r="AD26" t="inlineStr"/>
-      <c r="AE26" t="inlineStr"/>
-      <c r="AF26" t="inlineStr"/>
-      <c r="AG26" t="inlineStr"/>
-      <c r="AH26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>li-4360643379</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>linkedin</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4360643379</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Multi Skilled Technician</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>JLL</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Batangas, Calabarzon, Philippines</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="b">
-        <v>0</v>
-      </c>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/jll</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
-      <c r="AA27" t="inlineStr"/>
-      <c r="AB27" t="inlineStr"/>
-      <c r="AC27" t="inlineStr"/>
-      <c r="AD27" t="inlineStr"/>
-      <c r="AE27" t="inlineStr"/>
-      <c r="AF27" t="inlineStr"/>
-      <c r="AG27" t="inlineStr"/>
-      <c r="AH27" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/iTrack/scraped_jobs.xlsx
+++ b/iTrack/scraped_jobs.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH25"/>
+  <dimension ref="A1:AH28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -607,7 +607,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>in-a0f2177ec4d1d3ea</t>
+          <t>in-24bbb1027ad4d416</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -617,31 +617,31 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://ph.indeed.com/viewjob?jk=a0f2177ec4d1d3ea</t>
+          <t>https://ph.indeed.com/viewjob?jk=24bbb1027ad4d416</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>http://ph.indeed.com/job/accounting-intern-a0f2177ec4d1d3ea</t>
+          <t>https://jobs.lever.co/ninjavan/3ae83fe9-6325-4551-9fea-7a46fe87b508?lever-source=Indeed</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Accounting Intern</t>
+          <t>Human Resources Intern</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Agile Tech Ops Ince</t>
+          <t>Ninja Van</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ayala Avenue-Paseo de Roxas, P00, PH</t>
+          <t>Taguig, P00, PH</t>
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>46035</v>
+        <v>46037</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -661,6 +661,661 @@
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr">
+        <is>
+          <t>Ninja Van is a tech\-enabled logistics company on a mission to provide hassle\-free delivery services for businesses of all sizes across Southeast Asia. Launched in 2014, we started operations in Singapore and have become the region's largest and fastest growing last\-mile logistics company, partnering with over 35,000 merchants and delivering more than 1,000 parcels every minute across six countries.  
+At our core, we are a technology company that is disrupting a massive industry with cutting\-edge software and operational concepts. Powered by algorithm\-based optimisation, dynamic routing, end\-to\-end tracking and a data\-driven approach, we provide best\-of\-class delivery services that delight both the shippers and end customers. But we are just getting started! We have much room for improvement and many ideas that will further shape the industry.  
+The **Human Resources Unit** manages the entire life cycle of each employee \- from attraction, recruitment, onboarding, development, retention and separation. The unit focuses on strategizing initiatives and solutions that build a close\-knit culture, encourages professional and leadership growth and drive high performance among employees. It also ensures that the company is compliant to work and compensation standards set by relevant government agencies such as the Department of Labor.  
+As part of the Human Resources Unit, the **Human Resources Intern** will gain hands\-on exposure across key HR functions, supporting the team in managing the employee life cycle. The intern will be involved in **Talent Acquisition** by assisting with recruitment activities such as candidate screening, interview coordination, job postings, and recruitment reporting. They will also support **Compensation and Benefits** initiatives through administrative assistance in payroll processing, benefits documentation, data tracking, and coordination with internal stakeholders. In **Employee Relations**, the intern will help address employee inquiries, support documentation of HR cases, assist in employee engagement activities, and ensure proper maintenance of employee records in compliance with company policies and labor regulations.
+This role provides a strong foundation for understanding how HR strategies support Ninja Van’s fast\-paced, tech\-enabled logistics operations while contributing to a positive and high\-performing workplace culture.
+Submit a job application
+By applying to the job, you acknowledge that you have read, understood and agreed to our Privacy Policy Notice (the “Notice”) and consent to the collection, use and/or disclosure of your personal data by Ninja Logistics Pte Ltd (the “Company”) for the purposes set out in the Notice. In the event that your job application or personal data was received from any third party pursuant to the purposes set out in the Notice, you warrant that such third party has been duly authorised by you to disclose your personal data to us for the purposes set out in the the Notice.
+We may use artificial intelligence (AI) tools to support parts of the hiring process, such as reviewing applications, analyzing resumes, or assessing responses. These tools assist our recruitment team but do not replace human judgment. Final hiring decisions are ultimately made by humans. If you would like more information about how your data is processed, please contact us.</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>https://ph.indeed.com/cmp/Ninja-Van</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>https://d2q79iu7y748jz.cloudfront.net/s/_squarelogo/256x256/81bcc11b57b5954b98c86f9d8b8281e7</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>https://www.ninjavan.co/en-sg</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>501 to 1,000</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>$5M to $25M (USD)</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Our Mission: Connecting Southeast Asia to a world of possibilities, one delightful delivery at a time</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>in-86321f8f56c390bb</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>indeed</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://ph.indeed.com/viewjob?jk=86321f8f56c390bb</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>http://ph.indeed.com/job/accounting-intern-86321f8f56c390bb</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Accounting Intern</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Circuit Solutions Incorporated</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Pasig, P00, PH</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>46036</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>fulltime, internship</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="b">
+        <v>0</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>*Be part of our EXCITE (Experience CSI Internship in Tech Entrepreneurship) Program!*
+**Qualifications:**
+* Currently taking up Accounting, Financial Management, or Accounting Management
+* Full\-time intern, available to work Monday to Friday
+* Proficient in MS Excel
+* With understanding of basic accounting principles
+* Able to investigate and resolve issues independently
+* High attention to detail and accuracy
+* With positive attitude and strong passion for learning
+* Number of slot available: 1
+Job Types: Full\-time, OJT (On the job training)
+Pay: Php150\.00 \- Php200\.00 per day
+Application Question(s):
+* Do you have other subjects enrolled aside from your OJT?
+* When can you start?
+* How many hours is required for your internship?
+* Are you willing to do on\-site internship?
+Work Location: In person</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>https://ph.indeed.com/cmp/Circuit-Solutions-Incorporated</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>in-7d475c3a40bef8c0</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>indeed</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://ph.indeed.com/viewjob?jk=7d475c3a40bef8c0</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>http://ph.indeed.com/job/ojt-intern-human-resource-hrd-7d475c3a40bef8c0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>OJT | Intern Human Resource ( HRD )</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nutra Tech Biopharma, Inc.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Silang, 04A, PH</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>46036</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>internship</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>\- Currently enrolled in a Bachelor’s degree related to Human Resources, Psychology, Business Administration, or equivalent  
+\- location: Balubad, 2nd Silang Cavite  
+\-Required by school to complete an internship or OJT program
+The HR Intern / OJT assists the Human Resources Department in daily administrative and operational tasks while gaining hands\-on experience in HR functions. The role supports recruitment, employee records management, training coordination, and general HR activities in compliance with company policies.
+Job Type: OJT (On the job training)
+Work Location: In person</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>https://ph.indeed.com/cmp/Nutra-Tech-Biopharma,-Inc.</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>in-409ca859cb1b332c</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>indeed</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://ph.indeed.com/viewjob?jk=409ca859cb1b332c</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>http://ph.indeed.com/job/accounting-intern-409ca859cb1b332c</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Accounting Intern</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>PBO Global</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Work from Home, PH</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>46036</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>fulltime, internship</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="b">
+        <v>1</v>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>**Summary:**
+The objective of the program is to develop students into skilled accounting professionals who can contribute to the finance and accounting team. PBO Global is offering a remote Accounting Internship Program designed to provide practical, hands\-on experience in accounting operations, financial reporting, and business processes. This internship is suitable for students or fresh graduates looking to gain real\-world accounting experience in a corporate environment.
+This program runs for 2 to 4 months in line with the on\-the\-job training requirements of your school or university.
+**Duties \&amp; Responsibilities:**
+* Assisting the accounting team with day\-to\-day financial operations.
+* Recording and reconciling financial transactions using accounting software and MS Excel.
+* Supporting accounts payable and accounts receivable processes.
+* Assisting in preparing financial reports, statements, and summaries.
+* Conducting basic financial analysis and reporting.
+* Maintaining proper documentation and filing of financial records.
+* Supporting budgeting and expense monitoring activities.
+* Learning internal controls and compliance procedures.
+* Recording transactions and reconciling accounts.
+* Assisting with month\-end and year\-end financial closings.
+* Supporting payroll and billing processes.
+* Generating reports for management review.
+* Collaborating with the accounting team on audits and financial reviews.
+* Performing general administrative tasks to support the finance function.
+**Qualifications \&amp; Requirements:**
+* Open to college, vocational, or senior high school graduates interested in gaining practical accounting experience.
+* Enrolled in or graduated from courses related to Accounting, Finance, Business Administration, or ABM strand (for senior high school).
+* Strong numerical and analytical skills.
+* Proficient in MS Office, especially Excel.
+* Basic understanding of accounting principles and financial concepts.
+* Tech\-savvy and comfortable working remotely.
+* Self\-motivated, organized, and able to manage tasks independently.
+Job Types: Full\-time, OJT (On the job training)  
+Contract length: 4 months
+Benefits:
+* Work from home
+Work Location: Remote</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>https://ph.indeed.com/cmp/Pbo-Global-1</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>https://pboglobal.com.au/</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Clark Center, Unit B 5th Floor Clark Center 7 Berthaphil, Jose Abad Santos Ave, Clark, 2023 Pampanga</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11 to 50</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>in-e3ef37eb705926ce</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>indeed</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://ph.indeed.com/viewjob?jk=e3ef37eb705926ce</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://ag.wd3.myworkdayjobs.com/en-US/Airbus/job/Pasay-City/Technical-Support-Intern_JR10382626</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Technical Support Intern</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Airbus</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pasay, P00, PH</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>46036</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="b">
+        <v>0</v>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>emsom@airbus.com</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>**Job Description:**
+**Responsibilities:**
+* Assist in monitoring key performance indicators in the implementation of maintenance projects
+* Assist in the procurement of products, services, and other materials
+* Assosit in the preparation of costing and checking on the availability of data for spare parts and services within Airbus Helicopters Group or from an external supplier
+* Assist in the preparation of quotations under consideration of required maintenance man\-hours and cost for spare parts, materials, and services.
+* Assist in the preparation and issuance of purchase orders
+* Assist in monitoring all the orders and follow up on the undelivered spares from suppliers
+* Encoding of all parts ordered under order monitoring in the database
+* Adherence to company’s rules and regulations and safety policy
+**Personal \&amp; Interpersonal Skills**
+* Meticulous and keen on details
+* Performs job with the highest integrity
+* Promotes camaraderie among employees
+* Good communication skills (written and oral)
+* Tech\-Savvy
+* Knowledge in Aviation Industry is an advantage
+Professional skills:
+* Currently enrolled in Bachelor’s Degree in Aeronautical Engineering or any aviation related\-courses
+This job requires an awareness of any potential compliance risks and a commitment to act with integrity, as the foundation for the Company’s success, reputation and sustainable growth.
+**Company:**
+Airbus Helicopters Philippines Inc.
+**Employment Type:**
+Internship
+\-
+**Experience Level:**
+Student
+**Job Family:**
+Support to Management \&lt;JF\-FA\-ES\&gt;
+By submitting your CV or application you are consenting to Airbus using and storing information about you for monitoring purposes relating to your application or future employment. This information will only be used by Airbus.
+Airbus is committed to achieving workforce diversity and creating an inclusive working environment. We welcome all applications irrespective of social and cultural background, age, gender, disability, sexual orientation or religious belief.
+Airbus is, and always has been, committed to equal opportunities for all. As such, we will never ask for any type of monetary exchange in the frame of a recruitment process. Any impersonation of Airbus to do so should be reported to emsom@airbus.com .
+At Airbus, we support you to work, connect and collaborate more easily and flexibly. Wherever possible, we foster flexible working arrangements to stimulate innovative thinking.</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>https://ph.indeed.com/cmp/Airbus-e4b213b1</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>https://www.airbus.com</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10,000+</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>more than $10B (USD)</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>We look to recruit, develop, grow and retain the best, and welcome ALL as an equal opportunity employer.</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>in-46b21c09a7f9b13b</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>indeed</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://ph.indeed.com/viewjob?jk=46b21c09a7f9b13b</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>http://ph.indeed.com/job/project-management-intern-sports-46b21c09a7f9b13b</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Project Management Intern (Sports)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>XMPLR</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pasig, P00, PH</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>46035</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>internship</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="b">
+        <v>1</v>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>**Project Management Intern**
+The project management Intern is responsible for the day\-to\-day management of all aspects of XMPLR projects and works with other stakeholders to ensure their success.
+**Responsibilities—What you'll do:**
+· Assist in proposing, planning and developing potential project ideas.
+· Collaborate with the project team (e.g. organization staff, third\-party personnel, suppliers, and volunteers etc), for project deliverables
+· Implement and monitor project progress and meet deliverables within agreed timelines
+· Assist in stakeholder communication, resolving problems, conflicts and issues in relation to the projects as a customer service point of contact
+· Lead the development of marketing initiatives and communication campaigns for the projects
+· Lead the development and execution of the project marketing plans, content creation and publication
+· Plan, request and administer the budget allocated for the project
+· Prepare various documents (such as progress reports, budget utilization, customer service etc.) for presentations and audit purposes
+· Evaluate project performance across agreed KPIs in agreed timeframes
+**What will make you successful:**
+· Management, Marketing, or Communication undergrad or related field
+· Experience in project management, critical thinking, relationship management
+· Proactive, organized, detail\-oriented and able to manage multiple tasks simultaneously
+· Excellent communication and leadership skills
+· Fluent in English and Filipino
+· Tech and Social\-media savvy
+· Background in sports is a plus
+Job Type: OJT (On the job training)  
+Contract length: 6 months
+Benefits:
+* Flextime
+Work Location: Hybrid remote in Pasig</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>https://ph.indeed.com/cmp/Xmplr</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>in-a0f2177ec4d1d3ea</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>indeed</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://ph.indeed.com/viewjob?jk=a0f2177ec4d1d3ea</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>http://ph.indeed.com/job/accounting-intern-a0f2177ec4d1d3ea</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Accounting Intern</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Agile Tech Ops Ince</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Ayala Avenue-Paseo de Roxas, P00, PH</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>46035</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>internship</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr">
         <is>
           <t>**JOB TITLE:** Accounting Intern
 **COMPANY:** Agile Tech Ops Inc.
@@ -692,568 +1347,10 @@
 Work Location: In person</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>https://ph.indeed.com/cmp/Agile-Tech-Ops-Ince</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>in-225d4b3b461348b2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>indeed</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>https://ph.indeed.com/viewjob?jk=225d4b3b461348b2</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>https://intrepid.bamboohr.com/careers/1521?source=indeed&amp;src=indeed&amp;postedDate=2026-01-11</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Finance Intern (Required Internship Only)</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Intrepid</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Manila, P00, PH</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>46033</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>internship</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="b">
-        <v>0</v>
-      </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>**Who we are**
-Intrepid Asia is a leading Ecommerce and Digital Solutions Provider in South East Asia. We offer end\-to\-end omni\-channel ecommerce management, Livestreaming, Video production \&amp; Affiliate Management for Social Commerce plus full funnel Digital Marketing Services and advanced Market Intelligence, all powered by state of the art inhouse Technology to our client base of leading international brands across all key marketplaces and social platforms in all 6 SEA countries. Brands love our regional presence, our excellent data\-driven and growth\-focused services which are enabled by the strongest team in the industry, and our advanced marketing and tech capabilities.
-We are growing rapidly and as the exclusive partner of Flywheel in SEA, we offer many exciting opportunities to work with leading brands across multiple categories and key industry players. By joining us, you will work on the cutting edge of digital and social commerce in SEA, and experience what it takes to drive a successful ecommerce business end\-to\-end.
- **The team you will be part of**
-Our Finance Team is at the core of every major decision we make. We don’t just keep the books — we shape the direction of the business. By delivering on financial insights, strategic analysis, and data\-driven recommendations, the team plays a critical role in guiding growth and ensuring long\-term success. From planning and forecasting to optimizing performance and supporting key commercial initiatives, Our Finance team is a key partner across every function. With a strong focus on integrity, accuracy, and collaboration, its goal is to ensure the company remains financially strong, agile, and ready for the future.
- **The part you will play**
-We are looking for a Finance Intern who will be an active contributor to our Finance team. This role will report directly to the Senior Accountant and will provide hands\-on exposure to day\-to\-day finance operations, including accounting support, documentation, and financial administrative tasks. You will work closely with the Finance team and gain practical experience in a fast\-paced ecommerce environment.
- **As a Finance Intern, you will take charge of**
-* Assisting in the preparation and issuance of retail sales invoices
-* Filing, organizing, and maintaining accounting and finance documents
-* Supporting liquidation, reimbursement, and expense claims processes
-* Assisting in accounts receivable and accounts payable tracking
-* Helping ensure completeness and accuracy of financial records
-* Supporting month\-end and ad\-hoc finance reporting tasks
-* Coordinating with internal teams regarding finance\-related documentation
-* Performing other administrative and operational finance tasks as assigned
-**What we are looking for \- the ideal profile**
-* Currently pursuing a Bachelor’s degree in Finance, Accounting, Management Accounting, Business Administration, or a related course
-* Internship **must be a required internship** as part of the university curriculum
-* Able to commit for the full required internship period (minimum duration as required by school)
-* Basic understanding of accounting and finance principles
-* Proficient in Microsoft Suite and Google Workspace
-* Strong attention to detail and good organizational skills
-* Able to handle confidential financial information with integrity
-* Willing to learn, proactive, and able to work in a team environment
-**In return, you will be getting**
-* Join an all\-star Finance team which continues to raise the bar, with systems and processes (and company stability) at the level of sophistication of a small multinational, but with a 'start\-up' spirit of innovation and continuous improvement in an ever\-evolving world
-* In terms of learning opportunities, our organization is second to none. You will get to work on a variety of business models across many different clients as if we are 5 companies in one, and everyone is involved in projects to drive further improvement.
-* Regional teams and country Finance teams collaborate closely to ensure all finance aspects of our business are optimized, giving you a wide exposure and enhanced learning curve in a close\-knit and supportive team
-**We also offer**
-**Best of Both Worlds**
-We are a scale up: the sophistication of a small multinational, with the agility of a start\-up. This means you get to work on cutting\-edge projects, and besides your 'standard' job description, we love to see you show entrepreneurial initiative and want to see your take on how you can take your role and our company to the next level. Good ideas get implemented. You are the master of your own destiny.
- **Culture that Brings Out the Best**
-At Intrepid, culture is not just a buzzword, it is what we practice at work every day. We believe in collaboration over competition, transparency over politics, and willingness to learn over ego. You will be part of a team where people genuinely support one another, celebrate wins together, and face challenges head\-on as one. We put our all into the work but we balance it with fun, whether that is through team lunches, after\-work hangouts, events or shared laughter in the office. This is a place where you can thrive professionally while having a great time.
- **Grow Without Limits**
-Learning at Intrepid is constant and dynamic. You will have access to formal training through face\-to\-face sessions, coaching and our very own Intrepid Academy. On top of that, real\-world experience such as leading clients, working with advanced tech, and mastering best\-in\-class processes will accelerate your growth every step of the way. Surrounded by a talented team that raises the bar daily, in a rapidly growing and ever\-expanding business, the opportunities for your development are endless.
- **Rewarding You Right**
-We believe great work deserves great rewards at Intrepid. That’s why we offer competitive compensation and generous benefits, including comprehensive insurance and ample leave, to support you both in and out of the workplace. We want you to feel valued, cared for, and empowered to bring your best self to work every day.
- *Note: We will not be accepting any unsolicited resumes or CVs from headhunting or recruitment agencies at this point. Any CVs or profiles shared with us will not be entertained, and in the event of dispute, Intrepid will not be liable for any material compensation to third parties*</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>https://ph.indeed.com/cmp/Intrepid-1c14aa57</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>in-2dbb6c5d669cc55a</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>indeed</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>https://ph.indeed.com/viewjob?jk=2dbb6c5d669cc55a</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>https://intrepid.bamboohr.com/careers/1520?source=indeed&amp;src=indeed&amp;postedDate=2026-01-11</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Human Resources Intern (Required Internship Only)</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Intrepid</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Manila, P00, PH</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>46033</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>internship</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="b">
-        <v>0</v>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>**Who we are**
-Intrepid Asia is a leading Ecommerce and Digital Solutions Provider in South East Asia. We offer end\-to\-end omni\-channel ecommerce management, Livestreaming, Video production \&amp; Affiliate Management for Social Commerce plus full funnel Digital Marketing Services and advanced Market Intelligence, all powered by state of the art inhouse Technology to our client base of leading international brands across all key marketplaces and social platforms in all 6 SEA countries. Brands love our regional presence, our excellent data\-driven and growth\-focused services which are enabled by the strongest team in the industry, and our advanced marketing and tech capabilities.
-We are growing rapidly and as the exclusive partner of Flywheel in SEA, we offer many exciting opportunities to work with leading brands across multiple categories and key industry players. By joining us, you will work on the cutting edge of digital and social commerce in SEA, and experience what it takes to drive a successful ecommerce business end\-to\-end.
- **The team you will be part of**
-Our Talent \&amp; People Team is the heartbeat of our organization \- championing a culture where people thrive and potential is unlocked. From attracting top talent and shaping employee experiences to driving development, engagement, and retention, the team plays a strategic role in building and maintaining a high\-performing, empowered workforce. We are here to grow with the business and for the people behind it.
- **The part you will play**
-We are looking for a Human Resources Intern who will be an active contributor to our People Operations team. This role will report directly to our People Operations Specialist and will provide hands\-on exposure to various HR functions, supporting daily operations and ongoing initiatives.
- **As an HR Intern, you will take charge of**
-* Assisting in preparing orientation materials and schedules for new employees
-* Helping maintain employee records and ensure confidentiality
-* Supporting the resolution of employee queries and concerns
-* Assisting in organizing employee engagement activities and events
-* Assisting in maintaining and updating HR 201 files and database
-* Assisting in the preparation of HR\-related reports and documents as needed
-* Assisting in coordinating training sessions and workshops
-* Participating in the development of training materials
-* Providing general administrative support to the HR department
-* Participating in HR projects and initiatives as assigned
-**What we are looking for \- the ideal profile**
-* Currently pursuing a degree in Human Resource Management, Psychology, or other related fields, **with an internship requirement**
-* Strong written and verbal communication skills
-* Proficient in MS Office applications and Google Workspace
-* Detail\-oriented with the ability to handle sensitive and confidential information
-* Strong organizational skills with the ability to manage multiple tasks and meet deadlines
-**In return, you will be getting**
-* Tackling the sophisticated people's challenges in the rapidly evolving e\-commerce landscape with data insights and innovative solutions.
-* You will be joining an all\-star People Team that consistently raises the bar by combining the systems and processes of a small multinational with the collaborative, innovative, and agile spirit of a startup in an ever\-evolving world.
-* With our team’s rapid growth and the People Team launching new initiatives to enhance both employee experience and performance, you will benefit from a wide range of opportunities for development. Our structured learning programs covering both functional skills and broader growth are designed to support you at every stage of your journey
-* Our supportive culture and close collaboration between regional and local teams create a close\-knit work environment which many in our team love and thrive in
-**We also offer**
-**Best of Both Worlds**
-We are a scale up: the sophistication of a small multinational, with the agility of a start\-up. This means you get to work on cutting\-edge projects, and besides your 'standard' job description, we love to see you show entrepreneurial initiative and want to see your take on how you can take your role and our company to the next level. Good ideas get implemented. You are the master of your own destiny.
- **Culture that Brings Out the Best**
-At Intrepid, culture is not just a buzzword, it is what we practice at work every day. We believe in collaboration over competition, transparency over politics, and willingness to learn over ego. You will be part of a team where people genuinely support one another, celebrate wins together, and face challenges head\-on as one. We put our all into the work but we balance it with fun, whether that is through team lunches, after\-work hangouts, events or shared laughter in the office. This is a place where you can thrive professionally while having a great time.
- **Grow Without Limits**
-Learning at Intrepid is constant and dynamic. You will have access to formal training through face\-to\-face sessions, coaching and our very own Intrepid Academy. On top of that, real\-world experience such as leading clients, working with advanced tech, and mastering best\-in\-class processes will accelerate your growth every step of the way. Surrounded by a talented team that raises the bar daily, in a rapidly growing and ever\-expanding business, the opportunities for your development are endless.
- **Rewarding You Right**
-We believe great work deserves great rewards at Intrepid. That’s why we offer competitive compensation and generous benefits, including comprehensive insurance and ample leave, to support you both in and out of the workplace. We want you to feel valued, cared for, and empowered to bring your best self to work every day.
- *Note: We will not be accepting any unsolicited resumes or CVs from headhunting or recruitment agencies at this point. Any CVs or profiles shared with us will not be entertained, and in the event of dispute, Intrepid will not be liable for any material compensation to third parties*</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>https://ph.indeed.com/cmp/Intrepid-1c14aa57</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>in-f1e13e490a93b540</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>indeed</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://ph.indeed.com/viewjob?jk=f1e13e490a93b540</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>http://ph.indeed.com/job/it-programming-intern-f1e13e490a93b540</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>IT / Programming Intern</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Lucky Boba</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Sangandaan, P00, PH</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>46032</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>temporary, internship</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="b">
-        <v>0</v>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>luckyboba.hr@gmail.com</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>**We're Hiring Interns!**
-Are you passionate about technology and eager to gain  
-hands\-on experience in IT and programming? Join our team and kickstart your  
-career!
-**Position:** IT / Programming Intern
-**Who We’re Looking For:**  
-**Students currently pursuing:**
-IT Programming  
-Computer Engineering  
-Computer Science  
-Any Programming\-related course
-**What You’ll Do:**  
-Assist in software development and coding projects  
-Support IT operations and system maintenance  
-Collaborate with our tech team on real\-world projects  
-Learn best practices in programming, debugging, and testing
-**What We’re Looking For:**  
-Strong interest in programming and technology  
-Basic knowledge of programming languages (e.g., Java, Python, C\#, or JavaScript)  
-Eagerness to learn and take on challenges  
-Good communication and teamwork skills
-**Perks \&amp; Benefits:**  
-Hands\-on experience in real projects  
-Mentorship from experienced developers  
-Flexible working hours  
-Certificate of Internship upon completion
-**How to Apply:**  
-Submit your CV \&amp; Portfolio**: luckyboba.hr@gmail.com**
-Start your tech journey with us!
-Job Types: Temporary, OJT (On the job training)  
-Contract length: 3 months
-Benefits:
-* Flexible schedule
-* Flextime
-Work Location: In person</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>https://ph.indeed.com/cmp/Lucky-Boba-1</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>li-4332535951</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>linkedin</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4332535951</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Technician 1 Monitoring Services (Technical Support)</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Risewave Consulting, Inc.</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Quezon City, National Capital Region, Philippines</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>46034</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="b">
-        <v>0</v>
-      </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>https://ph.linkedin.com/company/risewave-consulting-inc</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>li-4359997663</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>linkedin</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4359997663</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Multi Skilled Technician (Taguig)</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>JLL</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Taguig, National Capital Region, Philippines</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>46034</v>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="b">
-        <v>0</v>
-      </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/jll</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>li-4352672394</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>linkedin</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/jobs/view/4352672394</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>PHL Senior Technician - L3 - Represented/Tariff</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Dow</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Las Piñas, National Capital Region, Philippines</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>46034</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/dow-chemical</t>
+          <t>https://ph.indeed.com/cmp/Agile-Tech-Ops-Ince</t>
         </is>
       </c>
       <c r="W8" t="inlineStr"/>
@@ -1272,7 +1369,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>li-4351866176</t>
+          <t>li-4355150222</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1282,27 +1379,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4351866176</t>
+          <t>https://www.linkedin.com/jobs/view/4355150222</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Multi-Skilled Technician -Lipa</t>
+          <t>NAPA Technician</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CBRE Asia Pacific</t>
+          <t>Ng Khai Development Corporation</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lipa, Calabarzon, Philippines</t>
+          <t>Cebu, Central Visayas, Philippines</t>
         </is>
       </c>
       <c r="H9" s="2" t="n">
-        <v>46034</v>
+        <v>46036</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
@@ -1321,7 +1418,7 @@
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>https://sg.linkedin.com/company/cbre-asia-pacific</t>
+          <t>https://ph.linkedin.com/company/ng-khai-development-corporation</t>
         </is>
       </c>
       <c r="W9" t="inlineStr"/>
@@ -1340,7 +1437,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>li-4345396142</t>
+          <t>li-4355110581</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1350,27 +1447,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4345396142</t>
+          <t>https://www.linkedin.com/jobs/view/4355110581</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Multi-Skilled Technician - Lipa</t>
+          <t>Multi Skilled Technician</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CBRE Asia Pacific</t>
+          <t>FPD ASIA PROPERTY SERVICES, INC.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lipa, Calabarzon, Philippines</t>
+          <t>Taguig, National Capital Region, Philippines</t>
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>46034</v>
+        <v>46036</v>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
@@ -1389,7 +1486,7 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>https://sg.linkedin.com/company/cbre-asia-pacific</t>
+          <t>https://ph.linkedin.com/company/fpd-asia-property-services-inc-</t>
         </is>
       </c>
       <c r="W10" t="inlineStr"/>
@@ -1408,7 +1505,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>li-4334726725</t>
+          <t>li-4346096853</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1418,23 +1515,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4334726725</t>
+          <t>https://www.linkedin.com/jobs/view/4346096853</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Renewables Technical Lead</t>
+          <t>SERVICE TECHNICIAN (SAN PEDRO OFFICE BASED)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aggreko</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
+          <t>EPTA GROUP</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Muntinlupa City, National Capital Region, Philippines</t>
+        </is>
+      </c>
       <c r="H11" s="2" t="n">
-        <v>46033</v>
+        <v>46036</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
@@ -1453,7 +1554,7 @@
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
-          <t>https://uk.linkedin.com/company/aggreko</t>
+          <t>https://it.linkedin.com/company/epta-group</t>
         </is>
       </c>
       <c r="W11" t="inlineStr"/>
@@ -1472,7 +1573,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>li-4359964843</t>
+          <t>li-4355013135</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1482,27 +1583,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4359964843</t>
+          <t>https://www.linkedin.com/jobs/view/4355013135</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Multi Skilled Technician</t>
+          <t>Multi - Skilled Technician</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>Med-Metrix</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Makati, National Capital Region, Philippines</t>
+          <t>Pasig, National Capital Region, Philippines</t>
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>46033</v>
+        <v>46036</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
@@ -1521,7 +1622,7 @@
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/jll</t>
+          <t>https://www.linkedin.com/company/med-metrix</t>
         </is>
       </c>
       <c r="W12" t="inlineStr"/>
@@ -1540,7 +1641,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>li-4360643379</t>
+          <t>li-4354868085</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1550,27 +1651,23 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4360643379</t>
+          <t>https://www.linkedin.com/jobs/view/4354868085</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Multi Skilled Technician</t>
+          <t>Technical Lead (Senior Full Stack)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JLL</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Batangas, Calabarzon, Philippines</t>
-        </is>
-      </c>
+          <t>Mediatropy</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" s="2" t="n">
-        <v>46033</v>
+        <v>46036</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
@@ -1589,7 +1686,7 @@
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/jll</t>
+          <t>https://sg.linkedin.com/company/mediatropy</t>
         </is>
       </c>
       <c r="W13" t="inlineStr"/>
@@ -1608,7 +1705,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>li-4345212547</t>
+          <t>li-4354705043</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1618,27 +1715,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4345212547</t>
+          <t>https://www.linkedin.com/jobs/view/4354705043</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Deskside Technician</t>
+          <t>STP Technician</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stefanini North America and APAC</t>
+          <t>Metro Pacific Water Solutions, Inc.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pasay, National Capital Region, Philippines</t>
+          <t>Davao, Davao Region, Philippines</t>
         </is>
       </c>
       <c r="H14" s="2" t="n">
-        <v>46032</v>
+        <v>46035</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
@@ -1657,7 +1754,7 @@
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr">
         <is>
-          <t>https://br.linkedin.com/company/stefanini-na-apac</t>
+          <t>https://ph.linkedin.com/company/metro-pacific-water-solutions</t>
         </is>
       </c>
       <c r="W14" t="inlineStr"/>
@@ -1676,7 +1773,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>li-4334598816</t>
+          <t>li-4361169891</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1686,27 +1783,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4334598816</t>
+          <t>https://www.linkedin.com/jobs/view/4361169891</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Service Technician Castilla y León</t>
+          <t>Sr Tech Svc Desk</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vestas</t>
+          <t>Unisys</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Buenavista, Western Visayas, Philippines</t>
+          <t>Manila, National Capital Region, Philippines</t>
         </is>
       </c>
       <c r="H15" s="2" t="n">
-        <v>46032</v>
+        <v>46035</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
@@ -1725,7 +1822,7 @@
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
-          <t>https://dk.linkedin.com/company/vestas</t>
+          <t>https://www.linkedin.com/company/unisys</t>
         </is>
       </c>
       <c r="W15" t="inlineStr"/>
@@ -1744,7 +1841,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>li-4350237071</t>
+          <t>li-4308923917</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1754,27 +1851,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4350237071</t>
+          <t>https://www.linkedin.com/jobs/view/4308923917</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Technician I, Managed Services</t>
+          <t>Technician III</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Copeland</t>
+          <t>Microchip Technology Inc.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Quezon City, National Capital Region, Philippines</t>
+          <t>Davao, Davao Region, Philippines</t>
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>46032</v>
+        <v>46035</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
@@ -1793,7 +1890,7 @@
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/copeland</t>
+          <t>https://www.linkedin.com/company/microchip-technology</t>
         </is>
       </c>
       <c r="W16" t="inlineStr"/>
@@ -1812,7 +1909,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>li-4350286936</t>
+          <t>li-4354495027</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1822,27 +1919,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4350286936</t>
+          <t>https://www.linkedin.com/jobs/view/4354495027</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Technician I, Managed Sevices</t>
+          <t>Mega FM Technician, SPX Express (Zone 1 - Parañaque / Las Piñas)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Copeland</t>
+          <t>SPX Express</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Quezon City, National Capital Region, Philippines</t>
+          <t>Manila, National Capital Region, Philippines</t>
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>46032</v>
+        <v>46035</v>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
@@ -1861,7 +1958,7 @@
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/copeland</t>
+          <t>https://www.linkedin.com/company/spx-express</t>
         </is>
       </c>
       <c r="W17" t="inlineStr"/>
@@ -1880,7 +1977,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>li-4359757191</t>
+          <t>li-4340379368</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1890,27 +1987,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4359757191</t>
+          <t>https://www.linkedin.com/jobs/view/4340379368</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Medewerker Technische Dienst</t>
+          <t>Motorpool Service Technician/Mechanical Technician</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stayokay</t>
+          <t>Aboitiz Foods</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bacnotan, Ilocos Region, Philippines</t>
+          <t>Iligan, Northern Mindanao, Philippines</t>
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>46032</v>
+        <v>46035</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
@@ -1929,7 +2026,7 @@
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr">
         <is>
-          <t>https://nl.linkedin.com/company/stayokay</t>
+          <t>https://ph.linkedin.com/company/aboitiz-foods</t>
         </is>
       </c>
       <c r="W18" t="inlineStr"/>
@@ -1948,7 +2045,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>li-4350187030</t>
+          <t>li-4354460426</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1958,27 +2055,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4350187030</t>
+          <t>https://www.linkedin.com/jobs/view/4354460426</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Technician I, Managed Services</t>
+          <t>Multi-Skilled Technician - Lipa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Copeland</t>
+          <t>CBRE Asia Pacific</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Quezon City, National Capital Region, Philippines</t>
+          <t>Lipa, Calabarzon, Philippines</t>
         </is>
       </c>
       <c r="H19" s="2" t="n">
-        <v>46032</v>
+        <v>46034</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
@@ -1997,7 +2094,7 @@
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/copeland</t>
+          <t>https://sg.linkedin.com/company/cbre-asia-pacific</t>
         </is>
       </c>
       <c r="W19" t="inlineStr"/>
@@ -2016,7 +2113,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>li-4345577544</t>
+          <t>li-4325695361</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2026,23 +2123,23 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4345577544</t>
+          <t>https://www.linkedin.com/jobs/view/4325695361</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>IS Technician - ISHELP</t>
+          <t>Technology - Infrastructure, Summer Analyst (Internship), Philippines, 2026</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>GHD</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cebu, Central Visayas, Philippines</t>
+          <t>Taguig, National Capital Region, Philippines</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -2063,7 +2160,7 @@
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
         <is>
-          <t>https://au.linkedin.com/company/ghd</t>
+          <t>https://www.linkedin.com/company/citi</t>
         </is>
       </c>
       <c r="W20" t="inlineStr"/>
@@ -2082,7 +2179,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>li-4351819555</t>
+          <t>li-4359145289</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2092,23 +2189,23 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4351819555</t>
+          <t>https://www.linkedin.com/jobs/view/4359145289</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Multi Skilled Technician</t>
+          <t>Field Service/Biomed Technician</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FPD ASIA PROPERTY SERVICES, INC.</t>
+          <t>OMNIBUS BIO-MEDICAL SYSTEMS INC.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Taguig, National Capital Region, Philippines</t>
+          <t>Hinatuan, Caraga, Philippines</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
@@ -2129,7 +2226,7 @@
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr">
         <is>
-          <t>https://ph.linkedin.com/company/fpd-asia-property-services-inc-</t>
+          <t>https://ph.linkedin.com/company/omnibus-bio-medical-systems-incorporated</t>
         </is>
       </c>
       <c r="W21" t="inlineStr"/>
@@ -2148,7 +2245,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>li-4332549682</t>
+          <t>li-4359003442</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2158,25 +2255,21 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4332549682</t>
+          <t>https://www.linkedin.com/jobs/view/4359003442</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Pump Technician</t>
+          <t>VIP Gulfstream Technician</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trade One Incorporated</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Quezon City, National Capital Region, Philippines</t>
-        </is>
-      </c>
+          <t>AEXTECH</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
@@ -2195,7 +2288,7 @@
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr">
         <is>
-          <t>https://ph.linkedin.com/company/tradeoneincorporated</t>
+          <t>https://ph.linkedin.com/company/aextech</t>
         </is>
       </c>
       <c r="W22" t="inlineStr"/>
@@ -2214,7 +2307,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>li-4361161826</t>
+          <t>li-4357623505</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2224,23 +2317,23 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4361161826</t>
+          <t>https://www.linkedin.com/jobs/view/4357623505</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Multi-Skilled Technician</t>
+          <t>IS Technician - ISHELP Americas</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CBRE Asia Pacific</t>
+          <t>GHD</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lipa, Calabarzon, Philippines</t>
+          <t>Cebu, Central Visayas, Philippines</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
@@ -2261,7 +2354,7 @@
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr">
         <is>
-          <t>https://sg.linkedin.com/company/cbre-asia-pacific</t>
+          <t>https://au.linkedin.com/company/ghd</t>
         </is>
       </c>
       <c r="W23" t="inlineStr"/>
@@ -2280,7 +2373,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>li-4354460426</t>
+          <t>li-4359104125</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2290,25 +2383,21 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4354460426</t>
+          <t>https://www.linkedin.com/jobs/view/4359104125</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Multi-Skilled Technician - Lipa</t>
+          <t>Salesforce Technical Lead (Work from home)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CBRE Asia Pacific</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Lipa, Calabarzon, Philippines</t>
-        </is>
-      </c>
+          <t>Application House</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
@@ -2317,7 +2406,7 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
@@ -2327,7 +2416,7 @@
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr">
         <is>
-          <t>https://sg.linkedin.com/company/cbre-asia-pacific</t>
+          <t>https://uk.linkedin.com/company/application-house</t>
         </is>
       </c>
       <c r="W24" t="inlineStr"/>
@@ -2346,7 +2435,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>li-4345634591</t>
+          <t>li-4357607586</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2356,23 +2445,23 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4345634591</t>
+          <t>https://www.linkedin.com/jobs/view/4357607586</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>SAP Academy for Services &amp; Consulting (APAC) - Technical Quality Manager (TQM) - Philippines</t>
+          <t>Pump Technician</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Trade One Incorporated</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Taguig, National Capital Region, Philippines</t>
+          <t>Quezon City, National Capital Region, Philippines</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -2393,7 +2482,7 @@
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr">
         <is>
-          <t>https://de.linkedin.com/company/sap</t>
+          <t>https://ph.linkedin.com/company/tradeoneincorporated</t>
         </is>
       </c>
       <c r="W25" t="inlineStr"/>
@@ -2409,6 +2498,204 @@
       <c r="AG25" t="inlineStr"/>
       <c r="AH25" t="inlineStr"/>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>li-4362701531</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>linkedin</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4362701531</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Senior Technician, Probe PMEE</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Allegro MicroSystems</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>National Capital Region, Philippines</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="b">
+        <v>0</v>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/allegro-microsystems</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>li-4348356368</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>linkedin</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4348356368</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Technician 3, Engineering Services</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Analog Devices</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Cavite, Calabarzon, Philippines</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="b">
+        <v>0</v>
+      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/analog-devices</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>li-4359024458</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>linkedin</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4359024458</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Senior Software, Platform, or Product Engineer (Technical Lead)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>PCI Tech Center</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Manila, National Capital Region, Philippines</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="b">
+        <v>0</v>
+      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>https://ph.linkedin.com/company/pcitechcenter</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/iTrack/scraped_jobs.xlsx
+++ b/iTrack/scraped_jobs.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH16"/>
+  <dimension ref="A1:AH23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -607,7 +607,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>in-6215084bb377a242</t>
+          <t>in-18c7462de88ed3f3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -617,31 +617,31 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://ph.indeed.com/viewjob?jk=6215084bb377a242</t>
+          <t>https://ph.indeed.com/viewjob?jk=18c7462de88ed3f3</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://joinbytedance.com/search/7595897579285694725</t>
+          <t>http://ph.indeed.com/job/accounting-intern-hybrid-setup-18c7462de88ed3f3</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Category &amp; Creator Intern Project Intern (Mother, Baby and Health, E-Commerce) - 2026 Start (BS/MS)</t>
+          <t>Accounting Intern (Hybrid Setup)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ByteDance</t>
+          <t>Greenpoint Business Consultancy Inc.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Manila, P00, PH</t>
+          <t>Makati, P00, PH</t>
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>46038</v>
+        <v>46045</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -654,104 +654,47 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>-earlycareers@bytedance.com</t>
-        </is>
-      </c>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr">
         <is>
-          <t>**Location:**  
-Taguig
-**Team:**  
-Commerce ops
-**Employment Type:**  
-Intern
-**Job Code:**  
-A240211
-Responsibilities
-FMCG, Fast Moving Consumer Goods, Mother, Baby and Health team focuses on driving the growth of the growing the Mom \&amp; Baby and Health business on eCommerce via seller and creator initiatives.
-The intern will be able to help gather and analyze category insights, as well as get first hand experience in creator management and growth. This involves strategic planning and direct communication with relevant category creators, and various initiatives related to Mom \&amp; Baby and Health creator growth.
-**What you will gain:**  
-* Practical experience in E\-commerce category operations, competitor analysis, and creator management.
-* Opportunities to collaborate with and learn from experienced professionals.
-* Insights into market trends and strategic decision\-making
-As a project intern, you will have the opportunity to engage in impactful short\-term projects that provide you with a glimpse of professional real\-world experience. You will gain practical skills through on\-the\-job learning in a fast\-paced work environment and develop a deeper understanding of your career interests.
-Applications will be reviewed on a rolling basis \- we encourage you to apply early.
-Responsibilities
-Category Data Tracking \&amp; Analysis Support
-* Update performance trackers to monitor key metrics and areas for improvement
-* Support in strategizing and executing plans to address key category priorities and projects
-Competitor Analysis
-* Conduct in\-depth studies of competitor actions and strategies, providing recommendations for counteraction plans
-* Reach out to top sellers on other platforms to onboard on the platform
-* Analyze price competitiveness to inform pricing strategies and enhance market positioning
-Creator Management
-* Assist the Creator Manager/s in outreaching and onboarding new category creators
-* Provide executional support in setting up promotional tools and mounting special projects in order to achieve creator GMV targets and growth
-Qualifications
-Minimum Qualifications
-* Currently pursuing an Undergraduate/Master in business or a related discipline.
-* Strong analytical skills with attention to detail.
-* Excellent organizational and project management abilities.
-* Strong written and verbal communication skills.
-* Ability to work collaboratively and adapt in a dynamic environment.
-Preferred Qualifications
-* Comfortable working with cross\-functional teams in a fast\-paced environment.
-* Previous internship or organizational experience related to content operations, communications, or community building is an advantage.
-* Familiar or experience with eCommerce platform
-If you have any questions, please reach out to us at apac\-earlycareers@bytedance.com
-Job Information
-About Us
-Founded in 2012, ByteDance's mission is to inspire creativity and enrich life. With a suite of more than a dozen products, including TikTok, Lemon8, CapCut and Pico as well as platforms specific to the China market, including Toutiao, Douyin, and Xigua, ByteDance has made it easier and more fun for people to connect with, consume, and create content.
-Why Join ByteDance
-Inspiring creativity is at the core of ByteDance's mission. Our innovative products are built to help people authentically express themselves, discover and connect – and our global, diverse teams make that possible. Together, we create value for our communities, inspire creativity and enrich life \- a mission we work towards every day.
-As ByteDancers, we strive to do great things with great people. We lead with curiosity, humility, and a desire to make impact in a rapidly growing tech company. By constantly iterating and fostering an "Always Day 1" mindset, we achieve meaningful breakthroughs for ourselves, our Company, and our users. When we create and grow together, the possibilities are limitless. Join us.
-Diversity \&amp; Inclusion
-ByteDance is committed to creating an inclusive space where employees are valued for their skills, experiences, and unique perspectives. Our platform connects people from across the globe and so does our workplace. At ByteDance, our mission is to inspire creativity and enrich life. To achieve that goal, we are committed to celebrating our diverse voices and to creating an environment that reflects the many communities we reach. We are passionate about this and hope you are too.</t>
+          <t>**Company Description**
+Greenpoint is a full suite financial services solutions company offering outsourced bookkeeping, accounting, audit, and corporate financial services to startups, SMEs and family businesses. Our core values lie on SEED \- Sustainability, Empathy, Evolution, and Drive. Founded in early 2021, we aim to provide end\-to\-end, more affordable, and easily scalable solutions that fit to each of the unique needs of the companies we work with. Our team members have worked in the industries of retail, ecommerce, food and restaurants, healthcare and diagnostics, real estate, distribution, financial services, tech, and energy among others.
+**Role Description**
+This is an internship role for an Accounting Intern with a hybrid work arrangement located in Makati and some flexibility for remote work. The Accounting Intern will be responsible for day\-to\-day activities such as preparing financial statements, utilizing accounting software, conducting journal entries, financial analysis, and other finance\-related activities that the operations require. The Accounting Intern will also work closely with Senior Accountants or the Operations Manager to develop and implement standard accounting processes in a timely and efficient manner.
+**REQUIREMENTS:**
+* Currently enrolled in courses related to BS Accountancy or Management Accounting (pref. graduating)
+* Must have access to a personal laptop.
+Job Type: OJT (On the job training)
+Pay: From Php600\.00 per week upon completion of 40 hrs.
+Job Type: OJT (On the job training)
+Pay: Php600\.00 \- Php800\.00 per week
+Benefits:
+* Flexible schedule
+* Paid training
+* Promotion to permanent employee
+* Work from home
+Application Question(s):
+* Do you have a personal laptop available for use throughout the internship? (Yes/No)
+Work Location: In person</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
-          <t>https://ph.indeed.com/cmp/Bytedance</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>https://d2q79iu7y748jz.cloudfront.net/s/_squarelogo/256x256/8f4d80ac074d9a65cbadcaa7d49cd411</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>http://www.bytedance.com</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Beijing, Beijing</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10,000+</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Decline to state</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>ByteDance is a global incubator of platforms at the cutting edge of commerce, content and entertainment services - over 1.9 billion people interact with ByteDance products monthly.</t>
-        </is>
-      </c>
+          <t>https://ph.indeed.com/cmp/Greenpoint-Business-Consultancy-Inc.</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr"/>
@@ -762,37 +705,45 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>li-4360097768</t>
+          <t>in-7d7ed0625019b1a1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>indeed</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4360097768</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>https://ph.indeed.com/viewjob?jk=7d7ed0625019b1a1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>http://ph.indeed.com/job/digital-marketing-intern-7d7ed0625019b1a1</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Service Technician (Urgent hiring)</t>
+          <t>Digital Marketing Intern</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hino Truck Dealership</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>Homeschool Global Learning Inc.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Pasig, P00, PH</t>
+        </is>
+      </c>
       <c r="H3" s="2" t="n">
-        <v>46039</v>
+        <v>46045</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>fulltime</t>
+          <t>internship</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
@@ -803,59 +754,66 @@
       <c r="O3" t="b">
         <v>0</v>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>associate</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Manufacturing</t>
-        </is>
-      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr">
         <is>
-          <t>* Installing new vehicle wiring systems.
-* Installing and troubleshooting immobilizer and alarm systems.
-* Gathering information from customers about issues with their electrical system.
-* Diagnosing electrical issues and proposing a course of action.
-* Providing customers with estimated time and cost for repairs.
-* Servicing of electrical automotive parts.
- Job Type: Full\-time
-**Benefits**
-* Company events
-* Opportunities for promotion
-* Promotion to permanent employee
-**Schedule**
-* 8 hour shift
-* Day shift
-* With Bachelor's Degree in Automotive Technology/Electrical Engineering or Electronics) or NC I/ NC II or equivalent
-* Has exposure to ref\-van cooling system.
-* Ability to demonstrate professionalism in the workplace at all times
-* Excellent customer service skills
-* Strong problem\-solving skills
-* With knowledge of modern vehicular electrical systems
-* Willing to be assigned in Hino Jose Abad Santos
-* Available to start anytime</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Motor Vehicle Manufacturing</t>
-        </is>
-      </c>
+          <t>**Role Overview**
+The Digital Marketing Intern will support the Digital Marketing Officer in executing day\-to\-day digital marketing activities for Yudu Learning App. This role is ideal for students or fresh graduates who want hands\-on experience in performance marketing, social media management, content production, and analytics within a fast\-growing edtech environment.
+The intern will gain practical exposure to real campaigns, real metrics, and real business impact—beyond purely academic tasks.
+**Key Responsibilities**
+**Campaign \&amp; Ads Support**
+* Assist in setting up, monitoring, and updating paid ad campaigns across Meta and TikTok
+* Help prepare ad copies, variations, and creative briefs for testing
+* Track daily campaign performance and flag issues or anomalies
+**Social Media \&amp; Content Execution**
+* Assist in day\-to\-day social media posting across Yudu’s platforms
+* Help draft captions, hashtags, and basic ad or post copy
+* Support community management by responding to comments and messages under guidance
+* Assist in producing simple content such as short videos, reels, carousels, or basic graphics
+**Reporting \&amp; Data Assistance**
+* Help gather data for weekly and monthly reports
+* Assist in updating tracking sheets and dashboards
+* Support basic performance analysis (e.g., top\-performing posts, ads, or formats)
+**Research \&amp; Trend Spotting**
+* Monitor social media and digital marketing trends, especially in education, parenting, and mobile apps
+* Research competitor content, ads, and campaigns
+* Compile insights and recommendations for testing
+**Marketing Operations \&amp; Coordination**
+* Assist in coordinating with designers, videographers, or content contributors
+* Help ensure proper file naming, content scheduling, and asset organization
+* Support ad\-hoc marketing tasks as needed
+**Tools \&amp; Exposure**
+* Meta Ads Manager and TikTok Ads (guided)
+* Social media platforms (Facebook, Instagram, TikTok)
+* Google Sheets and basic dashboards
+* App store analytics (Play Store / App Store – view access)
+* Content scheduling and collaboration tools
+**Qualifications**
+* Currently enrolled in or recently graduated from Marketing, Communications, Business, Multimedia, or related programs
+* Strong interest in digital marketing, social media, and content creation
+* Basic writing and communication skills
+* Willingness to learn analytics, ads, and campaign optimization
+* Organized, detail\-oriented, and reliable
+**Preferred Attributes**
+* Familiarity with social media platforms and trends
+* Basic video editing or graphic design skills (Canva, CapCut, etc.) is a plus
+* Interest in education, tech, or mobile apps
+* Proactive attitude and openness to feedback
+Job Type: OJT (On the job training)  
+Contract length: 2 months
+Work Location: In person</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
-          <t>https://ph.linkedin.com/company/hinotrucks</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>https://media.licdn.com/dms/image/v2/D560BAQEZ57sUMfNE_g/company-logo_100_100/company-logo_100_100/0/1684307650334/hinotrucks_logo?e=2147483647&amp;v=beta&amp;t=AyaiUU_x1eLnNGDGk-zFGgfnF27vyq2HDpIv7FYHBSY</t>
-        </is>
-      </c>
+          <t>https://ph.indeed.com/cmp/Homeschool-Global-Learning-Inc.-1</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
@@ -871,41 +829,45 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>li-4315990898</t>
+          <t>in-4082a008b72034ed</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>indeed</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4315990898</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>https://ph.indeed.com/viewjob?jk=4082a008b72034ed</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>http://ph.indeed.com/job/content-creation-intern-4082a008b72034ed</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Technician I Monitoring Service</t>
+          <t>Content Creation Intern</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Copeland</t>
+          <t>AHG Lab</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Quezon City, National Capital Region, Philippines</t>
+          <t>Taguig, P00, PH</t>
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>46039</v>
+        <v>46045</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>fulltime</t>
+          <t>internship</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -914,78 +876,65 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="b">
-        <v>0</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>entry level</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr">
         <is>
-          <t>**About Us**
- We are a global climate technologies company engineered for sustainability. We create sustainable and efficient residential, commercial and industrial spaces through HVACR technologies. We protect temperature\-sensitive goods throughout the cold chain. And we bring comfort to people globally. Best\-in\-class engineering, design and manufacturing combined with category\-leading brands in compression, controls, software and monitoring solutions result in next\-generation climate technology that is built for the needs of the world ahead.
- Whether you are a professional looking for a career change, an undergraduate student exploring your first opportunity, or recent graduate with an advanced degree, we have opportunities that will allow you to innovate, be challenged and make an impact. Join our team and start your journey today!
-**JOB OBJECTIVE**
- This position is required to perform basic and advanced support for alarm management and to professionally handle, monitor and process refrigeration and HVAC alarms, including but not limited to: diagnosing, interrogating, troubleshooting via connecting to customer software, relaying refrigeration / HVAC alarms, and other customer requests pursuant to customer specifications for a 24/7 department operations.
- This position is also required to answer inbound calls, service requests, confirm work orders, perform graph analysis and troubleshooting of refrigeration and HVAC alarms of Basic and Resolution Food Retail customers.
-**Responsibilities And Outputs**
-**MAIN DUTIES**
-**Alarm Management \&amp; Smart Dispatch**
-* Responsible for interrogation of refrigeration and/or HVAC alarms received and diagnosing them based on Service Level Agreement with external customers.
-* Deliver alarm information with accurate documentation by calling or sending email to external customers.
-* Provide sound decision based on alarm history and graph analysis.
-* Update and confirm completed work orders pursuant to customer procedures.
-* Answer inbound and transferred calls and address them as necessary
-**Additional Functions**
- Other functions that may arise.
-**JOB SPECIFICATIONS**
-**EDUCATIONAL BACKGROUND**
- Graduate of any 4\-year degree
-**Work Experience Or Training**
- Fresh graduate is acceptable
- Preferred with experience gained from interactive customer service and related functions.
- Background in offshore service operations is an advantage
-**Skills And Abilities**
- Computer Applications such as MS Office (Basic Knowledge in MS Outlook, MS Word, MS Powerpoint, Sharepoint and Basic Knowledge in MS Excel)
- Managed Services business systems and tools (Salesforce, Connect\+, Genesys)
-**Other Work Conditions**
-* Willing to Work on Shifting operations which may include Work on Weekends, to support the assigned business and customers.
-* Willing to render overtime or rest day overtime on a voluntary basis when operational needs arise during critical days and/or peak season
-* Must be able to Effectively and Independently function while maintaining a Positive Energy level in an environment of constantly shifting demands.
-**Our Commitment to Our People**
- Across the globe, we are united by a singular Purpose: Sustainability is no small ambition. That’s why everything we do is geared toward a sustainable future—for our generation and all those to come. Through groundbreaking innovations, HVACR technology and cold chain solutions, we are reducing carbon emissions and improving energy efficiency in spaces of all sizes, from residential to commercial to industrial.
- Our employees are our greatest strength. We believe that our culture of passion, openness, and collaboration empowers us to work toward the same goal \- to make the world a better place. We invest in the end\-to\-end development of our people, beginning at onboarding and through senior leadership, so they can thrive personally and professionally.
- Flexible and competitive benefits plans offer the right options to meet your individual/family needs. We provide employees with flexible time off plans, including paid parental leave (maternal and paternal), vacation and holiday leave.
- Together, we have the opportunity – and the power – to continue to revolutionize the technology behind air conditioning, heating and refrigeration, and cultivate a better future. Learn more about us and how you can join our team!
-**Our Commitment to Inclusion \&amp; Belonging**
- At Copeland, we cultivate a strong sense of inclusion and belonging where individuals of all backgrounds, and with diverse perspectives, are embraced and treated fairly to enable a stronger workforce. Our employee resource groups play an important role in culture and community building at Copeland.
-**Equal Opportunity Employer**
- Copeland is an Equal Opportunity/Affirmative Action employer. All qualified applicants will receive consideration for employment without regard to sex, race, color, religion, national origin, age, marital status, political affiliation, sexual orientation, gender identity, genetic information, disability or protected veteran status. We are committed to providing a workplace free of any discrimination or harassment.</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Climate Technology Product Manufacturing</t>
-        </is>
-      </c>
+          <t>**ABOUT THE COMPANY:**
+GoGym is a tech\-enabled pocket Gym which enables Filipinos to access health and wellness anywhere they go. At GoGym, we aim to provide affordable and accessible gyms to everyone, extending our reach on health and fitness into the online presence through our mobile app.
+**ABOUT THE JOB:**
+We are seeking a creative and data\-driven Content Creation Intern to join our team. The ideal candidate will have a passion for social media, a keen eye for design, and a strategic mindset. The intern will be responsible for creating engaging content, managing content calendars, analyzing social media performance, and assisting with Facebook Ads campaigns.
+**HOW TO APPLY:**
+Send us your:
+* updated resume or CV
+* portfolio or any material showcasing your experience in content creation, including both video and graphic content
+**JOB RESPONSIBILITIES:**
+* **Content Creation:** Develop and design eye\-catching reels and static posts for Instagram and Facebook that align with our brand’s voice and aesthetic.
+* **Content Calendar Management:** Create and maintain a content calendar to strategically plan and schedule posts, ensuring a consistent and engaging presence across social media platforms.
+* **Copywriting \&amp; Editing:** Write compelling and on\-brand copy for social media posts, ads, and other digital content. Perform editing tasks for both written content and multimedia.
+* **Graphic Design \&amp; Video Editing:** Utilize Canva and basic Adobe Suite tools to create visually appealing graphics, and perform basic video editing for social media content.
+* **Data Analysis:** Monitor and analyze social media performance metrics such as reach, engagement, and awareness. Generate reports and propose strategies based on data insights to improve social media presence and effectiveness.
+* **Facebook Ads:** Assist in planning, executing, and optimizing Facebook Ads campaigns to achieve marketing objectives.
+**JOB QUALIFICATIONS:**
+* Currently pursuing or recently completed a degree in **Marketing**, **Communications**, **Graphic Design**, or a related field.
+* Strong proficiency in Canva; basic knowledge of Adobe Creative Suite tools (Photoshop, Illustrator, Premiere Pro, etc.).
+* Experience with video editing software and basic video editing skills.
+* Knowledge of social media platforms, particularly Instagram and Facebook, and a strong understanding of their best practices.
+* Analytical mindset with the ability to interpret social media data and generate actionable insights.
+* Excellent communication and copywriting skills.
+* Ability to manage multiple tasks and projects with strong attention to detail.
+* Creative thinker with a passion for storytelling and visual design.
+**WHY WORK WITH US?**
+* Diversity and inclusion
+* Work\-life balance
+* Flexible working hours
+* Amazing growth opportunities
+* Competitive compensation
+* Work with a young, passionate, and friendly team
+* Free walk\-in to any GoGym branch throughout the internship period
+Job Type: OJT (On the job training)  
+Contract length: 6 months
+Pay: Php3,500\.00 per month
+Benefits:
+* Flexible schedule
+* Flextime
+* Gym membership
+* Paid training
+* Work from home
+Work Location: In person</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/copeland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>https://media.licdn.com/dms/image/v2/D560BAQFB1nmUiuousg/company-logo_100_100/company-logo_100_100/0/1690464855164/copeland_hq_logo?e=2147483647&amp;v=beta&amp;t=ocvydZtz2w62gpAmELm1A4RlK-C1vBfe9lD4C0bJxKc</t>
-        </is>
-      </c>
+          <t>https://ph.indeed.com/cmp/Ahg-Lab-1</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
@@ -1001,43 +950,43 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>li-4363722523</t>
+          <t>in-0c5f72dae79b9fe4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>indeed</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4363722523</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>https://ph.indeed.com/viewjob?jk=0c5f72dae79b9fe4</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://tecsurge.com/careers/797-senior-hr-officer</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tech Svc Desk - L1</t>
+          <t>Senior HR Officer</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Unisys</t>
+          <t>TecSurge</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Manila, National Capital Region, Philippines</t>
+          <t>Cebu City, P07, PH</t>
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>46038</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>fulltime</t>
-        </is>
-      </c>
+        <v>46044</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -1046,54 +995,96 @@
       <c r="O5" t="b">
         <v>0</v>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>entry level</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Engineering and Information Technology</t>
-        </is>
-      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
-          <t>GlobalRecruiting@unisys.com</t>
+          <t>careers@tecsurge.com</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>**What Success Looks Like In This Role**
-* Answers moderately complex questions, following guidelines and using judgment based on experience with related incidents and service requests.
-* Requests handled include support of hardware, software, client and COTS applications as well as network and user administration.
-* Escalates complex problems to other resolver teams or vendors.
-* Utilizes problem solving and analytical skills to effectively resolve challenging incidents.
-* Supports L1 agents in ongoing day to day questions related to client incidents, requests and queries.
-**You will be successful in this role if you have:**
- High School Diploma or GED required May require technical certification or Associate Degree Generally, 1\-2years’ experience in area of responsibility
- Unisys is proud to be an equal opportunity employer that considers all qualified applicants without regard to age, caste, citizenship, color, disability, family medical history, family status, ethnicity, gender, gender expression, gender identity, genetic information, marital status, national origin, parental status, pregnancy, race, religion, sex, sexual orientation, transgender status, veteran status or any other category protected by law.
- This commitment includes our efforts to provide for all those who seek to express interest in employment the opportunity to participate without barriers. If you are a US job seeker unable to review the job opportunities herein, or cannot otherwise complete your expression of interest, without additional assistance and would like to discuss a request for reasonable accommodation, please contact our Global Recruiting organization at GlobalRecruiting@unisys.com or alternatively Toll Free: 888\-560\-1782 (Prompt 4\). US job seekers can find more information about Unisys’ EEO commitment here.</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>IT Services and IT Consulting</t>
-        </is>
-      </c>
+          <t>Effective: March 2026
+Location: Service Operation Centre in Cebu
+### **Position Summary**
+The Senior HR Officer is responsible for Talent Acquisition, Development, and Organizational Effectiveness at TecSurge. This role supports the development of a high\-performing, engaged, and future\-ready workforce aligned with business objectives.
+The role leads strategic HR initiatives across talent acquisition, learning \&amp; development, employee engagement, and organizational development, while acting as a senior escalation point for complex HR matters. The Senior HR Officer also mentors HR team members and drives continuous improvement in people practices.
+### **Your Responsibilities**
+Depending upon your level of expertise and experience, your responsibilities may include:
+* Talent Acquisition \&amp; Onboarding
+* + Lead end\-to\-end recruitment strategy and execution, including workforce planning and employer branding.
+* Learning \&amp; Development
+* + Design and implement learning and development initiatives aligned with business requirements and future capability needs.
+* Performance Management \&amp; Employee Relations
+* + Drive performance management cycles, employee engagement surveys, and culture\-building initiatives.
+	+ Act as the escalation point for employee grievances, welfare matters, and disciplinary cases.
+	+ Champion initiatives that enhance employee experience, engagement, and retention.
+* Organizational Development
+* + Partner with leaders to assess organizational capabilities and design interventions to improve performance and culture.
+	+ Facilitate strategic workforce planning and succession planning activities.
+	+ Analyse engagement, performance, and turnover data to inform Organizational Development strategies.
+* Leadership \&amp; Mentorship
+* + Mentor HR Officers and interns to build HR capability and support professional development.
+	+ Advise managers on employee relations, performance management, and team development matters.
+* Cross\-Functional Responsibilities
+* + Provide backup support in payroll, training administration, or recruitment when required.
+	+ Collaborate with the HR Officer – People Operations on compliance, reporting, and HR systems.
+### **Your Competencies**
+* Degree in Human Resources, Business Administration, or a related discipline.
+* Minimum 6–8 years of progressive HR experience, with exposure to talent acquisition, learning \&amp; development, employee engagement, and organizational development.
+* Demonstrated experience handling complex employee relations and performance management matters.
+* Strong understanding of workforce planning, succession planning, and Organizational Development frameworks.
+* Ability to analyse HR data and translate insights into practical, business\-focused solutions.
+* Strong stakeholder management and communication skills, with the ability to influence at all levels of the organization.
+* Proven experience mentoring or guiding junior HR team members.
+* Knowledge of Singapore employment legislation and HR best practices is preferred.
+### **TecSurge Careers**
+TecSurge employees are obsessed with customer responsiveness, quality, and efficiency. We strive to do the job right the first time, so it never has to be done again. We always think through issues deeply and consider all implications before acting. Our employees are either already acknowledged experts in their field or have that on their career path.
+### **Our Way of Working**
+We are committed to providing an unrivalled customer experience and to be the most responsive, trusted, time efficient and cost\-effective business partner to our clients.
+### **Our Values**
+Reliable – we say what we do and do what we say.
+Responsive – we communicate in a transparent and timely way.
+Flexible – we provide solutions tailored to meet client requirements.
+Straightforward – we are easy to do business with.
+### **Who we are**
+TecSurge is an independent expert team providing a unique 24x7 worldwide service to efficiently apply, manage and support complex software applications for Engineering Procurement Construction and Owner / Operator companies.
+*“TecSurge is passionate about making the use of complex engineering software easy.”*
+Mr. Anton Schreibmueller, President and CEO of TecSurge
+### **What we offer**
+At TecSurge, we believe that flat hierarchies, unconventional dynamics in dealing with issues, and entrepreneurial thinking create the best prerequisites for joint success. Success is achieved by providing excellent services. We offer our staff exposure to a diverse range of clients, projects and technology, as part of a friendly and tech\-savvy team determined to exceed our customer’s expectations.
+**Benefits of working with TecSurge**: the possibility of personal development; an experience\-based salary; independent work organization; dynamic company; pleasant working environment.
+By applying, you consent that TecSurge will process your personal data for recruitment and employment purposes in accordance with our Privacy Policy.
+Visit tecsurge.com to find out more about us and what we do. Send your latest CV together with the following info to careers@tecsurge.com
+* Current Salary
+* Expected Salary
+* Notice Period
+* Reason for Leaving</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/unisys</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>https://media.licdn.com/dms/image/v2/C4E0BAQGP5PO--smhpQ/company-logo_100_100/company-logo_100_100/0/1669644012632/unisys_logo?e=2147483647&amp;v=beta&amp;t=umb8iP0FSyszRAXDeGsJpUGK6O-4wNFoU_SMGnzdc28</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
+          <t>https://ph.indeed.com/cmp/Tecsurge</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>https://tecsurge.com/</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11 to 50</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
@@ -1106,7 +1097,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>li-4359224143</t>
+          <t>li-4365672655</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1116,27 +1107,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4359224143</t>
+          <t>https://www.linkedin.com/jobs/view/4365672655</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Multi Skilled Technician</t>
+          <t>Tech Svc Desk</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ABSI</t>
+          <t>Unisys</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Quezon City, National Capital Region, Philippines</t>
+          <t>Manila, National Capital Region, Philippines</t>
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>46038</v>
+        <v>46046</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -1153,45 +1144,51 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>not applicable</t>
+          <t>entry level</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Engineering and Information Technology</t>
         </is>
       </c>
       <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>GlobalRecruiting@unisys.com</t>
+        </is>
+      </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>**Description**
-* Perform routine maintenance and repairs on various equipment and systems.
-* Diagnose technical issues and implement effective solutions.
-* Collaborate with team members to improve overall operational efficiency.
-* Maintain records of repairs and maintenance activities.
-* Ensure compliance with safety regulations and organizational standards.
-**Requirements**
-* Educational Qualifications: Diploma in a relevant technical field
-* Experience Level: 02 years
-* Skills and Competencies: Basic understanding of mechanical and electrical systems
-* Responsibilities and Duties: Ability to work independently and as part of a team
-* Qualities and Traits: Strong problem\-solving skills and attention to detail</t>
+          <t>**What Success Looks Like In This Role**
+* Responsible for providing the first line of post\-sales telephone technical support of hardware, systems, sub\-systems and/or applications for customers and/or employees.
+* Typically provides technical support for external customers.
+* Applies basic diagnostic techniques to identify problems, investigate causes and recommend solutions to correct common failures.
+* Discover and document process and procedures, which need to be published to the team or on the Knowledgebase.
+* Escalates complex problems to a higher level of expertise within organization.
+**You will be successful in this role if you have:**
+* Education, training and/or relevant experience equivalent to the completion of a relevant certificate course and/or relevant experience in Information Technology service delivery
+* Competence in MS Office and other standard software
+* Understanding of Active Directory to unlock and reset passwords
+* Analytical and diagnostic skills
+* Good Communication Skills
+ Unisys is proud to be an equal opportunity employer that considers all qualified applicants without regard to age, caste, citizenship, color, disability, family medical history, family status, ethnicity, gender, gender expression, gender identity, genetic information, marital status, national origin, parental status, pregnancy, race, religion, sex, sexual orientation, transgender status, veteran status or any other category protected by law.
+ This commitment includes our efforts to provide for all those who seek to express interest in employment the opportunity to participate without barriers. If you are a US job seeker unable to review the job opportunities herein, or cannot otherwise complete your expression of interest, without additional assistance and would like to discuss a request for reasonable accommodation, please contact our Global Recruiting organization at GlobalRecruiting@unisys.com or alternatively Toll Free: 888\-560\-1782 (Prompt 4\). US job seekers can find more information about Unisys’ EEO commitment here.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Human Resources Services</t>
+          <t>IT Services and IT Consulting</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>https://ph.linkedin.com/company/weareabsi</t>
+          <t>https://www.linkedin.com/company/unisys</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>https://media.licdn.com/dms/image/v2/C560BAQHenX_TiUNjJQ/company-logo_100_100/company-logo_100_100/0/1630640825212/absiph_logo?e=2147483647&amp;v=beta&amp;t=UmQDn0ASCSWFG4SyoBzhOf7zR5bNoRpUj5HV3qPk18g</t>
+          <t>https://media.licdn.com/dms/image/v2/C4E0BAQGP5PO--smhpQ/company-logo_100_100/company-logo_100_100/0/1669644012632/unisys_logo?e=2147483647&amp;v=beta&amp;t=umb8iP0FSyszRAXDeGsJpUGK6O-4wNFoU_SMGnzdc28</t>
         </is>
       </c>
       <c r="X6" t="inlineStr"/>
@@ -1209,7 +1206,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>li-4363544025</t>
+          <t>li-4362085094</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1219,31 +1216,31 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4363544025</t>
+          <t>https://www.linkedin.com/jobs/view/4362085094</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sr Tech Svc Desk</t>
+          <t>Part Time Technician (Preferably based in Quezon City)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Unisys</t>
+          <t>PRISM+</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Manila, National Capital Region, Philippines</t>
+          <t>Quezon City, National Capital Region, Philippines</t>
         </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>46038</v>
+        <v>46046</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>fulltime</t>
+          <t>parttime</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -1256,72 +1253,53 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>mid-senior level</t>
+          <t>associate</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>GlobalRecruiting@unisys.com</t>
-        </is>
-      </c>
+      <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr">
         <is>
-          <t>****What Success Looks Like In This Role:****
- Key Responsibilities
-****What Success Looks Like In This Role:****
-* Perform consistent monitoring on Service Desk agent interactions with End Users as well as the related tickets. Ensure that all designated agents in the team are coached timely and effectively.
-* Coaching abilities to drive agent performances
-* Provide input for Knowledge Article updates and recommend other improvement suggestions.
-* Prepare reports and quality indicators, provide Quality results to Service Desk Leadership members, and implement continuous improvement action plans for enhancing End User Experience.
-* Collaborate with Knowledge, training, Quality and Operation to drive results
-* Prepare and Drive Quality assurance Weekly, Monthly business presentation \[WBR, MBR]
-* Active participation in quality initiatives and Team objectives and high\-quality execution of the Quality Process.
-* Conduct sessions with Service Desk agents and staff members to calibrate on call guidelines and discuss on Quality Metrics.
-* May involve Client interaction and activities
-* SD basic technical troubleshooting experience
-* Demonstrated awareness of industry best practices in Quality Assurance and proficiency in leveraging market\-relevant technologies to ensure high standards of product quality.
-**You will be successful in this role if you have:**
-**Key Qualifications**
-**You will be successful in this role if you have** 
-**:**
-* Minimum 2\+ years of IT Service Desk Level 1 experience
-* Excellent verbal and written communication in English and any additional applicable languages
-* Bachelors’ Degree in any field is desired.
-* Key Skills:
-+ Good understanding of IT Service Desk Level 1 Support processes
-+ MIS reporting, trending reporting and Analytics
-+ Good knowledge of Service Desk Tools, Applications
-+ Experience creating and updating reports. Should be able to interpret data and trend analysis.
-+ Able to resolve escalations and keep stakeholders informed
-+ Highly resourceful, self\-driven, and proactive attitude that demonstrate ownership
-+ Growth Mindset that generates curiousness about the working environment
-+ Knowledge of PowerBi Reporting, MIS Excel
-+ Hands on experience on Ticketing tool like – ServiceNow and Genesys
-+ Knowledge of Speech and Text Analytics, Auto Assist, Sentiment Analysis is an added advantage
-+ Should be able to work with Global Team and related Operations Functions
- Unisys is proud to be an equal opportunity employer that considers all qualified applicants without regard to age, caste, citizenship, color, disability, family medical history, family status, ethnicity, gender, gender expression, gender identity, genetic information, marital status, national origin, parental status, pregnancy, race, religion, sex, sexual orientation, transgender status, veteran status or any other category protected by law.
- This commitment includes our efforts to provide for all those who seek to express interest in employment the opportunity to participate without barriers. If you are a US job seeker unable to review the job opportunities herein, or cannot otherwise complete your expression of interest, without additional assistance and would like to discuss a request for reasonable accommodation, please contact our Global Recruiting organization at GlobalRecruiting@unisys.com or alternatively Toll Free: 888\-560\-1782 (Prompt 4\). US job seekers can find more information about Unisys’ EEO commitment here.</t>
+          <t>Part Time Technician
+ Job Description
+ Responsible for Diagnosing, Assessing and Troubleshooting/Fixing Computer Monitors.
+ Key Requirements \&amp; Skills
+ 1\.Technical Proficiency
+ a.Hardware Diagnostics and Troubleshooting{{:}} Identifying and Fixing Issues with
+ Computer Monitors
+ b.Component Replacement{{:}} Replacing Defective Parts like power supplies,
+ backlights or boards
+ c.Assembly/Disassembly{{:}} Knowledge of taking apart and putting together Computer
+ Hardware
+**Requirements**
+**2\. Education** 
+ a. Formal{{:}} A minimum of a High School Diploma, with a preference for a Vocational/Bachelor's degree in any IT\-related field.
+ b. Certifications{{:}} Relevant certifications associated with IT/Job Description.
+**3\. Experience** 
+ a. Practical experience with hardware maintenance and repair.
+**4\. Soft Skills** 
+ a. Strong problem\-solving and critical thinking abilities.
+ b. Capacity to follow repair manuals and st</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>IT Services and IT Consulting</t>
+          <t>Technology, Information and Internet</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/unisys</t>
+          <t>https://sg.linkedin.com/company/prismplus</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>https://media.licdn.com/dms/image/v2/C4E0BAQGP5PO--smhpQ/company-logo_100_100/company-logo_100_100/0/1669644012632/unisys_logo?e=2147483647&amp;v=beta&amp;t=umb8iP0FSyszRAXDeGsJpUGK6O-4wNFoU_SMGnzdc28</t>
+          <t>https://media.licdn.com/dms/image/v2/D560BAQGaj09omkunVg/company-logo_100_100/company-logo_100_100/0/1681886341660/prismplus_logo?e=2147483647&amp;v=beta&amp;t=wdJzZD-DpGrW0eYt-aMf8kbGkaOPIph_Ts87Heim7xE</t>
         </is>
       </c>
       <c r="X7" t="inlineStr"/>
@@ -1339,7 +1317,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>li-4329268482</t>
+          <t>li-4363449926</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1349,10 +1327,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4329268482</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>https://www.linkedin.com/jobs/view/4363449926</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://bossjob.com/job/pump-man-quezon-city-232638&amp;urlHash=OE9W</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>Pump Technician</t>
@@ -1360,7 +1342,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MicroSourcing</t>
+          <t>Trade One Incorporated</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1369,7 +1351,7 @@
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>46038</v>
+        <v>46046</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1386,80 +1368,71 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>mid-senior level</t>
+          <t>associate</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Engineering and Information Technology</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr">
         <is>
-          <t>**Discover your 100% YOU with MicroSourcing!**
-**Position:** 
- Fuel Systems Maintenance Engineer (Senior)
-**Location:** 
- 1880 Building, Eastwood, Quezon City
-**Work setup \&amp; shift:** 
- Onsite \| Dayshift
-**Why join MicroSourcing?**
-**You'll Have**
-* Competitive Rewards\*: Enjoy above\-market compensation, healthcare coverage on day one for you and your dependents, paid time\-off with cash conversion, group life insurance, and performance bonuses.
-* A Collaborative Spirit: Contribute to a positive and engaging work environment by participating in company\-sponsored events and activities.
-* Work\-Life Harmony: Maintain a balance between work and life with flexible work arrangements.
-* Career Growth: Access opportunities for continuous learning and career advancement.
-* Inclusive Teamwork: Be part of a team that celebrates diversity and fosters an inclusive culture.
-**Your Role:**
-**As a Fuel Systems Maintenance Engineer, You Will**
-* Manage the national service provider responsible for fuel system and hose maintenance contracts, ensuring compliance with contractual obligations and performance KPIs.
-* Oversee pump maintenance activities (fuel or oil), ensuring optimal performance, reliability, and safety.
-* Background in working with oil or petroleum companies/stations such as Shell, Seaoil, particularly with underground tanking systems.
-* Leverage CMMS platforms (e.g., Maximo, Simpro) to track work orders, maintenance schedules, and asset histories.
-* Review service provider performance through data analysis, audits, and stakeholder feedback to drive accountability and continuous improvement.
-* Coordinate urgent and preventive maintenance works, allocating resources based on service level agreements.
-* Develop and implement process optimization initiatives to enhance productivity, reduce downtime, and lower maintenance costs.
-* Ensure compliance with OH\&amp;S regulations and industry best practices for retail, petroleum, and convenience environments.
-* Manage subcontractors for repairs, upgrades, and projects, prioritizing quality and timeliness.
-* Maintain accurate maintenance records, update CMMS systems, and ensure timely processing of work orders.
-* Foster strong working relationships with internal departments, service providers, and contractors to align objectives and streamline execution.
-**What You Need:**
-**Non\-negotiables**
-* Degree in Engineering or Mechanical Engineering, or at least 5 years’ experience in managing repairs and maintenance works.
-* Proven hands\-on experience in pump maintenance (fuel or water) within a commercial, industrial, or retail environment.
-* Proficiency with Maintenance Management Systems or CMMS tools such as Maximo, Simpro, or similar platforms.
-* Strong communication, problem\-solving, and critical thinking skills.
-* Familiarity with OH\&amp;S legislative requirements in retail, petrol, or convenience industries.
-* Ability to read and interpret building plans.
-* Demonstrated track record in improving maintenance processes, performance, and cost efficiency.
-**Preferred skills/expertise**
-* Prior experience in the petroleum industry.
-* Ability to manage multiple maintenance projects simultaneously.
-* Solution\-oriented mindset with a focus on innovative, cost\-effective maintenance solutions.
-**About MicroSourcing**
- With over 9,000 professionals across 13 delivery centers, MicroSourcing is the pioneer and largest offshore provider of managed services in the Philippines.
-**Our commitment to 100% YOU**
- MicroSourcing firmly believes that our company's strength lies in our people's diversity and talent. We are proud to foster an inclusive culture that embraces individuals of all races, genders, ethnicities, abilities, and backgrounds. We provide space for everyone, embracing different perspectives, and making room for opportunities for each individual to thrive.
- At MicroSourcing, equality is not merely a slogan – it's our commitment. Our way of life. Here, we don't just accept your unique authentic self – we celebrate it, valuing every individual's contribution to our collective success and growth. Join us in celebrating YOU and your 100%!
- For more information, visit https://www.microsourcing.com/
-* Terms \&amp; conditions apply</t>
+          <t>A Pump Technician is responsible for the installation, maintenance, repair, and troubleshooting of various types of pumps used in industrial applications such as wastewater management, water treatment, and other engineering sectors. They ensure that pumps and related systems operate efficiently and reliably.
+****Key Responsibilities:****
+* Install, inspect, and maintain different types of pumps, including centrifugal, positive displacement, and submersible pumps.
+* Troubleshoot and repair malfunctioning pumps and systems, including identifying mechanical and electrical issues.
+* Perform routine maintenance such as lubricating, replacing seals, and checking for wear on pump parts.
+* Conduct tests on pumps to ensure proper operation and efficiency.
+* Perform alignment, calibration, and adjustment of pumps and related components.
+* Ensure compliance with safety regulations and industry standards during operations.
+* Maintain accurate records of repairs, maintenance schedules, and inventory of spare parts.
+* Provide technical support and guidance to other staff and operators.
+* Assist in the design and implementation of pump systems and solutions for specific projects.
+* Prepare client acceptance documents and service reports.
+****Education:****
+* Vocational/technical certification in Mechanical Engineering or related fields.
+* A degree in Mechanical Engineering is an advantage but not required.
+****Experience:****
+* At least 1\-2 years of experience in pump maintenance, repair, or installation in industrial settings.
+* Experience with submersible pumps or similar pump systems is highly preferred.
+****Skills:****
+* Strong knowledge of pump systems, mechanics, and troubleshooting techniques.
+* Familiarity with pump operation and maintenance procedures.
+* Ability to use tools and equipment to repair pumps, including testing devices, wrenches, and torque equipment.
+* Basic understanding of electrical systems and controls related to pump motors.
+* Knowledge on Fire Pump and Jockey Pump Operation.
+****Certifications:****
+* Relevant certifications (e.g., in electrical or mechanical systems) are a plus.
+* Safety and environmental certifications (e.g., OSHA or similar) would be advantageous.
+****Personal Traits:****
+* Attention to detail and commitment to safety.
+* Ability to work independently and as part of a team.
+* Willingness to work/travel at site
+ Job Type: Full\-time
+**Supplemental Pay:**
+* 13th month salary
+* Commission pay
+* Overtime pay
+**Experience:**
+* Pump Technician: 1 year (Preferred)</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>Outsourcing and Offshoring Consulting</t>
+          <t>Industrial Machinery Manufacturing and Engineering Services</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>https://ph.linkedin.com/company/microsourcing</t>
+          <t>https://ph.linkedin.com/company/tradeoneincorporated</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>https://media.licdn.com/dms/image/v2/D560BAQHXU-kxH2qMGQ/company-logo_100_100/B56ZtFAbwlJoAU-/0/1766389300808/microsourcing_logo?e=2147483647&amp;v=beta&amp;t=t-3jV02pO-tnqdyeHHbk0LDcJrn7CqEmBpbSU4sYur0</t>
+          <t>https://media.licdn.com/dms/image/v2/C560BAQEy1t75srxr8w/company-logo_100_100/company-logo_100_100/0/1650437290125/trade_one_incorporated_logo?e=2147483647&amp;v=beta&amp;t=tx1mzwKbrXkk4xJSF1amUiGC_FZy9K8GqrzeXzxLXWg</t>
         </is>
       </c>
       <c r="X8" t="inlineStr"/>
@@ -1477,7 +1450,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>li-4348356368</t>
+          <t>li-4363389869</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1487,27 +1460,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4348356368</t>
+          <t>https://www.linkedin.com/jobs/view/4363389869</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Technician 3, Engineering Services</t>
+          <t>Multi Skilled Technician</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Analog Devices</t>
+          <t>FPD ASIA PROPERTY SERVICES, INC.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cavite, Calabarzon, Philippines</t>
+          <t>Taguig, National Capital Region, Philippines</t>
         </is>
       </c>
       <c r="H9" s="2" t="n">
-        <v>46037</v>
+        <v>46046</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1524,49 +1497,47 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>mid-senior level</t>
+          <t>entry level</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Management and Manufacturing</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr">
         <is>
-          <t>**About Analog Devices**
- Analog Devices, Inc. (NASDAQ: ADI ) is a global semiconductor leader that bridges the physical and digital worlds to enable breakthroughs at the Intelligent Edge. ADI combines analog, digital, and software technologies into solutions that help drive advancements in digitized factories, mobility, and digital healthcare, combat climate change, and reliably connect humans and the world. With revenue of more than $9 billion in FY24 and approximately 24,000 people globally, ADI ensures today's innovators stay Ahead of What's Possible™. Learn more at www.analog.com and on LinkedIn and Twitter (X).
- Oversee vendor selection based on project complexity and urgency, conducts thorough cost and purchase request reviews, and ensures timely resolution of queries and on\-schedule delivery of all project requirements by actively monitoring each routed PR through completion.
-* Responsible for thoroughly reviewing assigned NHO projects by verifying complete documentation, assessing hardware complexity, and considering relevant historical orders to ensure optimal candidate selection and project readiness.
-* Responsible for selecting vendors for RFQs based on previous performance history, project complexity, and demonstrated vendor capability.
-* Cost review
-* Routing of Ereq : All necessary items pertaining to each project should be routed in ereq.
-* Placing of order to Vendor once PO is available and files are Final and ready for build.
-* Responsible for actively monitoring project progress, ensuring all requirements are met and no outstanding queries remain unresolved. This includes regular coordination and meetings with vendors, project owners, production planning, and other relevant groups to address issues and drive timely completion.
-* Ontime delivery of each order, cycle time are met.
-* Settle of invoice , No aging invoice for payment (Softco)
-*For positions requiring access to technical data, Analog Devices, Inc. may have to obtain export licensing approval from the U.S. Department of Commerce \- Bureau of Industry and Security and/or the U.S. Department of State \- Directorate of Defense Trade Controls. As such, applicants for this position – except US Citizens, US Permanent Residents, and protected individuals as defined by 8 U.S.C. 1324b(a)(3\) – may have to go through an export licensing review process.*
-*Analog Devices is an equal opportunity employer. We foster a culture where everyone has an opportunity to succeed regardless of their race, color, religion, age, ancestry, national origin, social or ethnic origin, sex, sexual orientation, gender, gender identity, gender expression, marital status, pregnancy, parental status, disability, medical condition, genetic information, military or veteran status, union membership, and political affiliation, or any other legally protected group.*
- Job Req Type: Experienced
- Required Travel: No
- Shift Type: Normal Time (Philippines)</t>
+          <t>**Regular**
+* Responsible for the proper maintenance and operation of the following building equipment and facilities:
+ i. Air\-conditioning System
+ ii. Water and Sewerage System
+ iii. Drainage system
+ iv. Fire Protection and Fire Alarm System
+ v. Electrical System
+* Handles unit owners/tenants complaints or assistance needed in electrical and mechanical systems.
+* Coordinates with the Building/Facilities Manager or Building/Facilities Engineer for instructions
+* All other related tasks as required
+* Candidate must possess at least a Vocational Diploma / Short Course Certificate, Others or equivalent.
+* At least 1 year(s) of working experience in the related field is required for this position.
+* Preferably 1\-4 Yrs Experienced Employees specializing in Maintenance/Repair (Facilities \&amp; Machinery) or equivalent.
+* Full\-Time position(s) available.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturing</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/analog-devices</t>
+          <t>https://ph.linkedin.com/company/fpd-asia-property-services-inc-</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>https://media.licdn.com/dms/image/v2/C4E0BAQFIPofjzp1AXA/company-logo_100_100/company-logo_100_100/0/1639584615887/analog_devices_logo?e=2147483647&amp;v=beta&amp;t=bZQxkGOzeJS9pxUXfTNodZxtiX1mfW0JP5NP_60ixZQ</t>
+          <t>https://media.licdn.com/dms/image/v2/C560BAQEnlmXvL32qhA/company-logo_100_100/company-logo_100_100/0/1631314925577?e=2147483647&amp;v=beta&amp;t=LZ73eUv4mwvhjlUx1q8OrBYJBxI2sGGeHwMfbo3kILo</t>
         </is>
       </c>
       <c r="X9" t="inlineStr"/>
@@ -1584,7 +1555,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>li-4362763720</t>
+          <t>li-4324728408</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1594,27 +1565,23 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4362763720</t>
+          <t>https://www.linkedin.com/jobs/view/4324728408</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Technician III-Facilities</t>
+          <t>Assistant Service Technician</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Microchip Technology Inc.</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Davao, Davao Region, Philippines</t>
-        </is>
-      </c>
+          <t>Johnson Controls</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" s="2" t="n">
-        <v>46037</v>
+        <v>46046</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1636,55 +1603,54 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Management and Manufacturing</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr">
         <is>
-          <t>Are you looking for a unique opportunity to be a part of something great? Want to join a 17,000\-member team that works on the technology that powers the world around us? Looking for an atmosphere of trust, empowerment, respect, diversity, and communication? How about an opportunity to own a piece of a multi\-billion dollar (with a B!) global organization? We offer all that and more at Microchip Technology Inc.
- People come to work at Microchip because we help design the technology that runs the world. They stay because our culture supports their growth and stability. They are challenged and driven by an incredible array of products and solutions with unlimited career potential. Microchip’s nationally\-recognized Leadership Passage Programs support career growth where we proudly enroll over a thousand people annually. We take pride in our commitment to employee development, values\-based decision making, and strong sense of community, driven by our Vision, Mission, and 11 Guiding Values; we affectionately refer to it as the
- *Aggregate System* 
- and it’s won us countless awards for diversity and workplace excellence.
- Our company is built by dedicated team players who love to challenge the status quo; we did not achieve record revenue and over 30 years of quarterly profitability without a great team dedicated to empowering innovation. People like you.
- Visit our careers page to see what exciting opportunities and company perks await!
-**Job Description**
- Applies electrical/mechanical theory and related knowledge to test and modify developmental or operational electrical/mechanical machinery and electrical control equipment and circuitry in industrial plants. This role is responsible for ensuring a 100% proper operation of plant facilities equipment and to troubleshoot any electrical/mechanical malfunctioning and complete appropriate repairs and maintenance.
-* Oversee Maintenance and Operation of Facility equipment, machinery, facilities systems.
-* Responsible for the ongoing physical maintenance and safety of the building facilities support systems and ensure all facility equipment are in good health.
-* Responds to customer/client requests, events, or incidents as they occur.
-* Operation \&amp; Maintenance day\-to\-day execution, Spares management, Equipment Status/ History record.
-* Ensure Safety standards are properly implemented during operation and maintenance of Facility equipment.
-* To execute all Maintenance Plan during maintenance shutdown and ensure that all sub\-contractor follow planned activities.
-* To raise the issue in\-case of any risk or potential ITP related to Microchip Facility equipment. To escalate Facility issues in\-case of any incident.
-* To maintain Operation and Maintenance Record based on ISO standards.
-* To provide Daily Operations and Maintenance report.
-**Requirements/Qualifications**
-* Associate degree or completion of Technical School in Electrical or Mechanical Courses.
-* Min. of 3 yrs relevant experience in Facilities Ops and Maintenance in Semiconductor Industry or Mechanical/ Electrical Functions in Industrial Plant
-**Travel Time**
- No Travel
-**To all recruitment agencies** 
- :
- *Microchip Technology Inc.
- **does not** 
- accept unsolicited agency resumes. Please do not forward resumes to our recruiting team or other Microchip employees. Microchip is not responsible for any fees related to unsolicited resumes.*</t>
+          <t>**What You Will Do**
+ Provides very basic support of installation, maintenance, and repair of building systems and equipment to clients or project sites.
+**How Will You Do It**
+* Chiller Operatorship:
+* Ensures on time opening and closing of chillers as per schedule.
+* Monitors chillers for water level and temperature.
+* Inspects, monitors and documents plant equipment and its function on an hourly or daily basis
+* Performs preventive maintenance of chillers in coordination with Project Engineer.
+* Diagnoses problems and coordinates Project Engineer
+* Completes all service reports and log sheets on a daily basis or as per schedule. Makes oral and written reports to be submitted to client on a daily basis. Maintains work area, equipment and chiller plant room in a neat and orderly condition
+* Reports all chiller concerns to the client and Project Engineer.
+* Will be assigned to provincial projects to operate newly installed chillers. Performs other duties that may be assigned from time to time in relation to the job summary
+* Chiller Technician:
+* Performs preventive maintenance, check\-up and repairs of chiller units
+* Makes the necessary repairs and gives recommendation for damaged or malfunctioning chiller units
+* Prepares daily service reports.
+* Performs other duties that may be assigned from time to time in relation to the job summary
+**What We Look For**
+* Must be a graduate of Refrigeration and Aircon Servicing Certification (DomRAC II)
+* Has at least 3\-5 year related work experience in chiller operatorship and troubleshooting
+* High preference to candidates who has experience on centralize chillers
+* Open for candidates with VRV/VRF and AHU experience
+**What We Offer**
+* On the job/cross training opportunities
+* Encouraging and collaborative team environment
+* Dedication to safety through our Zero Harm policy</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>Appliances, Electrical, and Electronics Manufacturing and Semiconductor Manufacturing</t>
+          <t>Industrial Machinery Manufacturing</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/microchip-technology</t>
+          <t>https://ie.linkedin.com/company/johnson-controls</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>https://media.licdn.com/dms/image/v2/C4D0BAQFajoqqZYfHYQ/company-logo_100_100/company-logo_100_100/0/1631310605581?e=2147483647&amp;v=beta&amp;t=ywIo_KMe1v7dPc7wPNTSXoWbzSdrPwNQmR5Hjg2Qocc</t>
+          <t>https://media.licdn.com/dms/image/v2/D560BAQFLnizgdgpDFA/company-logo_100_100/company-logo_100_100/0/1728672007366/johnson_controls_logo?e=2147483647&amp;v=beta&amp;t=2M4dlywu0qlZ8x6OXlndDbP0lKGE0lrUOcbNVuWvcMs</t>
         </is>
       </c>
       <c r="X10" t="inlineStr"/>
@@ -1702,7 +1668,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>li-4359182415</t>
+          <t>li-4365610460</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1712,31 +1678,31 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4359182415</t>
+          <t>https://www.linkedin.com/jobs/view/4365610460</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://jobs.iqvia.com/jobs/R1507261-0?source=LinkedIn_Slots&amp;amp;utm_source=linkedin.com&amp;amp;utm_medium=job_posting&amp;urlHash=lw1M</t>
+          <t>https://www.talentmate.com/jobs/philippines/cordon-cagayan-valley/skilled-train-maintainer-driver/2601-21584-4&amp;urlHash=2tgi</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sr Reference File Maintainer Assoc</t>
+          <t>Skilled Train Maintainer Driver</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>IQVIA</t>
+          <t>TALENTMATE</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Taguig, National Capital Region, Philippines</t>
+          <t>Cordon, Cagayan Valley, Philippines</t>
         </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>46037</v>
+        <v>46046</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1753,50 +1719,101 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>entry level</t>
+          <t>internship</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Management and Manufacturing</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>abuse@talentmate.com</t>
+        </is>
+      </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>**Job Responsibilities**
-* Complete maintenance of reference data (healthcare Organizations and Prescribers) as essential for ANZ Production.
-* Perform research such as Internet Search, Phone Verification, Database Matches and etc. to gather information from third parties that will validate the completeness or accuracy of the data.
-* Perform outbound phone verification of details on Organization and Prescriber records to validate accuracy of reference data maintained as well as capture client\-required details such as primary office address and primary profession/specialty.
-* Performs ad hoc data analysis and participates on various process improvement as needed.
-* Validate that the information gathered from third\-party sources represents accurate new data that should result in an update, creation, or deletion in the database existing data.
-**Job Requirement**
-* 2\-year experience in handling voice and healthcare account
-* College undergraduates with BPO experience are also welcome to apply.
-* Basic knowledge in Windows applications (Excel, Word).
-* Strong verbal and / or written communication skills in either the language of the country supplied or English.
-* Critical thinking and problem\-solving skills.
-* Demonstrate strong understanding of complex concepts and processes.
-* Has initiative and is self\-motivated to see through until resolution concerns raised by Clients.
-* Candidate must be willing to work in night shift
-* Amenable to onsite training in Mckinley, Taguig
- IQVIA is a leading global provider of clinical research services, commercial insights and healthcare intelligence to the life sciences and healthcare industries. We create intelligent connections to accelerate the development and commercialization of innovative medical treatments to help improve patient outcomes and population health worldwide. Learn more at https://jobs.iqvia.com</t>
+          <t>**Job Description**
+**Business function:** 
+ Engineering
+**Grade:** 
+ STM
+**Salary:** 
+ £52,031\.00 per annum, paid at 75% during the training period
+**Hours:** 
+ 35 per week
+**Role type:** 
+ On site
+ People come to Northern for trains they can rely on. Behind every safe, clean, on\-time service is a team of engineers making sure each unit is ready to roll.
+ As part of our Engineering team, you’d play a hands\-on role in keeping our fleet moving. This is a dual\-skilled position that brings together train maintenance and depot driving, giving you real variety and a clear sense of purpose every time you step onto the depot. Whether you’re fault\-finding, servicing, or moving units to keep the plan on track, your work directly supports millions of journeys across the North.
+ You don’t need previous train driving experience. We’ll train you from the ground up, combining classroom learning with practical, on\-site experience to help you build a long\-term career in rail engineering.
+**What You’ll Be Doing**
+* Carrying out maintenance, servicing, inspections and fault\-finding on our trains, making sure they’re safe and ready for service.
+* Preparing units for daily operation, including cleaning, checks and supporting planned maintenance activities.
+* Safely moving and positioning trains around the maintenance depot to support the engineering plan.
+* Working closely with colleagues across Engineering to maintain traction and rolling stock to the highest standards.
+* Following all safety rules, procedures and working instructions, while keeping a clean, secure and well\-organised working environment.
+* Working flexibly across shifts, including nights and weekends.
+**About You**
+ Engineering know\-how, focus and the right attitude – that’s what matters here.
+**You’ll Bring**
+* An NVQ Level 3 qualification in Engineering, with hands\-on experience of mechanical and electrical systems.
+* The ability to fault\-find and troubleshoot in a fast\-paced, technical environment.
+* A strong safety mindset, with the focus and concentration needed for a safety critical role.
+* Flexibility to adapt to changing maintenance and operational demands.
+* Clear communication skills and a calm, team\-first approach, even under pressure.
+* The motivation to lead by example and take pride in high\-quality work.
+* A commitment to completing our full train driver training programme and staying fully compliant.
+* No previous train driving experience is needed. You’ll begin with around six weeks of classroom\-based training in Leeds or Manchester, followed by practical training at your depot.
+**Please note:** 
+ This is a safety\-critical role and is subject to Rail Safety \&amp; Standards Board (RSSB) regulations. You must meet the following criteria or your application will be automatically rejected:
+* You live within a 45\-minute car journey of the station you’ll work from.
+* You’re at least 18 years old at the time of application.
+* You can pass a safety\-critical medical, including drugs and alcohol screening.
+* You do not have defective colour vision.
+**What’s in it for you?**
+ At Northern, We Don’t Just Value Our People \- We Go The Extra Mile To Support Them. Here’s a Taste Of What You Can Look Forward To
+* Free Travel: Unlimited free travel for you, your partner, and your dependents on Northern services. Plus up to 75% discount on other networks in the UK and Europe.
+* Generous Pension Scheme: We top up your contributions by 1\.5 times.
+* Enhanced Family Benefits: We offer 9 months of full pay for maternity leave and 2 weeks for paternity leave.
+* Cycle to Work Scheme: Save up to 42% on a bike and spread the cost.
+* Exclusive Discounts: From shopping to wellbeing, Northern Perks has you covered.
+* Employee Assistance Programme: 24/7 support for family, lifestyle, and more.
+* Training and Career Development: We offer tailored training to our colleagues and opportunities to gain recognised qualifications. Plus enhanced career pathways no matter what part of the business you’re in.
+* Recognition: We know how important it is to show how much we appreciate our people. That’s why we have our Northern Lights and Northern Sparks Awards, recognising and celebrating brilliance every day.
+**Why Northern?**
+ We’re more than just a train operator. We’re the heartbeat of the North – connecting communities, creating opportunities, and driving sustainable growth. With 2,500 trains running daily, we’re on a mission to improve rail travel and enhance the customer experience while protecting the environment.
+ Back in 1825, the first passenger train set off in the North of England, after which rail quickly spread across the globe – and this year, we’re celebrating 200 years of the modern railway. As we look back on the historic events that led us here, we also look towards the future as we move into the era of Great British Rail. Join us at this pivotal moment in rail history and play your part in our journey.
+**A place for everyone**
+ The best journeys happen when everyone feels welcome on board.
+ At Northern, we don’t just move people from A to B – we’re building a team where everyone feels they belong. Our talent team can make reasonable adjustments to the process if that’s something you need. Were also a Level 2 Disability Confident employer, so if you meet the minimum criteria for the role, we’ll always offer an interview.
+ We automate parts of our screening process to remove any unconscious bias and to make sure every application is treated fairly. All successful offers will be subject to a DBS check and a medical assessment.
+ No matter your background, experience, or whether you call it a bap, barm, or cob… there’s a place for you here in the railway.
+ Job Details
+ Role Level: Internship Work Type: Full\-Time Country: Philippines City: Cordon Cagayan Valley Company Website: http://www.northernrailway.co.uk Job Function: Engineering Company Industry/
+ Sector: Rail Transportation
+ What We Offer
+**About The Company**
+ Searching, interviewing and hiring are all part of the professional life. The TALENTMATE Portal idea is to fill and help professionals doing one of them by bringing together the requisites under One Roof. Whether you're hunting for your Next Job Opportunity or Looking for Potential Employers, we're here to lend you a Helping Hand.
+ Report
+ Disclaimer: talentmate.com is only a platform to bring jobseekers \&amp; employers together. Applicants are advised to research the bonafides of the prospective employer independently. We do NOT endorse any requests for money payments and strictly advice against sharing personal or bank related information. We also recommend you visit Security Advice for more information. If you suspect any fraud or malpractice, email us at abuse@talentmate.com.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>Hospitals and Health Care</t>
+          <t>IT Services and IT Consulting</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/iqvia</t>
+          <t>https://ae.linkedin.com/company/talentmateglobal</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>https://media.licdn.com/dms/image/v2/C560BAQFW8oSPns4-Cw/company-logo_100_100/company-logo_100_100/0/1678802429367/iqvia_logo?e=2147483647&amp;v=beta&amp;t=QOXo3llXq86V8X_W17HYn3FC5VtElAP1K_rAxCkyhIs</t>
+          <t>https://media.licdn.com/dms/image/v2/D4D0BAQG-8UDhIAH2KQ/company-logo_100_100/company-logo_100_100/0/1725607290186/talentmateglobal_logo?e=2147483647&amp;v=beta&amp;t=b4zIShiUy2aHby6bC64NYAf7jQFuB7uQJ4EgebH4PEA</t>
         </is>
       </c>
       <c r="X11" t="inlineStr"/>
@@ -1814,7 +1831,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>li-4363897559</t>
+          <t>li-4321406339</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1824,26 +1841,32 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4363897559</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>https://www.linkedin.com/jobs/view/4321406339</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://bossjob.com/job/truck-automotive-technician-quezon-city-431451&amp;urlHash=jQQd</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tech Svc Desk - L1</t>
+          <t>Senior Technician</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Unisys</t>
+          <t>Advance Marketing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Manila, National Capital Region, Philippines</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Quezon City, National Capital Region, Philippines</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>46046</v>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>fulltime</t>
@@ -1859,47 +1882,47 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>entry level</t>
+          <t>associate</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Engineering and Information Technology</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>GlobalRecruiting@unisys.com</t>
-        </is>
-      </c>
+      <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr">
         <is>
-          <t>**What Success Looks Like In This Role**
-* Answers moderately complex questions, following guidelines and using judgment based on experience with related incidents and service requests.
-* Requests handled include support of hardware, software, client and COTS applications as well as network and user administration.
-* Escalates complex problems to other resolver teams or vendors.
-* Utilizes problem solving and analytical skills to effectively resolve challenging incidents.
-* Supports L1 agents in ongoing day to day questions related to client incidents, requests and queries.
-**You will be successful in this role if you have:**
- High School Diploma or GED required May require technical certification or Associate Degree Generally, 1\-2years’ experience in area of responsibility
- Unisys is proud to be an equal opportunity employer that considers all qualified applicants without regard to age, caste, citizenship, color, disability, family medical history, family status, ethnicity, gender, gender expression, gender identity, genetic information, marital status, national origin, parental status, pregnancy, race, religion, sex, sexual orientation, transgender status, veteran status or any other category protected by law.
- This commitment includes our efforts to provide for all those who seek to express interest in employment the opportunity to participate without barriers. If you are a US job seeker unable to review the job opportunities herein, or cannot otherwise complete your expression of interest, without additional assistance and would like to discuss a request for reasonable accommodation, please contact our Global Recruiting organization at GlobalRecruiting@unisys.com or alternatively Toll Free: 888\-560\-1782 (Prompt 4\). US job seekers can find more information about Unisys’ EEO commitment here.</t>
+          <t>**Qualifications**
+* Bachelors degree in a related automotive course
+* At least 2 years of automotive experience
+* With NC II certification
+* Willing to render overtime when necessary
+* Advanced knowledge of automotive equipment, tools, and repair procedures
+* Strong attention to detail and commitment to safety standards
+**Responsibilities**
+* Perform diagnostics, repair, and maintenance on vehicles
+* Implement and maintain 5S standards in the shop
+* Install tires and provide proper product recommendations
+* Conduct wheel alignment and balancing
+* Ensure tools and equipment are properly used and maintained
+* Assist senior technicians as needed</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>IT Services and IT Consulting</t>
+          <t>Motor Vehicle Manufacturing</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/unisys</t>
+          <t>https://in.linkedin.com/company/advancemarketing-india</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>https://media.licdn.com/dms/image/v2/C4E0BAQGP5PO--smhpQ/company-logo_100_100/company-logo_100_100/0/1669644012632/unisys_logo?e=2147483647&amp;v=beta&amp;t=umb8iP0FSyszRAXDeGsJpUGK6O-4wNFoU_SMGnzdc28</t>
+          <t>https://media.licdn.com/dms/image/v2/D560BAQF8Apm4rdg10A/img-crop_100/B56ZmirzbnHkAM-/0/1759371016800?e=2147483647&amp;v=beta&amp;t=BFIqeXZz-o9jn3QOtS0IErEnaxn8zjbqnEiFPiX7cCg</t>
         </is>
       </c>
       <c r="X12" t="inlineStr"/>
@@ -1917,7 +1940,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>li-4364028786</t>
+          <t>li-4312526569</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1927,30 +1950,28 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4364028786</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>https://unisys.wd5.myworkdayjobs.com/External/job/Citynet\u002d\u002d-Mandaluyong-City/Tech-Svc-Desk\u002d\u002d-L1_REQ569844?source=LinkedIn&amp;urlHash=VzXq</t>
-        </is>
-      </c>
+          <t>https://www.linkedin.com/jobs/view/4312526569</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tech Svc Desk - L1</t>
+          <t>Technician I - Reliability</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Unisys</t>
+          <t>Microchip Technology Inc.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Manila, National Capital Region, Philippines</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Davao, Davao Region, Philippines</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>46046</v>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>fulltime</t>
@@ -1971,42 +1992,58 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Engineering and Information Technology</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>GlobalRecruiting@unisys.com</t>
-        </is>
-      </c>
+      <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr">
         <is>
-          <t>**What Success Looks Like In This Role**
-* Answers moderately complex questions, following guidelines and using judgment based on experience with related incidents and service requests.
-* Requests handled include support of hardware, software, client and COTS applications as well as network and user administration.
-* Escalates complex problems to other resolver teams or vendors.
-* Utilizes problem solving and analytical skills to effectively resolve challenging incidents.
-* Supports L1 agents in ongoing day to day questions related to client incidents, requests and queries.
-**You will be successful in this role if you have:**
- High School Diploma or GED required May require technical certification or Associate Degree Generally, 1\-2years’ experience in area of responsibility
- Unisys is proud to be an equal opportunity employer that considers all qualified applicants without regard to age, caste, citizenship, color, disability, family medical history, family status, ethnicity, gender, gender expression, gender identity, genetic information, marital status, national origin, parental status, pregnancy, race, religion, sex, sexual orientation, transgender status, veteran status or any other category protected by law.
- This commitment includes our efforts to provide for all those who seek to express interest in employment the opportunity to participate without barriers. If you are a US job seeker unable to review the job opportunities herein, or cannot otherwise complete your expression of interest, without additional assistance and would like to discuss a request for reasonable accommodation, please contact our Global Recruiting organization at GlobalRecruiting@unisys.com or alternatively Toll Free: 888\-560\-1782 (Prompt 4\). US job seekers can find more information about Unisys’ EEO commitment here.</t>
+          <t>Are you looking for a unique opportunity to be a part of something great? Want to join a 17,000\-member team that works on the technology that powers the world around us? Looking for an atmosphere of trust, empowerment, respect, diversity, and communication? How about an opportunity to own a piece of a multi\-billion dollar (with a B!) global organization? We offer all that and more at Microchip Technology Inc.
+ People come to work at Microchip because we help design the technology that runs the world. They stay because our culture supports their growth and stability. They are challenged and driven by an incredible array of products and solutions with unlimited career potential. Microchip’s nationally\-recognized Leadership Passage Programs support career growth where we proudly enroll over a thousand people annually. We take pride in our commitment to employee development, values\-based decision making, and strong sense of community, driven by our Vision, Mission, and 11 Guiding Values; we affectionately refer to it as the
+ *Aggregate System* 
+ and it’s won us countless awards for diversity and workplace excellence.
+ Our company is built by dedicated team players who love to challenge the status quo; we did not achieve record revenue and over 30 years of quarterly profitability without a great team dedicated to empowering innovation. People like you.
+ Visit our careers page to see what exciting opportunities and company perks await!
+**Job Description**
+ ESD Technician: The primary responsibility is to drive continues ESD Operations and maintain uninterrupted equipment’s in Rel\-ESD Laboratory. Minimize downtimes and equipment overdue’s as possible. Provide technical assistance and engineering support within established guidelines with the objective to determine and improve product/process quality and reliability. Ensure Continues drive in ensuring that published reports and papers are of appropriate quality and content. They partners with operations, business units and other key stakeholders to understand and implement qualification, evaluation and monitoring plans and strategies.
+ ESD Lab Management and Executions of ESD activities and procedures for NPI/Non\-NPI Qualifications, Evaluations, and Customer Risk Assessment in accordance with the qualification plans, international standards, and internal specifications, to improve component/process quality and reliability.
+**Requirements/Qualifications**
+ Degree holder of Engineering, or Technical graduate equivalent courses.
+* Basic knowledge and Application of Reliability Testing and Operations
+* Knowledge on International Quality Standards (ex. JEDEC, AEC, J\-IPC/JEDEC)
+* Has a minimum of (1\) year relevant experience in a semiconductor manufacturing environment with work experience from Quality and Reliability Laboratory Operations
+* 7 basic quality tools, Fail Mode and Effects Analysis (FMEA), Control Plan, 5\-Why, Fault Tree, and 8\-Discipline Problem Solving.
+* Basic understanding of semiconductor Assembly and Test processes.
+* Self\-motivated and goal\-oriented
+* Basic knowledge in Operation of Reliability/FA Processes and Equipment
+* Team player \&amp; can communicate effectively with others
+* Must have good interpersonal skills
+* Preferably with work background in a semiconductor company.
+* Skills in using Reliability tools and accessories (ex. DMM, Oscilloscope, Signal generator, curve tracer).
+* Experienced to analyze and interpret electronics circuits, schematic diagrams and lay\-outs.
+**Travel Time**
+ 0% \- 25%
+**To all recruitment agencies** 
+ :
+ *Microchip Technology Inc.
+ **does not** 
+ accept unsolicited agency resumes. Please do not forward resumes to our recruiting team or other Microchip employees. Microchip is not responsible for any fees related to unsolicited resumes.*</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>IT Services and IT Consulting</t>
+          <t>Appliances, Electrical, and Electronics Manufacturing and Semiconductor Manufacturing</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/unisys</t>
+          <t>https://www.linkedin.com/company/microchip-technology</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>https://media.licdn.com/dms/image/v2/C4E0BAQGP5PO--smhpQ/company-logo_100_100/company-logo_100_100/0/1669644012632/unisys_logo?e=2147483647&amp;v=beta&amp;t=umb8iP0FSyszRAXDeGsJpUGK6O-4wNFoU_SMGnzdc28</t>
+          <t>https://media.licdn.com/dms/image/v2/C4D0BAQFajoqqZYfHYQ/company-logo_100_100/company-logo_100_100/0/1631310605581?e=2147483647&amp;v=beta&amp;t=ywIo_KMe1v7dPc7wPNTSXoWbzSdrPwNQmR5Hjg2Qocc</t>
         </is>
       </c>
       <c r="X13" t="inlineStr"/>
@@ -2024,7 +2061,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>li-4363789095</t>
+          <t>li-4312539214</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2034,26 +2071,28 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4363789095</t>
+          <t>https://www.linkedin.com/jobs/view/4312539214</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tech Svc Desk - L1</t>
+          <t>Technician I - Failure Analysis</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Unisys</t>
+          <t>Microchip Technology Inc.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Manila, National Capital Region, Philippines</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Davao, Davao Region, Philippines</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>46046</v>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>fulltime</t>
@@ -2078,38 +2117,61 @@
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>GlobalRecruiting@unisys.com</t>
-        </is>
-      </c>
+      <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr">
         <is>
-          <t>**What Success Looks Like In This Role**
-* Answers moderately complex questions, following guidelines and using judgment based on experience with related incidents and service requests.
-* Requests handled include support of hardware, software, client and COTS applications as well as network and user administration.
-* Escalates complex problems to other resolver teams or vendors.
-* Utilizes problem solving and analytical skills to effectively resolve challenging incidents.
-* Supports L1 agents in ongoing day to day questions related to client incidents, requests and queries.
-**You will be successful in this role if you have:**
- High School Diploma or GED required May require technical certification or Associate Degree Generally, 1\-2years’ experience in area of responsibility
- Unisys is proud to be an equal opportunity employer that considers all qualified applicants without regard to age, caste, citizenship, color, disability, family medical history, family status, ethnicity, gender, gender expression, gender identity, genetic information, marital status, national origin, parental status, pregnancy, race, religion, sex, sexual orientation, transgender status, veteran status or any other category protected by law.
- This commitment includes our efforts to provide for all those who seek to express interest in employment the opportunity to participate without barriers. If you are a US job seeker unable to review the job opportunities herein, or cannot otherwise complete your expression of interest, without additional assistance and would like to discuss a request for reasonable accommodation, please contact our Global Recruiting organization at GlobalRecruiting@unisys.com or alternatively Toll Free: 888\-560\-1782 (Prompt 4\). US job seekers can find more information about Unisys’ EEO commitment here.</t>
+          <t>Are you looking for a unique opportunity to be a part of something great? Want to join a 17,000\-member team that works on the technology that powers the world around us? Looking for an atmosphere of trust, empowerment, respect, diversity, and communication? How about an opportunity to own a piece of a multi\-billion dollar (with a B!) global organization? We offer all that and more at Microchip Technology Inc.
+ People come to work at Microchip because we help design the technology that runs the world. They stay because our culture supports their growth and stability. They are challenged and driven by an incredible array of products and solutions with unlimited career potential. Microchip’s nationally\-recognized Leadership Passage Programs support career growth where we proudly enroll over a thousand people annually. We take pride in our commitment to employee development, values\-based decision making, and strong sense of community, driven by our Vision, Mission, and 11 Guiding Values; we affectionately refer to it as the
+ *Aggregate System* 
+ and it’s won us countless awards for diversity and workplace excellence.
+ Our company is built by dedicated team players who love to challenge the status quo; we did not achieve record revenue and over 30 years of quarterly profitability without a great team dedicated to empowering innovation. People like you.
+ Visit our careers page to see what exciting opportunities and company perks await!
+**Job Description**
+ A failure analysis technician is responsible in providing failure analysis to support customer returns, qualifications, and other engineering evaluations. Collaboration with FA requestors and other cross\-functional teams is also required. He/she must observe proper housekeeping, environmental, health, and safety protocols while doing his/her tasks.
+**Requirements/Qualifications**
+**Education Level**
+ At least a graduate of technical/vocational course
+**Working Experience**
+ Not required
+* Basic understanding of failure analysis flow.
+* Basic knowledge and skill in performing non\-destructive and destructive FA techniques.
+* Basic knowledge and skill in operating failure analysis tools and equipment.
+* Basic knowledge of basic semiconductor Fab, Assembly and Test process flow.
+* Basic knowledge of chemical handling safety training.
+* Basic knowledge in electrical testing and datalog interpretation.
+* Basic skill in physical failure techniques.
+**Other Requirements**
+* No known allergy to chemicals.
+* Good vision and dexterity.
+* Computer literate (MS Word, PowerPoint, and Excel).
+* Able to extract, analyze, and report data as necessary.
+* Good written and oral communication skills.
+* Good analytical skills, self\-motivated, team player, and able to proactively communicate with others.
+* Can collaborate with cross\-functional and cross\-cultural teams
+* Ability to manage time and priorities effectively.
+* Can understand and follow more complex procedures and instructions.
+**Travel Time**
+ 0% \- 25%
+**To all recruitment agencies** 
+ :
+ *Microchip Technology Inc.
+ **does not** 
+ accept unsolicited agency resumes. Please do not forward resumes to our recruiting team or other Microchip employees. Microchip is not responsible for any fees related to unsolicited resumes.*</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>IT Services and IT Consulting</t>
+          <t>Appliances, Electrical, and Electronics Manufacturing and Semiconductor Manufacturing</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/unisys</t>
+          <t>https://www.linkedin.com/company/microchip-technology</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>https://media.licdn.com/dms/image/v2/C4E0BAQGP5PO--smhpQ/company-logo_100_100/company-logo_100_100/0/1669644012632/unisys_logo?e=2147483647&amp;v=beta&amp;t=umb8iP0FSyszRAXDeGsJpUGK6O-4wNFoU_SMGnzdc28</t>
+          <t>https://media.licdn.com/dms/image/v2/C4D0BAQFajoqqZYfHYQ/company-logo_100_100/company-logo_100_100/0/1631310605581?e=2147483647&amp;v=beta&amp;t=ywIo_KMe1v7dPc7wPNTSXoWbzSdrPwNQmR5Hjg2Qocc</t>
         </is>
       </c>
       <c r="X14" t="inlineStr"/>
@@ -2127,7 +2189,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>li-4363768833</t>
+          <t>li-4318991467</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2137,26 +2199,28 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4363768833</t>
+          <t>https://www.linkedin.com/jobs/view/4318991467</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tech Svc Desk - L1</t>
+          <t>Technology &amp; Innovation Internship</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Unisys</t>
+          <t>Globe Telecom</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Manila, National Capital Region, Philippines</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Taguig, National Capital Region, Philippines</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>46045</v>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>fulltime</t>
@@ -2172,47 +2236,61 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>entry level</t>
+          <t>internship</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Engineering and Information Technology</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>GlobalRecruiting@unisys.com</t>
-        </is>
-      </c>
+      <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr">
         <is>
-          <t>**What Success Looks Like In This Role**
-* Answers moderately complex questions, following guidelines and using judgment based on experience with related incidents and service requests.
-* Requests handled include support of hardware, software, client and COTS applications as well as network and user administration.
-* Escalates complex problems to other resolver teams or vendors.
-* Utilizes problem solving and analytical skills to effectively resolve challenging incidents.
-* Supports L1 agents in ongoing day to day questions related to client incidents, requests and queries.
-**You will be successful in this role if you have:**
- High School Diploma or GED required May require technical certification or Associate Degree Generally, 1\-2years’ experience in area of responsibility
- Unisys is proud to be an equal opportunity employer that considers all qualified applicants without regard to age, caste, citizenship, color, disability, family medical history, family status, ethnicity, gender, gender expression, gender identity, genetic information, marital status, national origin, parental status, pregnancy, race, religion, sex, sexual orientation, transgender status, veteran status or any other category protected by law.
- This commitment includes our efforts to provide for all those who seek to express interest in employment the opportunity to participate without barriers. If you are a US job seeker unable to review the job opportunities herein, or cannot otherwise complete your expression of interest, without additional assistance and would like to discuss a request for reasonable accommodation, please contact our Global Recruiting organization at GlobalRecruiting@unisys.com or alternatively Toll Free: 888\-560\-1782 (Prompt 4\). US job seekers can find more information about Unisys’ EEO commitment here.</t>
+          <t>At Globe, our goal is to create a wonderful world for our people, business, and nation. By uniting people of passion who believe they can make a difference, we are confident that we can achieve this goal.
+**Job Description**
+ About us
+ Here at Globe, we treat people right to create a Globe of Good. We’re committed to uplifting the lives of Filipinos through wonderful experiences that open up choices, overcome challenges, and discover new ways to enjoy life. Every Ka\-Globe is empowered and inspired to create everyday possibilities—not just for themselves, but for the communities we serve.
+**Build Tomorrow, Today**
+ At Globe, tech isn’t just backend—it’s front and center of change. As a Technology \&amp; Innovation Intern, you’ll join our product squads, data experts, or security teams to help build digital experiences that reach millions. From app features to AI, you won’t just observe—you’ll create.
+**What You Could Work On**
+* Assist with software development and testing
+* Explore data insights and visualization tools
+* Support cybersecurity, DevOps, or infra projects
+* Help design user interfaces or enhance product UX
+* Collaborate on innovation sprints and solution prototyping
+**You’ll Thrive Here If You Are**
+* A problem\-solver who likes to build, test, and iterate
+* A student in Computer Science, Engineering, UX/UI, or related fields
+* Excited to learn in an agile, team\-based environment
+* Curious about AI, design thinking, and digital transformation
+**Why Join Us**
+* Work with cutting\-edge tech on real\-world products
+* Be mentored by engineers, designers, and product managers
+* Join a tech culture that encourages experimentation and play
+**What To Expect**
+ Our internship applications are open year\-round. Once you apply, you’ll be added to our talent pool. We’ll review applications and reach out when an internship opportunity that matches your skills and interests becomes available. There’s no need to wait for a fixed cycle—just apply once, and we’ve got you on our radar.
+*Make ideas happen—apply now and Create Everyday Possibilities.*
+**Equal Opportunity Employer**
+ Globe’s hiring process promotes equal opportunity to applicants, Any form of discrimination is not tolerated throughout the entire employee lifecycle, including the hiring process such as in posting vacancies, selecting, and interviewing applicants.
+ Globe’s Diversity, Equity and Inclusion Policy Commitment can be accessed here
+ Make Your Passion Part of Your Profession. Attracting the best and brightest Talents is pivotal to our success. If you are ready to share our purpose of Creating a Globe of Good, explore opportunities with us.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>IT Services and IT Consulting</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/unisys</t>
+          <t>https://ph.linkedin.com/company/globe-telecom</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>https://media.licdn.com/dms/image/v2/C4E0BAQGP5PO--smhpQ/company-logo_100_100/company-logo_100_100/0/1669644012632/unisys_logo?e=2147483647&amp;v=beta&amp;t=umb8iP0FSyszRAXDeGsJpUGK6O-4wNFoU_SMGnzdc28</t>
+          <t>https://media.licdn.com/dms/image/v2/D560BAQEjAqSiyz4dDw/company-logo_100_100/B56ZiWTzA6HUAY-/0/1754868429275/globe_telecom_logo?e=2147483647&amp;v=beta&amp;t=vXa7NfMYdKrF9YUc-et4Tw4orMLQe8npN7wdqnkiTMQ</t>
         </is>
       </c>
       <c r="X15" t="inlineStr"/>
@@ -2230,7 +2308,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>li-4363728904</t>
+          <t>li-4363394023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2240,26 +2318,28 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4363728904</t>
+          <t>https://www.linkedin.com/jobs/view/4363394023</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tech Svc Desk - L1</t>
+          <t>Field Service/Biomed Technician</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Unisys</t>
+          <t>OMNIBUS BIO-MEDICAL SYSTEMS INC.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Manila, National Capital Region, Philippines</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Hinatuan, Caraga, Philippines</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>46045</v>
+      </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>fulltime</t>
@@ -2275,47 +2355,59 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>entry level</t>
+          <t>mid-senior level</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Engineering and Information Technology</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>GlobalRecruiting@unisys.com</t>
-        </is>
-      </c>
+      <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr">
         <is>
-          <t>**What Success Looks Like In This Role**
-* Answers moderately complex questions, following guidelines and using judgment based on experience with related incidents and service requests.
-* Requests handled include support of hardware, software, client and COTS applications as well as network and user administration.
-* Escalates complex problems to other resolver teams or vendors.
-* Utilizes problem solving and analytical skills to effectively resolve challenging incidents.
-* Supports L1 agents in ongoing day to day questions related to client incidents, requests and queries.
-**You will be successful in this role if you have:**
- High School Diploma or GED required May require technical certification or Associate Degree Generally, 1\-2years’ experience in area of responsibility
- Unisys is proud to be an equal opportunity employer that considers all qualified applicants without regard to age, caste, citizenship, color, disability, family medical history, family status, ethnicity, gender, gender expression, gender identity, genetic information, marital status, national origin, parental status, pregnancy, race, religion, sex, sexual orientation, transgender status, veteran status or any other category protected by law.
- This commitment includes our efforts to provide for all those who seek to express interest in employment the opportunity to participate without barriers. If you are a US job seeker unable to review the job opportunities herein, or cannot otherwise complete your expression of interest, without additional assistance and would like to discuss a request for reasonable accommodation, please contact our Global Recruiting organization at GlobalRecruiting@unisys.com or alternatively Toll Free: 888\-560\-1782 (Prompt 4\). US job seekers can find more information about Unisys’ EEO commitment here.</t>
+          <t>* Do field work like install new biomedical equipment by establishing, adjusting, calibrating and testing performance
+* Maintain biomedical equipment by completing preventive maintenance schedules, conducting tests, following manufacturer's instruction; and troubleshooting and repairing malfunctions
+* Submit completely furnished service reports on a daily basis to the person\-in\-charge for report validation and making of calibration certificates
+* Update job knowledge by participating in educational and/or training opportunities; read technical publications; maintain personal network
+* Build good relationship with the customer
+* Attend trainings as required by the Management
+* Perform administrative tasks that are required for the process
+* Provide clerical and administrative support to the management as requested
+* Perform ad hoc task whenever necessary
+**Schedule**
+* 8 hour shift
+* Monday to Saturday
+**Supplemental Pay Types**
+* 13th month salary
+* Overtime pay
+**Willingness To Travel**
+* 100% (Required)
+* Graduate of ECE Engineering courses or TESDA Courses related to Biomedical
+* Previous work\-related experience is required
+* Ability to travel and conduct area/field work on a daily basis to perform and provide quality service to our customers/clients
+* Must possess good customer relations skills
+* Willing to be trained for months' time to further enhance the job knowledge and technical skills
+* Ability to learn new technical concepts quickly
+* Able to think clearly and provide a practical solution during a difficult situation
+**Experience**
+* Field Service/Biomed Technician: 3 years (Required)</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>IT Services and IT Consulting</t>
+          <t>Hospitals and Health Care</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/unisys</t>
+          <t>https://ph.linkedin.com/company/omnibus-bio-medical-systems-incorporated</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>https://media.licdn.com/dms/image/v2/C4E0BAQGP5PO--smhpQ/company-logo_100_100/company-logo_100_100/0/1669644012632/unisys_logo?e=2147483647&amp;v=beta&amp;t=umb8iP0FSyszRAXDeGsJpUGK6O-4wNFoU_SMGnzdc28</t>
+          <t>https://media.licdn.com/dms/image/v2/C4D0BAQFHlS1CXmkf-Q/company-logo_100_100/company-logo_100_100/0/1631323287974?e=2147483647&amp;v=beta&amp;t=DcYM2JoLES3_wIJz6vW_5Ug4YNbURd7m4mQqIysIroc</t>
         </is>
       </c>
       <c r="X16" t="inlineStr"/>
@@ -2330,6 +2422,882 @@
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>li-4363423934</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>linkedin</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4363423934</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://bossjob.com/job/marketing-internship-taguig-368491&amp;urlHash=K_xP</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Content Creation Intern</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>OneEngine Business Consultancy</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Taguig, National Capital Region, Philippines</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>internship</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>entry level</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Marketing, Public Relations, and Advertising</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>GoGym is a tech\-enabled pocket Gym which enables Filipinos to access health and wellness anywhere they go. At GoGym, we aim to provide affordable and accessible gyms to everyone, extending our reach on health and fitness into the online presence through our mobile app.
+**About The Job**
+ We are seeking a creative and data\-driven Content Creation Intern to join our team. The ideal candidate will have a passion for social media, a keen eye for design, and a strategic mindset. The intern will be responsible for creating engaging content, managing content calendars, analyzing social media performance, and assisting with Facebook Ads campaigns.
+**How To Apply**
+ Send us your:
+* updated resume or CV
+* portfolio or any material showcasing your experience in content creation, including both video and graphic content
+**Job Responsibilities**
+* Content Creation: Develop and design eye\-catching reels and static posts for Instagram and Facebook that align with our brands voice and aesthetic.
+* Content Calendar Management: Create and maintain a content calendar to strategically plan and schedule posts, ensuring a consistent and engaging presence across social media platforms.
+* Copywriting \&amp; Editing: Write compelling and on\-brand copy for social media posts, ads, and other digital content. Perform editing tasks for both written content and multimedia.
+* Graphic Design \&amp; Video Editing: Utilize Canva and basic Adobe Suite tools to create visually appealing graphics, and perform basic video editing for social media content.
+* Data Analysis: Monitor and analyze social media performance metrics such as reach, engagement, and awareness. Generate reports and propose strategies based on data insights to improve social media presence and effectiveness.
+* Facebook Ads: Assist in planning, executing, and optimizing Facebook Ads campaigns to achieve marketing objectives.
+**Job Qualifications**
+* Currently pursuing or recently completed a degree in Marketing, Communications, Graphic Design, or a related field.
+* Strong proficiency in Canva; basic knowledge of Adobe Creative Suite tools (Photoshop, Illustrator, Premiere Pro, etc.).
+* Experience with video editing software and basic video editing skills.
+* Knowledge of social media platforms, particularly Instagram and Facebook, and a strong understanding of their best practices.
+* Analytical mindset with the ability to interpret social media data and generate actionable insights.
+* Excellent communication and copywriting skills.
+* Ability to manage multiple tasks and projects with strong attention to detail.
+* Creative thinker with a passion for storytelling and visual design.
+**WHY WORK WITH US?**
+* Diversity and inclusion
+* Work\-life balance
+* Flexible working hours
+* Amazing growth opportunities
+* Competitive compensation
+* Work with a young, passionate, and friendly team
+* Free walk\-in to any GoGym branch throughout the internship period</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Business Consulting and Services and Strategic Management Services</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>https://ph.linkedin.com/company/one-engine</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D560BAQHkNGx2A0Ehiw/company-logo_100_100/B56ZcftsN4GsAQ-/0/1748583761380/one_engine_logo?e=2147483647&amp;v=beta&amp;t=lyVEVxPcvuxaGPbmfAzqljl78cQF3nLz6E9jEDEaDt0</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>li-4360394791</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>linkedin</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4360394791</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Skilled Train Maintainer/ Driver</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Northern</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Cordon, Cagayan Valley, Philippines</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="b">
+        <v>0</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>internship</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Engineering and Information Technology</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>**Business function:** 
+ Engineering
+**Grade:** 
+ STM
+**Salary:** 
+ £52,031\.00 per annum, paid at 75% during the training period
+**Hours:** 
+ 35 per week
+**Role type:** 
+ On site
+ People come to Northern for trains they can rely on. Behind every safe, clean, on\-time service is a team of engineers making sure each unit is ready to roll.
+ As part of our Engineering team, you’d play a hands\-on role in keeping our fleet moving. This is a dual\-skilled position that brings together train maintenance and depot driving, giving you real variety and a clear sense of purpose every time you step onto the depot. Whether you’re fault\-finding, servicing, or moving units to keep the plan on track, your work directly supports millions of journeys across the North.
+ You don’t need previous train driving experience. We’ll train you from the ground up, combining classroom learning with practical, on\-site experience to help you build a long\-term career in rail engineering.
+**What You’ll Be Doing**
+* Carrying out maintenance, servicing, inspections and fault\-finding on our trains, making sure they’re safe and ready for service.
+* Preparing units for daily operation, including cleaning, checks and supporting planned maintenance activities.
+* Safely moving and positioning trains around the maintenance depot to support the engineering plan.
+* Working closely with colleagues across Engineering to maintain traction and rolling stock to the highest standards.
+* Following all safety rules, procedures and working instructions, while keeping a clean, secure and well\-organised working environment.
+* Working flexibly across shifts, including nights and weekends.
+**About You**
+ Engineering know\-how, focus and the right attitude – that’s what matters here.
+ You’ll bring:
+* An NVQ Level 3 qualification in Engineering, with hands\-on experience of mechanical and electrical systems.
+* The ability to fault\-find and troubleshoot in a fast\-paced, technical environment.
+* A strong safety mindset, with the focus and concentration needed for a safety critical role.
+* Flexibility to adapt to changing maintenance and operational demands.
+* Clear communication skills and a calm, team\-first approach, even under pressure.
+* The motivation to lead by example and take pride in high\-quality work.
+* A commitment to completing our full train driver training programme and staying fully compliant.
+* No previous train driving experience is needed. You’ll begin with around six weeks of classroom\-based training in Leeds or Manchester, followed by practical training at your depot.
+**Please note:** 
+ This is a safety\-critical role and is subject to Rail Safety \&amp; Standards Board (RSSB) regulations. You must meet the following criteria or your application will be automatically rejected:
+* You live within a 45\-minute car journey of the station you’ll work from.
+* You’re at least 18 years old at the time of application.
+* You can pass a safety\-critical medical, including drugs and alcohol screening.
+* You do not have defective colour vision.
+**What’s in it for you?**
+ At Northern, we don’t just value our people \- we go the extra mile to support them. Here’s a taste of what you can look forward to:
+* Free Travel: Unlimited free travel for you, your partner, and your dependents on Northern services. Plus up to 75% discount on other networks in the UK and Europe.
+* Generous Pension Scheme: We top up your contributions by 1\.5 times.
+* Enhanced Family Benefits: We offer 9 months of full pay for maternity leave and 2 weeks for paternity leave.
+* Cycle to Work Scheme: Save up to 42% on a bike and spread the cost.
+* Exclusive Discounts: From shopping to wellbeing, Northern Perks has you covered.
+* Employee Assistance Programme: 24/7 support for family, lifestyle, and more.
+* Training and Career Development: We offer tailored training to our colleagues and opportunities to gain recognised qualifications. Plus enhanced career pathways no matter what part of the business you’re in.
+* Recognition: We know how important it is to show how much we appreciate our people. That’s why we have our Northern Lights and Northern Sparks Awards, recognising and celebrating brilliance every day.
+**Why Northern?**
+ We’re more than just a train operator. We’re the heartbeat of the North – connecting communities, creating opportunities, and driving sustainable growth. With 2,500 trains running daily, we’re on a mission to improve rail travel and enhance the customer experience while protecting the environment.
+ Back in 1825, the first passenger train set off in the North of England, after which rail quickly spread across the globe – and this year, we’re celebrating 200 years of the modern railway. As we look back on the historic events that led us here, we also look towards the future as we move into the era of Great British Rail. Join us at this pivotal moment in rail history and play your part in our journey.
+**A place for everyone**
+ The best journeys happen when everyone feels welcome on board.
+ At Northern, we don’t just move people from A to B – we’re building a team where everyone feels they belong. Our talent team can make reasonable adjustments to the process if that’s something you need. We're also a Level 2 Disability Confident employer, so if you meet the minimum criteria for the role, we’ll always offer an interview.
+ We automate parts of our screening process to remove any unconscious bias and to make sure every application is treated fairly. All successful offers will be subject to a DBS check and a medical assessment.
+ No matter your background, experience, or whether you call it a bap, barm, or cob… there’s a place for you here in the railway.</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Rail Transportation</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/northerntrains</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D4E0BAQFWmB-ZNCYtrQ/company-logo_100_100/company-logo_100_100/0/1721214046155/northerntrains_logo?e=2147483647&amp;v=beta&amp;t=j05WgVR0BbJzrw4cAugU7EF95383RONc3AoyWfgfTgA</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>li-4363392660</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>linkedin</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4363392660</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Senior FLS Technician</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>NUSTAR Resort</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Cebu, Central Visayas, Philippines</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="b">
+        <v>0</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>mid-senior level</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>**Department**
+ Fire Life Safety \&amp; STP
+**Employee Type**
+ Probationary
+**Job Responsibilities**
+* Responsible for maintaining, inspecting, testing, and repairing fire protection and life safety systems in compliance with local codes, standards, and company policies. Their role typically includes leadership or mentoring of junior technicians.
+* System Maintenance \&amp; Inspection
++ Conduct regular inspection, testing, and preventive maintenance of fire protection systems (sprinklers, alarms, extinguishers, smoke control, emergency lighting). Ensure life safety systems comply with NFPA standards and local fire codes. Identify and report deficiencies, recommending corrective actions.
+* Installation \&amp; Commissioning
++ Assist or oversee installation of fire alarm, suppression, and detection systems. Verify system functionality through acceptance testing. Coordinate with contractors and vendors during new installations or upgrades.
+* Troubleshooting \&amp; Repair
++ Diagnose and repair malfunctions in fire alarm panels, detectors, sprinklers, and emergency systems. Ensure minimal downtime of critical safety systems. Maintain accurate records of repairs, replacements, and incidents.
+* Documentation \&amp; Reporting
++ Prepare inspection reports, maintenance logs, and compliance documentation. Update system schematics and technical manuals. Provide reports for management, insurance audits, or regulatory authorities.
+* Emergency Response Support
++ Respond to fire alarm activations, system failures, or safety incidents. Support evacuation procedures and emergency drills. Ensure all safety systems function during high\-risk events.
+**Qualifications**
+* Technical Skills
++ Deep knowledge of fire alarm and life safety systems, including:
++ Fire alarms and detection systems
++ Sprinkler and suppression systems
++ Smoke control and pressurization fans
++ Emergency lighting and exit systems
++ Proficient in reading electrical schematics, blueprints, and system layouts
++ Troubleshooting, repair, and preventive maintenance expertise
++ Familiarity with NFPA, OSHA, and local fire codes
++ Use of testing and calibration tools for fire systems
+* Soft Skills
++ Strong problem\-solving and analytical skills
++ Attention to detail, especially for inspections and compliance documentation
++ Good communication skills for reporting, coordination, and training
++ Leadership and mentoring capabilities
++ Ability to work under pressure during emergency situations
+**Experience Range Range (Years)**
+ 3 \- 5 years
+**Job posted on**
+ 2026\-01\-23</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Hospitality</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>https://ph.linkedin.com/company/nustar-resort-and-casino</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D560BAQGmFGBMiqoSjg/company-logo_100_100/B56ZfAFYI9GoAQ-/0/1751274324973/nustar_resort_and_casino_logo?e=2147483647&amp;v=beta&amp;t=MOsJOwFTd4RUNsa-hS1GopB8RbiFxd5N8B-s85f4fRw</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>li-4363461493</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>linkedin</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4363461493</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Service Elevator Technician</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Fujitec Elevators &amp; Escalators</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="b">
+        <v>0</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>entry level</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Engineering and Information Technology</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>KEY FUNCTIONS:
+ • Performing Preventive Maintenance Service for Elevator and Escalator 
+ • Performing Troubleshooting and Repair work for Elevator and Escalator
+ • Performing Replacement parts work
+ • Making Service Report
+ • Deliver necessary document to a client
+ • Manage and Securing Attendance documents
+ DUTIES AND RESPONSIBILITIES:
+ SERVICE MAINTENANCE:
+ • Following the company rules and Fujitec’s standard safety rules
+ • Improve own knowledge and skills
+ • Performing Prevent Maintenance service under the supervision of the Superior and/or Department Manager 
+ • Performing Troubleshooting and repair work under the supervision of the superior and/or Department Manager
+ • Performing Replacement parts work under the supervision of the Superior and/or Department Manager 
+ • Making a service report for a client on time
+ • Explaining the status of EV/ESC, what was performed in PMS and our suggestion(if any) to a client
+ • Negotiating/discussing an issue with a client under the supervision of Superior and/or Department Manager 
+ • Corresponding Emergency call back while you are assigned as standby staff by shifting.
+ • Reporting the result of your work to your immediate superior
+ • Delivering a necessary document such as a service invoice, contract, delivery receipt and alike to person within the department.
+ • Managing your tools, keepsafing and keeping them be clean and in good condition at all times.
+ • Attend Mantrap during nighttime, holidays, weekdays, and weekends.
+ • Can be assigned in the Regional temporarily
+ • Take overtime during Saturday, Sunday, Holiday and nighttime if necessary.</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Appliances, Electrical, and Electronics Manufacturing</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>https://in.linkedin.com/company/fujitecindia</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/C510BAQHhhrkpRzf61w/company-logo_100_100/company-logo_100_100/0/1630624195976?e=2147483647&amp;v=beta&amp;t=3RjGGcLS0CS3O_OlU6giNpfCs0NDwbETdj6XJ1F_0Ys</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>li-4363451933</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>linkedin</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4363451933</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Senior ServiceNow Technical Lead - Hybrid</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Lennor Group</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Taguig, National Capital Region, Philippines</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="b">
+        <v>0</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>mid-senior level</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Our brand, Lennor Metier Consulting, a DOLE\-licensed headhunting and recruitment agency in the Philippines, is proud to partner with a
+ **global leader in tech** 
+ in their search for a
+ **Senior ServiceNow Technical Lead** 
+ to report to
+ **BGC** 
+ on a
+ **hybrid set up** 
+**.**
+**Salary:** 
+ Open
+**Work Setup** 
+ : Hybrid
+**Shift Schedule** 
+ : Day Shift
+**Location** 
+ : BGC
+**Your Responsibilities**
+* Implement of various ServiceNow modules, Complex integrations, solution using industry best practices
+* Develop ServiceNow scripting like Business Rule, Script include, Fix scripts workflows, UI Action, UI Policy, Client scripts, Email Inbound
+* Manage end to end ServiceNow platform
+* Handle Document Management and HRSD
+* Handle REST and SOAP based integration, scripted REST, and SOAP API creation
+* Take care of Authentication via Auth 2\.0, certificates and Mid Server
+* Implement ServiceNow project in Domain separated instances
+* Install and manage MID Server
+* Develop custom applications
+* Implement LDAP/Active Directory/SSO
+* Implement Orchestration use cases
+**What We're Looking For**
+* Bachelor’s degree or equivalent combination of education and experience is required
+* At least 5 years of experience in ServiceNow is required.
+* Must have at least 8 years of experience within the IT Industry.
+* Knowledge of Flow Designer, Integration Hub
+* Worked on multiple ServiceNow modules
+* Design and modification of complex integrations
+* Review existing set up and provide best practice recommendations
+* Excellent knowledge of ServiceNow Best Practices and ongoing knowledge of latest ServiceNow features.
+* Experience with HTML coding and Jelly script strongly preferred
+* Certified System Admin
+* CIS, Certified Application developer
+* ITIL Foundations certification is preferred.
+**Ready to take the next step in your career? Submit your application now!**
+* We kindly request your patience as we receive a significant number of applications. Rest assured that our team will update your application's status soon. In the meantime, we encourage you to follow our LinkedIn page to stay informed about future opportunities and company updates.</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Technology, Information and Internet</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>https://ph.linkedin.com/company/lennorgroup</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D560BAQFW5J0IFpYZBQ/company-logo_100_100/company-logo_100_100/0/1727341872086/lennorgroup_logo?e=2147483647&amp;v=beta&amp;t=zXSqTkBJ0_tYpsTbUvtgzn0-J6bSgUxUE2tOQAaJ2pA</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>li-4365752229</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>linkedin</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4365752229</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://unisys.wd5.myworkdayjobs.com/External/job/Citynet\u002d\u002d-Mandaluyong-City/Tech-Svc-Desk_REQ570072?source=LinkedIn&amp;urlHash=_-z7</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Tech Svc Desk</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Unisys</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Manila, National Capital Region, Philippines</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="b">
+        <v>0</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>entry level</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Engineering and Information Technology</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>GlobalRecruiting@unisys.com</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>**What Success Looks Like In This Role**
+* Answers moderately complex questions, following guidelines and using judgment based on experience with related incidents and service requests.
+* Requests handled include support of hardware, software, client and COTS applications as well as network and user administration.
+* Escalates complex problems to other resolver teams or vendors.
+* Utilizes problem solving and analytical skills to effectively resolve challenging incidents.
+* Supports L1 agents in ongoing day to day questions related to client incidents, requests and queries.
+**You will be successful in this role if you have:**
+ High School Diploma or GED required May require technical certification or Associate Degree Generally, 1\-2years’ experience in area of responsibility
+ Unisys is proud to be an equal opportunity employer that considers all qualified applicants without regard to age, caste, citizenship, color, disability, family medical history, family status, ethnicity, gender, gender expression, gender identity, genetic information, marital status, national origin, parental status, pregnancy, race, religion, sex, sexual orientation, transgender status, veteran status or any other category protected by law.
+ This commitment includes our efforts to provide for all those who seek to express interest in employment the opportunity to participate without barriers. If you are a US job seeker unable to review the job opportunities herein, or cannot otherwise complete your expression of interest, without additional assistance and would like to discuss a request for reasonable accommodation, please contact our Global Recruiting organization at GlobalRecruiting@unisys.com or alternatively Toll Free: 888\-560\-1782 (Prompt 4\). US job seekers can find more information about Unisys’ EEO commitment here.</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>IT Services and IT Consulting</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/unisys</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/C4E0BAQGP5PO--smhpQ/company-logo_100_100/company-logo_100_100/0/1669644012632/unisys_logo?e=2147483647&amp;v=beta&amp;t=umb8iP0FSyszRAXDeGsJpUGK6O-4wNFoU_SMGnzdc28</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>li-4290381305</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>linkedin</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4290381305</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Simulator Technician 1-EN</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>CAE</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Mabalacat, Central Luzon, Philippines</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="b">
+        <v>0</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>entry level</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Engineering and Information Technology</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>-Careers@cae.com</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>**About This Role**
+**ESSENTIAL DUTIES AND RESPONSIBILITIES**
+* Learn and perform Preventive Maintenance tasks on the simulators and associated simulator systems.
+* Assist in diagnosing and correcting problems on the simulators and associated simulator systems.
+* Utilize Maintenance Management System to record and track maintenance activities.
+* Complete all designated training activities.
+* Perform preflight and post flight on designated simulators.
+* Perform basic visual alignments.
+* Run automatic QTG's.
+* Assist with refurbishment and hardware modifications.
+* Learn and comply with CAE Quality Management System.
+* Provide customer service support and address customer needs in a timely manner.
+* Perform housekeeping functions to maintain the simulators as required.
+* Perform logistics duties, including parts received, repair, and testing/validation.
+* Perform administrative tasks as required.
+* Perform tasks to support the technical services group as required.
+**Qualifications \&amp; Skills**
+* Demonstrate ability to interpret system prints and schematics.
+* Proficiency in operating test equipment (oscilloscope, multi\-meter, signal generator, logic analyzer, etc.).
+* Knowledge in analog and digital theory.
+* Computer literate (PC and / or computer mainframe/architecture).
+* Proficiency in soldering and circuit board repairs.
+* Some Knowledge of MS\-Office tools and suite
+**Position Type**
+ Regular
+ CAE thanks all applicants for their interest. However, only those whose background and experience match the requirements of the role will be contacted.
+**Equal Opportunity Employer**
+*CAE is an equal opportunity employer committed to providing equal employment opportunities to all applicants and employees without regard to race, nationality, colour, religion, sex, gender indentity and expression, sexual orientation, disability, neurodiversity, veteran status, age, or other characteristics protected by local laws.*
+*If you don't see yourself fully reflected in every job requirement listed in the job posting, we still encourage you to reach out and apply. At CAE, everyone is welcome to contribute to our success. Applicants needing reasonable accommodations should contact their recruiter at any point in the recruitment process. If you need assistance to submit your application because of incompatible assistive technology or a disability, please contact us at* 
+ CAECarrieres\-Careers@cae.com</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Aviation and Aerospace Component Manufacturing</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/school/cae/</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>https://media.licdn.com/dms/image/v2/D560BAQGyxpIB-rWe4Q/company-logo_100_100/company-logo_100_100/0/1719806773713/cae_logo?e=2147483647&amp;v=beta&amp;t=lCKrnbpfRuy2LBBRWmFYdTE7ebAwKU3kR9uqfvsqbgg</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
